--- a/ROSALES/Septiembre/expensas rosales Septiembre.xlsx
+++ b/ROSALES/Septiembre/expensas rosales Septiembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ROSALES\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778E924E-DA65-4E6C-A636-524D49705BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7B0A7E-35F6-4BDD-B616-A96C70DA0323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$67</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$37</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="141">
   <si>
     <t>TOTAL</t>
   </si>
@@ -430,15 +430,6 @@
     <t>LAS LINEAS GRISES CORRESPONDEN A PLANES DE PAGO VIGENTES -  RESTA ABONAR 6 CUOTAS DE $107.386,20 + LAS EXPENSAS AL DIA - PARTE DE LA DEUDA CANCELA EDESUR Y EXPENSAS CON TASA DE INTERES MENSUAL</t>
   </si>
   <si>
-    <t>ADELANTO PAGO 1 - TERRAZA</t>
-  </si>
-  <si>
-    <t>COMPRA DE MATERIALES TECHO - OBRA TERRAZA</t>
-  </si>
-  <si>
-    <t>Servisur - reemplazo de dos lamparas de cochera y dos en terraza - Fuga y reparacion en circuito de escaleras y pallier</t>
-  </si>
-  <si>
     <t>}</t>
   </si>
   <si>
@@ -448,10 +439,19 @@
     <t>LIQUIDACIÓN EXPENSAS SEPTIEMBRE 2025</t>
   </si>
   <si>
-    <t>Fumigacion mes de SEPTIEMBRE</t>
-  </si>
-  <si>
     <t>EGRESOS DEL MES DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Fumigacion</t>
+  </si>
+  <si>
+    <t>Fumigacion - diferencia mes anterior</t>
+  </si>
+  <si>
+    <t>ADELANTO PAGO 2 - TERRAZA</t>
+  </si>
+  <si>
+    <t>CUOTA PLAN DE PAGOS</t>
   </si>
 </sst>
 </file>
@@ -694,7 +694,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1070,7 +1069,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1367,7 +1366,6 @@
     <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="11" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="19" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1404,18 +1402,6 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="171" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1433,12 +1419,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1460,6 +1440,8 @@
     <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="20" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1548,10 +1530,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2333625" cy="1028699"/>
     <xdr:pic>
@@ -1573,7 +1555,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3943350" y="304800"/>
+          <a:off x="3390900" y="314325"/>
           <a:ext cx="2333625" cy="1028699"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1877,17 +1859,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F69"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:F68"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1895,132 +1877,130 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>123</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="217">
+      <c r="C18" s="33">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="215">
-        <v>319589.71000000002</v>
+      <c r="C19" s="208">
+        <v>236760.8</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>129</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="209">
-        <v>571077.30000000005</v>
-      </c>
+      <c r="C20" s="208"/>
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
         <v>26</v>
       </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="217">
+      <c r="C21" s="33">
         <v>75000</v>
       </c>
       <c r="D21" s="20"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
         <v>128</v>
       </c>
       <c r="B22" s="39"/>
-      <c r="C22" s="217">
+      <c r="C22" s="33">
         <v>14856</v>
       </c>
       <c r="D22" s="20"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
         <v>11</v>
       </c>
@@ -2036,22 +2016,22 @@
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="40"/>
       <c r="B24" s="41"/>
       <c r="C24" s="23">
         <f>SUM(C17:C23)</f>
-        <v>1140577.01</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+        <v>486670.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="35" t="s">
         <v>12</v>
       </c>
       <c r="B25" s="39"/>
       <c r="C25" s="178"/>
     </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
         <v>114</v>
       </c>
@@ -2063,329 +2043,319 @@
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
         <v>115</v>
       </c>
       <c r="B27" s="42"/>
-      <c r="C27" s="217">
+      <c r="C27" s="33">
         <v>5684</v>
       </c>
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="227" t="s">
-        <v>135</v>
-      </c>
-      <c r="B28" s="228"/>
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="176" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="140"/>
       <c r="C28" s="33">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="D28" s="45"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="218"/>
-      <c r="B29" s="219"/>
-      <c r="C29" s="220">
-        <v>30000</v>
-      </c>
-      <c r="D29" s="45"/>
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B29" s="42"/>
+      <c r="C29" s="33">
+        <v>55000</v>
+      </c>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="176" t="s">
-        <v>125</v>
-      </c>
-      <c r="B30" s="140"/>
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" s="42"/>
       <c r="C30" s="33">
-        <v>49940</v>
-      </c>
-      <c r="D30" s="45"/>
+        <v>10000</v>
+      </c>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="217">
-        <v>55000</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="B31" s="39"/>
+      <c r="C31" s="34">
+        <f>1500000-941421.86</f>
+        <v>558578.14</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="6"/>
       <c r="F31" s="12"/>
     </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="B32" s="39"/>
-      <c r="C32" s="34">
-        <v>300000</v>
-      </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="6"/>
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="40"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="23">
+        <f>SUM(C25:C31)</f>
+        <v>1013329.1969999999</v>
+      </c>
       <c r="F32" s="12"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="40"/>
-      <c r="B33" s="41"/>
-      <c r="C33" s="23">
-        <f>SUM(C25:C32)</f>
-        <v>974691.05700000003</v>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="30"/>
+      <c r="C33" s="43">
+        <f>+C32+C24</f>
+        <v>1499999.997</v>
       </c>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="30"/>
-      <c r="C34" s="43">
-        <f>+C33+C24</f>
-        <v>2115268.0669999998</v>
-      </c>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C34" s="24"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>18</v>
+      </c>
       <c r="C35" s="24"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" s="24"/>
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="28"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="33"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="28"/>
       <c r="B37" s="28"/>
-      <c r="C37" s="33"/>
+      <c r="C37" s="34"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="28"/>
       <c r="B38" s="28"/>
       <c r="C38" s="34"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="28"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="34"/>
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C39" s="25"/>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C40" s="25"/>
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="179" t="s">
+        <v>131</v>
+      </c>
+      <c r="B40" s="179"/>
+      <c r="C40" s="180"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="179" t="s">
-        <v>131</v>
-      </c>
-      <c r="B41" s="179"/>
-      <c r="C41" s="180"/>
+    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C41" s="25"/>
       <c r="F41" s="12"/>
     </row>
-    <row r="42" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C42" s="25"/>
-      <c r="F42" s="12"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="13" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="14">
-        <f>+C37+C38+C39+C42</f>
-        <v>0</v>
-      </c>
-      <c r="E43" s="6"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="18" t="s">
+      <c r="B42" s="13"/>
+      <c r="C42" s="14">
+        <f>+C36+C37+C38+C41</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="6"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B45" s="18"/>
-      <c r="C45" s="19">
-        <f>+C43+C34</f>
-        <v>2115268.0669999998</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="225" t="s">
+      <c r="B44" s="18"/>
+      <c r="C44" s="19">
+        <f>+C42+C33</f>
+        <v>1499999.997</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="218" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="226"/>
-      <c r="C47" s="226"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="226"/>
-      <c r="B48" s="226"/>
-      <c r="C48" s="226"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="226"/>
-      <c r="B49" s="226"/>
-      <c r="C49" s="226"/>
-    </row>
-    <row r="50" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="226"/>
-      <c r="B50" s="226"/>
-      <c r="C50" s="226"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-    </row>
-    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="4"/>
-      <c r="C51" s="157"/>
+      <c r="B46" s="219"/>
+      <c r="C46" s="219"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="219"/>
+      <c r="B47" s="219"/>
+      <c r="C47" s="219"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="219"/>
+      <c r="B48" s="219"/>
+      <c r="C48" s="219"/>
+    </row>
+    <row r="49" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="219"/>
+      <c r="B49" s="219"/>
+      <c r="C49" s="219"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+    </row>
+    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4"/>
+      <c r="C50" s="157"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="210" t="s">
+        <v>117</v>
+      </c>
+      <c r="B51" s="28"/>
+      <c r="C51" s="211">
+        <v>675304.75117282523</v>
+      </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="211" t="s">
-        <v>117</v>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="210" t="s">
+        <v>136</v>
       </c>
       <c r="B52" s="28"/>
-      <c r="C52" s="212">
-        <v>629534.61</v>
+      <c r="C52" s="31">
+        <f>-(C33-C31)</f>
+        <v>-941421.85699999996</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="211" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="210" t="s">
+        <v>113</v>
+      </c>
+      <c r="B53" s="28"/>
+      <c r="C53" s="212">
+        <f>'prorrateo '!F31</f>
+        <v>2045051.5300000003</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="210" t="s">
         <v>140</v>
       </c>
-      <c r="B53" s="28"/>
-      <c r="C53" s="31">
-        <f>-(C34-C32)</f>
-        <v>-1815268.0669999998</v>
-      </c>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="211" t="s">
-        <v>113</v>
-      </c>
       <c r="B54" s="28"/>
-      <c r="C54" s="213">
-        <f>'prorrateo '!F31</f>
-        <v>2538562.2581728254</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="211" t="s">
-        <v>134</v>
+      <c r="C54" s="212">
+        <v>107386.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="210" t="s">
+        <v>139</v>
       </c>
       <c r="B55" s="28"/>
-      <c r="C55" s="214">
-        <v>-307000</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="211" t="s">
-        <v>133</v>
+      <c r="C55" s="213">
+        <v>-376000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="210" t="s">
+        <v>8</v>
       </c>
       <c r="B56" s="28"/>
-      <c r="C56" s="214">
-        <v>-400000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="211" t="s">
-        <v>8</v>
-      </c>
-      <c r="B57" s="28"/>
-      <c r="C57" s="212">
-        <f>SUM(C50:C56)</f>
-        <v>645828.80117282551</v>
-      </c>
-      <c r="D57" s="5"/>
-    </row>
-    <row r="58" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="9"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="10"/>
-    </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="221"/>
-      <c r="B59" s="221"/>
-      <c r="C59" s="221"/>
-      <c r="F59" s="44"/>
-    </row>
-    <row r="60" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="222"/>
-      <c r="B60" s="222"/>
-      <c r="C60" s="222"/>
-    </row>
-    <row r="61" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="26" t="s">
+      <c r="C56" s="211">
+        <f>SUM(C49:C55)</f>
+        <v>1510320.6241728256</v>
+      </c>
+      <c r="D56" s="5"/>
+    </row>
+    <row r="57" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="9"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="10"/>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="214"/>
+      <c r="B58" s="214"/>
+      <c r="C58" s="214"/>
+      <c r="F58" s="44"/>
+    </row>
+    <row r="59" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="215"/>
+      <c r="B59" s="215"/>
+      <c r="C59" s="215"/>
+    </row>
+    <row r="60" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B61" s="27"/>
-      <c r="C61" s="29"/>
-    </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="28" t="s">
+      <c r="B60" s="27"/>
+      <c r="C60" s="29"/>
+    </row>
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="28" t="s">
         <v>24</v>
       </c>
+      <c r="B61" s="28"/>
+      <c r="C61" s="31">
+        <f>-C42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="28"/>
       <c r="B62" s="28"/>
-      <c r="C62" s="31">
-        <f>-C43</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C62" s="31"/>
+    </row>
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="28"/>
       <c r="B63" s="28"/>
-      <c r="C63" s="31"/>
-    </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="28"/>
-      <c r="B64" s="28"/>
-      <c r="C64" s="32"/>
-    </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="158" t="s">
-        <v>0</v>
-      </c>
-      <c r="B65" s="159"/>
-      <c r="C65" s="160">
-        <f>SUM(C61:C64)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="223" t="s">
+      <c r="C63" s="32"/>
+    </row>
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="158" t="s">
+        <v>0</v>
+      </c>
+      <c r="B64" s="159"/>
+      <c r="C64" s="160">
+        <f>SUM(C60:C63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="216" t="s">
         <v>127</v>
       </c>
-      <c r="B66" s="224"/>
-      <c r="C66" s="224"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="224"/>
-      <c r="B67" s="224"/>
-      <c r="C67" s="224"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="224"/>
-      <c r="B68" s="224"/>
-      <c r="C68" s="224"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
+      <c r="B65" s="217"/>
+      <c r="C65" s="217"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="217"/>
+      <c r="B66" s="217"/>
+      <c r="C66" s="217"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="217"/>
+      <c r="B67" s="217"/>
+      <c r="C67" s="217"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A59:C60"/>
-    <mergeCell ref="A66:C68"/>
-    <mergeCell ref="A47:C50"/>
-    <mergeCell ref="A28:B28"/>
+  <mergeCells count="3">
+    <mergeCell ref="A58:C59"/>
+    <mergeCell ref="A65:C67"/>
+    <mergeCell ref="A46:C49"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <hyperlinks>
@@ -2393,7 +2363,7 @@
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="82" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="87" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
@@ -2404,43 +2374,42 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="0.109375" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="11"/>
+    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="0.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="11"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="229" t="str">
-        <f>D1</f>
-        <v>}</v>
-      </c>
-      <c r="C1" s="229"/>
+      <c r="B1" s="220">
+        <v>1500000</v>
+      </c>
+      <c r="C1" s="220"/>
       <c r="D1" s="141" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E1" t="s">
         <v>119</v>
       </c>
-      <c r="G1" s="231"/>
-      <c r="H1" s="231"/>
-    </row>
-    <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G1" s="222"/>
+      <c r="H1" s="222"/>
+    </row>
+    <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
         <v>27</v>
       </c>
@@ -2462,7 +2431,7 @@
       <c r="G2" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="210" t="s">
+      <c r="H2" s="209" t="s">
         <v>109</v>
       </c>
       <c r="I2" s="50" t="s">
@@ -2478,7 +2447,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
         <v>32</v>
       </c>
@@ -2492,11 +2461,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E3" s="131">
-        <v>124487.04578100001</v>
+        <v>106583.98</v>
       </c>
       <c r="F3" s="177">
         <f>E3</f>
-        <v>124487.04578100001</v>
+        <v>106583.98</v>
       </c>
       <c r="G3" s="56">
         <f>E3-F3</f>
@@ -2506,21 +2475,21 @@
         <f>IF(G3&gt;0,G3*4%,0)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="56" t="e">
+      <c r="I3" s="56">
         <f>B$1*D3/100</f>
-        <v>#VALUE!</v>
+        <v>76650.000000000015</v>
       </c>
       <c r="J3" s="56">
         <f>G$1*D3/100</f>
         <v>0</v>
       </c>
       <c r="K3" s="56"/>
-      <c r="L3" s="57" t="e">
+      <c r="L3" s="57">
         <f>I3+G3+K3+J3+H3</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+        <v>76650.000000000015</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
         <v>34</v>
       </c>
@@ -2534,11 +2503,11 @@
         <v>5.09</v>
       </c>
       <c r="E4" s="131">
-        <v>123999.816639</v>
+        <v>106166.82</v>
       </c>
       <c r="F4" s="177">
-        <f t="shared" ref="F4:F18" si="0">E4</f>
-        <v>123999.816639</v>
+        <f t="shared" ref="F4:F12" si="0">E4</f>
+        <v>106166.82</v>
       </c>
       <c r="G4" s="56">
         <f t="shared" ref="G4:G29" si="1">E4-F4</f>
@@ -2548,21 +2517,21 @@
         <f t="shared" ref="H4:H29" si="2">IF(G4&gt;0,G4*4%,0)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="56" t="e">
+      <c r="I4" s="56">
         <f t="shared" ref="I4:I29" si="3">B$1*D4/100</f>
-        <v>#VALUE!</v>
+        <v>76350</v>
       </c>
       <c r="J4" s="56">
         <f t="shared" ref="J4:J29" si="4">G$1*D4/100</f>
         <v>0</v>
       </c>
       <c r="K4" s="56"/>
-      <c r="L4" s="57" t="e">
+      <c r="L4" s="57">
         <f t="shared" ref="L4:L29" si="5">I4+G4+K4+J4+H4</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+        <v>76350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>36</v>
       </c>
@@ -2576,35 +2545,35 @@
         <v>5.04</v>
       </c>
       <c r="E5" s="131">
-        <v>241472.783784</v>
+        <v>251925.51</v>
       </c>
       <c r="F5" s="177">
-        <f>E5-141155.37</f>
-        <v>100317.413784</v>
+        <f>132535-F23</f>
+        <v>110008.45</v>
       </c>
       <c r="G5" s="56">
         <f t="shared" si="1"/>
-        <v>141155.37</v>
+        <v>141917.06</v>
       </c>
       <c r="H5" s="56">
         <f t="shared" si="2"/>
-        <v>5646.2147999999997</v>
-      </c>
-      <c r="I5" s="56" t="e">
+        <v>5676.6823999999997</v>
+      </c>
+      <c r="I5" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>75600</v>
       </c>
       <c r="J5" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K5" s="56"/>
-      <c r="L5" s="57" t="e">
+      <c r="L5" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+        <v>223193.74239999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="58" t="s">
         <v>39</v>
       </c>
@@ -2616,11 +2585,11 @@
         <v>5.21</v>
       </c>
       <c r="E6" s="131">
-        <v>126923.19149100001</v>
+        <v>108669.77</v>
       </c>
       <c r="F6" s="177">
         <f>E6</f>
-        <v>126923.19149100001</v>
+        <v>108669.77</v>
       </c>
       <c r="G6" s="56">
         <f t="shared" si="1"/>
@@ -2630,22 +2599,22 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I6" s="56" t="e">
+      <c r="I6" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>78150</v>
       </c>
       <c r="J6" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K6" s="56"/>
-      <c r="L6" s="57" t="e">
+      <c r="L6" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
+        <v>78150</v>
       </c>
       <c r="O6" s="182"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>36</v>
       </c>
@@ -2659,11 +2628,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E7" s="131">
-        <v>124487.04578100001</v>
+        <v>106583.98</v>
       </c>
       <c r="F7" s="177">
         <f>E7</f>
-        <v>124487.04578100001</v>
+        <v>106583.98</v>
       </c>
       <c r="G7" s="56">
         <f t="shared" si="1"/>
@@ -2673,22 +2642,22 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I7" s="56" t="e">
+      <c r="I7" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>76650.000000000015</v>
       </c>
       <c r="J7" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K7" s="56"/>
-      <c r="L7" s="57" t="e">
+      <c r="L7" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
+        <v>76650.000000000015</v>
       </c>
       <c r="O7" s="182"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
         <v>42</v>
       </c>
@@ -2700,11 +2669,11 @@
         <v>5.09</v>
       </c>
       <c r="E8" s="131">
-        <v>123999.816639</v>
+        <v>106166.82</v>
       </c>
       <c r="F8" s="177">
         <f>E8</f>
-        <v>123999.816639</v>
+        <v>106166.82</v>
       </c>
       <c r="G8" s="56">
         <f t="shared" si="1"/>
@@ -2714,21 +2683,21 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I8" s="56" t="e">
+      <c r="I8" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>76350</v>
       </c>
       <c r="J8" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K8" s="56"/>
-      <c r="L8" s="57" t="e">
+      <c r="L8" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+        <v>76350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>44</v>
       </c>
@@ -2740,11 +2709,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E9" s="131">
-        <v>124487.04578100001</v>
+        <v>106583.98</v>
       </c>
       <c r="F9" s="177">
-        <f t="shared" si="0"/>
-        <v>124487.04578100001</v>
+        <f>E9</f>
+        <v>106583.98</v>
       </c>
       <c r="G9" s="56">
         <f t="shared" si="1"/>
@@ -2754,22 +2723,22 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I9" s="56" t="e">
+      <c r="I9" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>76650.000000000015</v>
       </c>
       <c r="J9" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K9" s="56"/>
-      <c r="L9" s="57" t="e">
+      <c r="L9" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
+        <v>76650.000000000015</v>
       </c>
       <c r="O9" s="182"/>
     </row>
-    <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="185" t="s">
         <v>46</v>
       </c>
@@ -2783,32 +2752,32 @@
         <v>5.09</v>
       </c>
       <c r="E10" s="189">
-        <v>123999.816639</v>
-      </c>
-      <c r="F10" s="190">
+        <v>106166.82</v>
+      </c>
+      <c r="F10" s="228">
         <f>E10</f>
-        <v>123999.816639</v>
-      </c>
-      <c r="G10" s="191">
+        <v>106166.82</v>
+      </c>
+      <c r="G10" s="190">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H10" s="191"/>
-      <c r="I10" s="191" t="e">
+      <c r="H10" s="190"/>
+      <c r="I10" s="190">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J10" s="191">
+        <v>76350</v>
+      </c>
+      <c r="J10" s="190">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K10" s="191"/>
-      <c r="L10" s="192" t="e">
+      <c r="K10" s="190"/>
+      <c r="L10" s="191">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+        <v>76350</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>112</v>
       </c>
@@ -2820,11 +2789,11 @@
         <v>5.04</v>
       </c>
       <c r="E11" s="131">
-        <v>122781.74378399999</v>
+        <v>105123.92</v>
       </c>
       <c r="F11" s="177">
         <f>E11</f>
-        <v>122781.74378399999</v>
+        <v>105123.92</v>
       </c>
       <c r="G11" s="56">
         <f t="shared" si="1"/>
@@ -2834,21 +2803,21 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I11" s="56" t="e">
+      <c r="I11" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>75600</v>
       </c>
       <c r="J11" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K11" s="56"/>
-      <c r="L11" s="57" t="e">
+      <c r="L11" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+        <v>75600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
         <v>49</v>
       </c>
@@ -2860,11 +2829,11 @@
         <v>5.21</v>
       </c>
       <c r="E12" s="131">
-        <v>126923.19149100001</v>
+        <v>108669.77</v>
       </c>
       <c r="F12" s="177">
         <f t="shared" si="0"/>
-        <v>126923.19149100001</v>
+        <v>108669.77</v>
       </c>
       <c r="G12" s="56">
         <f t="shared" si="1"/>
@@ -2874,21 +2843,21 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I12" s="56" t="e">
+      <c r="I12" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>78150</v>
       </c>
       <c r="J12" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K12" s="56"/>
-      <c r="L12" s="57" t="e">
+      <c r="L12" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+        <v>78150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>51</v>
       </c>
@@ -2902,11 +2871,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E13" s="131">
-        <v>124487.04578100001</v>
+        <v>106583.98</v>
       </c>
       <c r="F13" s="177">
-        <f t="shared" si="0"/>
-        <v>124487.04578100001</v>
+        <f>E13</f>
+        <v>106583.98</v>
       </c>
       <c r="G13" s="56">
         <f t="shared" si="1"/>
@@ -2916,25 +2885,25 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I13" s="56" t="e">
+      <c r="I13" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>76650.000000000015</v>
       </c>
       <c r="J13" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K13" s="56"/>
-      <c r="L13" s="57" t="e">
+      <c r="L13" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+        <v>76650.000000000015</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="208" t="s">
+      <c r="B14" s="207" t="s">
         <v>124</v>
       </c>
       <c r="C14" s="65" t="s">
@@ -2944,35 +2913,32 @@
         <v>5.09</v>
       </c>
       <c r="E14" s="131">
-        <v>374456.40098510444</v>
-      </c>
-      <c r="F14" s="177">
-        <f>E14</f>
-        <v>374456.40098510444</v>
-      </c>
+        <v>106166.82</v>
+      </c>
+      <c r="F14" s="177"/>
       <c r="G14" s="66">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>106166.82</v>
       </c>
       <c r="H14" s="66">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="66" t="e">
+        <v>4246.6728000000003</v>
+      </c>
+      <c r="I14" s="66">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>76350</v>
       </c>
       <c r="J14" s="66">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K14" s="66"/>
-      <c r="L14" s="184" t="e">
+      <c r="L14" s="184">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+        <v>186763.49280000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>55</v>
       </c>
@@ -2986,32 +2952,35 @@
         <v>5.04</v>
       </c>
       <c r="E15" s="131">
-        <v>383275.49139613437</v>
-      </c>
-      <c r="F15" s="177"/>
+        <v>503730.43</v>
+      </c>
+      <c r="F15" s="177">
+        <f>447039-F29</f>
+        <v>339096.76</v>
+      </c>
       <c r="G15" s="56">
         <f t="shared" si="1"/>
-        <v>383275.49139613437</v>
+        <v>164633.66999999998</v>
       </c>
       <c r="H15" s="56">
         <f t="shared" si="2"/>
-        <v>15331.019655845375</v>
-      </c>
-      <c r="I15" s="56" t="e">
+        <v>6585.3467999999993</v>
+      </c>
+      <c r="I15" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>75600</v>
       </c>
       <c r="J15" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K15" s="56"/>
-      <c r="L15" s="57" t="e">
+      <c r="L15" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+        <v>246819.01679999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
         <v>58</v>
       </c>
@@ -3025,11 +2994,11 @@
         <v>5.21</v>
       </c>
       <c r="E16" s="131">
-        <v>126923.19149100001</v>
+        <v>108669.77</v>
       </c>
       <c r="F16" s="177">
         <f>E16</f>
-        <v>126923.19149100001</v>
+        <v>108669.77</v>
       </c>
       <c r="G16" s="56">
         <f t="shared" si="1"/>
@@ -3039,21 +3008,21 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I16" s="56" t="e">
+      <c r="I16" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>78150</v>
       </c>
       <c r="J16" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K16" s="56"/>
-      <c r="L16" s="57" t="e">
+      <c r="L16" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>78150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>61</v>
       </c>
@@ -3065,35 +3034,32 @@
         <v>5.04</v>
       </c>
       <c r="E17" s="131">
-        <v>122781.74378399999</v>
-      </c>
-      <c r="F17" s="177">
-        <f t="shared" si="0"/>
-        <v>122781.74378399999</v>
-      </c>
+        <v>105123.92</v>
+      </c>
+      <c r="F17" s="177"/>
       <c r="G17" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>105123.92</v>
       </c>
       <c r="H17" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="56" t="e">
+        <v>4204.9567999999999</v>
+      </c>
+      <c r="I17" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>75600</v>
       </c>
       <c r="J17" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="56"/>
-      <c r="L17" s="57" t="e">
+      <c r="L17" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>184928.87679999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="62" t="s">
         <v>63</v>
       </c>
@@ -3105,35 +3071,32 @@
         <v>5.21</v>
       </c>
       <c r="E18" s="131">
-        <v>126923.19149100001</v>
-      </c>
-      <c r="F18" s="177">
-        <f t="shared" si="0"/>
-        <v>126923.19149100001</v>
-      </c>
+        <v>108669.77</v>
+      </c>
+      <c r="F18" s="177"/>
       <c r="G18" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>108669.77</v>
       </c>
       <c r="H18" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="56" t="e">
+        <v>4346.7908000000007</v>
+      </c>
+      <c r="I18" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>78150</v>
       </c>
       <c r="J18" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K18" s="56"/>
-      <c r="L18" s="57" t="e">
+      <c r="L18" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+        <v>191166.56080000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>65</v>
       </c>
@@ -3145,11 +3108,11 @@
         <v>7.4</v>
       </c>
       <c r="E19" s="131">
-        <v>180274.78253999999</v>
+        <v>154348.62</v>
       </c>
       <c r="F19" s="177">
         <f>E19</f>
-        <v>180274.78253999999</v>
+        <v>154348.62</v>
       </c>
       <c r="G19" s="56">
         <f t="shared" si="1"/>
@@ -3159,22 +3122,22 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I19" s="56" t="e">
+      <c r="I19" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>111000</v>
       </c>
       <c r="J19" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K19" s="56"/>
-      <c r="L19" s="57" t="e">
+      <c r="L19" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="24" x14ac:dyDescent="0.3">
-      <c r="A20" s="193"/>
+        <v>111000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="24" x14ac:dyDescent="0.25">
+      <c r="A20" s="192"/>
       <c r="B20" s="186" t="s">
         <v>116</v>
       </c>
@@ -3185,32 +3148,32 @@
         <v>1.08</v>
       </c>
       <c r="E20" s="189">
-        <v>26310.37</v>
-      </c>
-      <c r="F20" s="190">
+        <v>22526.55</v>
+      </c>
+      <c r="F20" s="228">
         <f>E20</f>
-        <v>26310.37</v>
-      </c>
-      <c r="G20" s="191">
+        <v>22526.55</v>
+      </c>
+      <c r="G20" s="190">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H20" s="191"/>
-      <c r="I20" s="191" t="e">
+      <c r="H20" s="190"/>
+      <c r="I20" s="190">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J20" s="191">
+        <v>16200</v>
+      </c>
+      <c r="J20" s="190">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K20" s="191"/>
-      <c r="L20" s="192" t="e">
+      <c r="K20" s="190"/>
+      <c r="L20" s="191">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="64"/>
       <c r="B21" s="59" t="s">
         <v>59</v>
@@ -3222,11 +3185,11 @@
         <v>1.08</v>
       </c>
       <c r="E21" s="131">
-        <v>26310.373668</v>
+        <v>22526.55</v>
       </c>
       <c r="F21" s="177">
         <f>E21</f>
-        <v>26310.373668</v>
+        <v>22526.55</v>
       </c>
       <c r="G21" s="56">
         <f t="shared" si="1"/>
@@ -3236,21 +3199,21 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I21" s="56" t="e">
+      <c r="I21" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>16200</v>
       </c>
       <c r="J21" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K21" s="66"/>
-      <c r="L21" s="57" t="e">
+      <c r="L21" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="142"/>
       <c r="B22" s="143"/>
       <c r="C22" s="144" t="s">
@@ -3260,34 +3223,34 @@
         <v>1.08</v>
       </c>
       <c r="E22" s="146">
-        <v>163371.97459218031</v>
+        <v>192433.41</v>
       </c>
       <c r="F22" s="181">
         <v>0</v>
       </c>
       <c r="G22" s="147">
         <f t="shared" si="1"/>
-        <v>163371.97459218031</v>
+        <v>192433.41</v>
       </c>
       <c r="H22" s="147">
         <f t="shared" si="2"/>
-        <v>6534.8789836872129</v>
-      </c>
-      <c r="I22" s="147" t="e">
+        <v>7697.3364000000001</v>
+      </c>
+      <c r="I22" s="147">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>16200</v>
       </c>
       <c r="J22" s="147">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K22" s="147"/>
-      <c r="L22" s="148" t="e">
+      <c r="L22" s="148">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>216330.7464</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="58"/>
       <c r="B23" s="59" t="s">
         <v>37</v>
@@ -3299,11 +3262,11 @@
         <v>1.08</v>
       </c>
       <c r="E23" s="131">
-        <v>48774.373668</v>
+        <v>22526.55</v>
       </c>
       <c r="F23" s="177">
         <f>E23</f>
-        <v>48774.373668</v>
+        <v>22526.55</v>
       </c>
       <c r="G23" s="56">
         <f t="shared" si="1"/>
@@ -3313,21 +3276,21 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I23" s="56" t="e">
+      <c r="I23" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>16200</v>
       </c>
       <c r="J23" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K23" s="56"/>
-      <c r="L23" s="57" t="e">
+      <c r="L23" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>51</v>
       </c>
@@ -3341,11 +3304,11 @@
         <v>1.08</v>
       </c>
       <c r="E24" s="131">
-        <v>26310.373668</v>
+        <v>22526.55</v>
       </c>
       <c r="F24" s="177">
         <f t="shared" ref="F24" si="6">E24</f>
-        <v>26310.373668</v>
+        <v>22526.55</v>
       </c>
       <c r="G24" s="56">
         <f t="shared" si="1"/>
@@ -3355,25 +3318,27 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I24" s="56" t="e">
+      <c r="I24" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>16200</v>
       </c>
       <c r="J24" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K24" s="56"/>
-      <c r="L24" s="57" t="e">
+      <c r="L24" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="59"/>
+      <c r="B25" s="207" t="s">
+        <v>124</v>
+      </c>
       <c r="C25" s="60" t="s">
         <v>72</v>
       </c>
@@ -3381,35 +3346,32 @@
         <v>1.08</v>
       </c>
       <c r="E25" s="131">
-        <v>53673.162282719997</v>
-      </c>
-      <c r="F25" s="177">
-        <f>E25</f>
-        <v>53673.162282719997</v>
-      </c>
+        <v>22526.55</v>
+      </c>
+      <c r="F25" s="177"/>
       <c r="G25" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22526.55</v>
       </c>
       <c r="H25" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="56" t="e">
+        <v>901.06200000000001</v>
+      </c>
+      <c r="I25" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>16200</v>
       </c>
       <c r="J25" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K25" s="56"/>
-      <c r="L25" s="57" t="e">
+      <c r="L25" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>39627.612000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
         <v>65</v>
       </c>
@@ -3421,11 +3383,11 @@
         <v>1.08</v>
       </c>
       <c r="E26" s="131">
-        <v>26310.373668</v>
+        <v>22526.55</v>
       </c>
       <c r="F26" s="177">
         <f t="shared" ref="F26:F28" si="7">E26</f>
-        <v>26310.373668</v>
+        <v>22526.55</v>
       </c>
       <c r="G26" s="56">
         <f t="shared" si="1"/>
@@ -3435,21 +3397,21 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I26" s="56" t="e">
+      <c r="I26" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>16200</v>
       </c>
       <c r="J26" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K26" s="56"/>
-      <c r="L26" s="57" t="e">
+      <c r="L26" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>65</v>
       </c>
@@ -3461,11 +3423,11 @@
         <v>1.08</v>
       </c>
       <c r="E27" s="131">
-        <v>26310.373668</v>
+        <v>22526.55</v>
       </c>
       <c r="F27" s="177">
         <f t="shared" si="7"/>
-        <v>26310.373668</v>
+        <v>22526.55</v>
       </c>
       <c r="G27" s="56">
         <f t="shared" si="1"/>
@@ -3475,25 +3437,25 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I27" s="56" t="e">
+      <c r="I27" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>16200</v>
       </c>
       <c r="J27" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K27" s="56"/>
-      <c r="L27" s="57" t="e">
+      <c r="L27" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
+        <v>16200</v>
       </c>
       <c r="O27" s="44">
         <f>F27+F26+F19</f>
-        <v>232895.52987599999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>199401.72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="68"/>
       <c r="B28" s="67" t="str">
         <f>B7</f>
@@ -3506,11 +3468,11 @@
         <v>1.08</v>
       </c>
       <c r="E28" s="131">
-        <v>26310.373668</v>
+        <v>22526.55</v>
       </c>
       <c r="F28" s="177">
         <f t="shared" si="7"/>
-        <v>26310.373668</v>
+        <v>22526.55</v>
       </c>
       <c r="G28" s="56">
         <f t="shared" si="1"/>
@@ -3520,21 +3482,21 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I28" s="56" t="e">
+      <c r="I28" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>16200</v>
       </c>
       <c r="J28" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K28" s="56"/>
-      <c r="L28" s="57" t="e">
+      <c r="L28" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="68" t="s">
         <v>55</v>
       </c>
@@ -3548,32 +3510,35 @@
         <v>1.08</v>
       </c>
       <c r="E29" s="131">
-        <v>82130.462442028787</v>
-      </c>
-      <c r="F29" s="177"/>
+        <v>107942.24</v>
+      </c>
+      <c r="F29" s="177">
+        <f>E29</f>
+        <v>107942.24</v>
+      </c>
       <c r="G29" s="56">
         <f t="shared" si="1"/>
-        <v>82130.462442028787</v>
+        <v>0</v>
       </c>
       <c r="H29" s="56">
         <f t="shared" si="2"/>
-        <v>3285.2184976811513</v>
-      </c>
-      <c r="I29" s="56" t="e">
+        <v>0</v>
+      </c>
+      <c r="I29" s="56">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>16200</v>
       </c>
       <c r="J29" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K29" s="56"/>
-      <c r="L29" s="57" t="e">
+      <c r="L29" s="57">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="69"/>
       <c r="B30" s="69"/>
       <c r="C30" s="70"/>
@@ -3587,7 +3552,7 @@
       <c r="K30" s="73"/>
       <c r="L30" s="73"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="74"/>
       <c r="B31" s="75"/>
       <c r="C31" s="76" t="s">
@@ -3600,86 +3565,86 @@
       <c r="E31" s="75"/>
       <c r="F31" s="137">
         <f>SUM(F3:F30)</f>
-        <v>2538562.2581728254</v>
+        <v>2045051.5300000003</v>
       </c>
       <c r="G31" s="77"/>
       <c r="H31" s="77"/>
-      <c r="I31" s="138" t="e">
+      <c r="I31" s="138">
         <f>SUM(I3:I30)</f>
-        <v>#VALUE!</v>
+        <v>1500000</v>
       </c>
       <c r="J31" s="138">
         <f>SUM(J3:J30)</f>
         <v>0</v>
       </c>
       <c r="K31" s="137"/>
-      <c r="L31" s="137" t="e">
+      <c r="L31" s="137">
         <f>SUM(L3:L29)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2375130.048</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J32" s="22"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="230" t="s">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="221" t="s">
         <v>132</v>
       </c>
-      <c r="B33" s="230"/>
-      <c r="C33" s="230"/>
-      <c r="D33" s="230"/>
-      <c r="E33" s="230"/>
-      <c r="F33" s="230"/>
-      <c r="G33" s="230"/>
-      <c r="H33" s="230"/>
-      <c r="I33" s="230"/>
-      <c r="J33" s="230"/>
-      <c r="K33" s="230"/>
-      <c r="L33" s="230"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="230"/>
-      <c r="B34" s="230"/>
-      <c r="C34" s="230"/>
-      <c r="D34" s="230"/>
-      <c r="E34" s="230"/>
-      <c r="F34" s="230"/>
-      <c r="G34" s="230"/>
-      <c r="H34" s="230"/>
-      <c r="I34" s="230"/>
-      <c r="J34" s="230"/>
-      <c r="K34" s="230"/>
-      <c r="L34" s="230"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="230"/>
-      <c r="B35" s="230"/>
-      <c r="C35" s="230"/>
-      <c r="D35" s="230"/>
-      <c r="E35" s="230"/>
-      <c r="F35" s="230"/>
-      <c r="G35" s="230"/>
-      <c r="H35" s="230"/>
-      <c r="I35" s="230"/>
-      <c r="J35" s="230"/>
-      <c r="K35" s="230"/>
-      <c r="L35" s="230"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="230"/>
-      <c r="B36" s="230"/>
-      <c r="C36" s="230"/>
-      <c r="D36" s="230"/>
-      <c r="E36" s="230"/>
-      <c r="F36" s="230"/>
-      <c r="G36" s="230"/>
-      <c r="H36" s="230"/>
-      <c r="I36" s="230"/>
-      <c r="J36" s="230"/>
-      <c r="K36" s="230"/>
-      <c r="L36" s="230"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B33" s="221"/>
+      <c r="C33" s="221"/>
+      <c r="D33" s="221"/>
+      <c r="E33" s="221"/>
+      <c r="F33" s="221"/>
+      <c r="G33" s="221"/>
+      <c r="H33" s="221"/>
+      <c r="I33" s="221"/>
+      <c r="J33" s="221"/>
+      <c r="K33" s="221"/>
+      <c r="L33" s="221"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="221"/>
+      <c r="B34" s="221"/>
+      <c r="C34" s="221"/>
+      <c r="D34" s="221"/>
+      <c r="E34" s="221"/>
+      <c r="F34" s="221"/>
+      <c r="G34" s="221"/>
+      <c r="H34" s="221"/>
+      <c r="I34" s="221"/>
+      <c r="J34" s="221"/>
+      <c r="K34" s="221"/>
+      <c r="L34" s="221"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="221"/>
+      <c r="B35" s="221"/>
+      <c r="C35" s="221"/>
+      <c r="D35" s="221"/>
+      <c r="E35" s="221"/>
+      <c r="F35" s="221"/>
+      <c r="G35" s="221"/>
+      <c r="H35" s="221"/>
+      <c r="I35" s="221"/>
+      <c r="J35" s="221"/>
+      <c r="K35" s="221"/>
+      <c r="L35" s="221"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="221"/>
+      <c r="B36" s="221"/>
+      <c r="C36" s="221"/>
+      <c r="D36" s="221"/>
+      <c r="E36" s="221"/>
+      <c r="F36" s="221"/>
+      <c r="G36" s="221"/>
+      <c r="H36" s="221"/>
+      <c r="I36" s="221"/>
+      <c r="J36" s="221"/>
+      <c r="K36" s="221"/>
+      <c r="L36" s="221"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
@@ -3697,45 +3662,45 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="0.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="13.88671875" customWidth="1"/>
-    <col min="11" max="11" width="0.109375" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" customWidth="1"/>
-    <col min="13" max="13" width="11.88671875" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="6" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="232" t="s">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="223" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="234"/>
+      <c r="B1" s="224"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
+      <c r="F1" s="224"/>
+      <c r="G1" s="224"/>
+      <c r="H1" s="224"/>
+      <c r="I1" s="224"/>
+      <c r="J1" s="224"/>
+      <c r="K1" s="224"/>
+      <c r="L1" s="224"/>
+      <c r="M1" s="224"/>
+      <c r="N1" s="225"/>
       <c r="O1" s="78"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="79"/>
       <c r="B2" s="79"/>
       <c r="C2" s="164"/>
@@ -3753,7 +3718,7 @@
       <c r="O2" s="80"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
       <c r="C3" s="166"/>
@@ -3771,7 +3736,7 @@
       <c r="O3" s="80"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="82"/>
       <c r="B4" s="82"/>
       <c r="C4" s="166"/>
@@ -3791,7 +3756,7 @@
       <c r="O4" s="80"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="82"/>
       <c r="B5" s="82"/>
       <c r="C5" s="166"/>
@@ -3809,7 +3774,7 @@
       <c r="O5" s="80"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="82"/>
       <c r="B6" s="82"/>
       <c r="C6" s="164"/>
@@ -3827,12 +3792,12 @@
       <c r="O6" s="80"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="83"/>
       <c r="B7" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="216">
+      <c r="C7" s="229">
         <v>639397.63</v>
       </c>
       <c r="D7" s="28"/>
@@ -3854,7 +3819,7 @@
       <c r="O7" s="80"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="83"/>
       <c r="B8" s="82" t="s">
         <v>79</v>
@@ -3870,16 +3835,16 @@
         <f>C8-J38</f>
         <v>-196408.73539999995</v>
       </c>
-      <c r="L8" s="236">
+      <c r="L8" s="227">
         <f>C7-J38</f>
         <v>442988.89460000006</v>
       </c>
-      <c r="M8" s="236"/>
+      <c r="M8" s="227"/>
       <c r="N8" s="86"/>
       <c r="O8" s="80"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="89" t="s">
         <v>80</v>
       </c>
@@ -3924,7 +3889,7 @@
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="100">
         <v>1</v>
       </c>
@@ -3974,13 +3939,13 @@
         <f>J10+L10</f>
         <v>43663.777914059989</v>
       </c>
-      <c r="O10" s="99" t="e">
+      <c r="O10" s="99">
         <f>N10+'prorrateo '!L3</f>
-        <v>#VALUE!</v>
+        <v>120313.77791406</v>
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="101">
         <v>2</v>
       </c>
@@ -4030,13 +3995,13 @@
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
         <v>45132.044335140017</v>
       </c>
-      <c r="O11" s="99" t="e">
+      <c r="O11" s="99">
         <f>N11+'prorrateo '!L4</f>
-        <v>#VALUE!</v>
+        <v>121482.04433514002</v>
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="100">
         <v>3</v>
       </c>
@@ -4086,16 +4051,16 @@
         <f t="shared" si="5"/>
         <v>25121.492887839999</v>
       </c>
-      <c r="O12" s="99" t="e">
+      <c r="O12" s="99">
         <f>N12+'prorrateo '!L5</f>
-        <v>#VALUE!</v>
+        <v>248315.23528783998</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="100">
         <v>4</v>
       </c>
@@ -4145,13 +4110,13 @@
         <f t="shared" si="5"/>
         <v>30338.835208660013</v>
       </c>
-      <c r="O13" s="99" t="e">
+      <c r="O13" s="99">
         <f>N13+'prorrateo '!L6</f>
-        <v>#VALUE!</v>
+        <v>108488.83520866002</v>
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="100">
         <v>6</v>
       </c>
@@ -4201,13 +4166,13 @@
         <f t="shared" si="5"/>
         <v>28451.526514060006</v>
       </c>
-      <c r="O14" s="99" t="e">
+      <c r="O14" s="99">
         <f>N14+'prorrateo '!L7</f>
-        <v>#VALUE!</v>
+        <v>105101.52651406002</v>
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="100">
         <v>7</v>
       </c>
@@ -4257,12 +4222,12 @@
         <f t="shared" si="5"/>
         <v>32930.355635140033</v>
       </c>
-      <c r="O15" s="99" t="e">
+      <c r="O15" s="99">
         <f>N15+'prorrateo '!L8</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+        <v>109280.35563514003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="100">
         <v>8</v>
       </c>
@@ -4312,67 +4277,67 @@
         <f t="shared" si="5"/>
         <v>30392.91741406003</v>
       </c>
-      <c r="O16" s="99" t="e">
+      <c r="O16" s="99">
         <f>N16+'prorrateo '!L9</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>107042.91741406004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="100">
         <v>9</v>
       </c>
       <c r="B17" s="91">
         <v>9</v>
       </c>
-      <c r="C17" s="194" t="s">
+      <c r="C17" s="193" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="195" t="s">
+      <c r="D17" s="194" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="196">
+      <c r="E17" s="195">
         <v>5.09</v>
       </c>
-      <c r="F17" s="198">
+      <c r="F17" s="197">
         <v>3290.2</v>
       </c>
-      <c r="G17" s="198">
+      <c r="G17" s="197">
         <v>3314.7</v>
       </c>
-      <c r="H17" s="199">
+      <c r="H17" s="198">
         <f t="shared" si="1"/>
         <v>24.5</v>
       </c>
-      <c r="I17" s="200">
+      <c r="I17" s="199">
         <f t="shared" si="0"/>
         <v>1.7150000000000001</v>
       </c>
-      <c r="J17" s="201">
+      <c r="J17" s="200">
         <f t="shared" si="2"/>
         <v>2297.7815000000001</v>
       </c>
-      <c r="K17" s="202">
+      <c r="K17" s="201">
         <f>K8*E17%</f>
         <v>-9997.2046318599969</v>
       </c>
-      <c r="L17" s="203">
+      <c r="L17" s="202">
         <f t="shared" si="3"/>
         <v>22548.134735140004</v>
       </c>
-      <c r="M17" s="204">
+      <c r="M17" s="203">
         <f t="shared" si="4"/>
         <v>24.5</v>
       </c>
-      <c r="N17" s="199">
+      <c r="N17" s="198">
         <f t="shared" si="5"/>
         <v>24845.916235140005</v>
       </c>
-      <c r="O17" s="99" t="e">
+      <c r="O17" s="99">
         <f>N17+'prorrateo '!L10</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>101195.91623514</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="100">
         <v>10</v>
       </c>
@@ -4422,12 +4387,12 @@
         <f t="shared" si="5"/>
         <v>31030.073887840001</v>
       </c>
-      <c r="O18" s="99" t="e">
+      <c r="O18" s="99">
         <f>N18+'prorrateo '!L11</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>106630.07388784</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="100">
         <v>11</v>
       </c>
@@ -4477,12 +4442,12 @@
         <f t="shared" si="5"/>
         <v>47783.217208659975</v>
       </c>
-      <c r="O19" s="99" t="e">
+      <c r="O19" s="99">
         <f>N19+'prorrateo '!L12</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125933.21720865997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="100">
         <v>12</v>
       </c>
@@ -4532,12 +4497,12 @@
         <f t="shared" si="5"/>
         <v>41984.990614060021</v>
       </c>
-      <c r="O20" s="99" t="e">
+      <c r="O20" s="99">
         <f>N20+'prorrateo '!L13</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>118634.99061406004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="100">
         <v>13</v>
       </c>
@@ -4587,12 +4552,12 @@
         <f t="shared" si="5"/>
         <v>32996.006535140012</v>
       </c>
-      <c r="O21" s="99" t="e">
+      <c r="O21" s="99">
         <f>N21+'prorrateo '!L14</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>219759.49933514002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="100">
         <v>14</v>
       </c>
@@ -4642,12 +4607,12 @@
         <f t="shared" si="5"/>
         <v>27081.641187839989</v>
       </c>
-      <c r="O22" s="99" t="e">
+      <c r="O22" s="99">
         <f>N22+'prorrateo '!L15</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>273900.65798783995</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="100">
         <v>15</v>
       </c>
@@ -4697,12 +4662,12 @@
         <f t="shared" si="5"/>
         <v>33893.362508660022</v>
       </c>
-      <c r="O23" s="99" t="e">
+      <c r="O23" s="99">
         <f>N23+'prorrateo '!L16</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>112043.36250866002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="100">
         <v>16</v>
       </c>
@@ -4752,12 +4717,12 @@
         <f t="shared" si="5"/>
         <v>27128.534687840009</v>
       </c>
-      <c r="O24" s="99" t="e">
+      <c r="O24" s="99">
         <f>N24+'prorrateo '!L17</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <v>212057.41148783997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="100">
         <v>17</v>
       </c>
@@ -4807,12 +4772,12 @@
         <f t="shared" si="5"/>
         <v>30188.776008659999</v>
       </c>
-      <c r="O25" s="99" t="e">
+      <c r="O25" s="99">
         <f>N25+'prorrateo '!L18</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>221355.33680866001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="100">
         <v>18</v>
       </c>
@@ -4862,56 +4827,56 @@
         <f>J26+L26</f>
         <v>58591.360600399901</v>
       </c>
-      <c r="O26" s="99" t="e">
+      <c r="O26" s="99">
         <f>N26+'prorrateo '!L19</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>169591.3606003999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="100">
         <v>19</v>
       </c>
       <c r="B27" s="92">
         <v>19</v>
       </c>
-      <c r="C27" s="205" t="s">
+      <c r="C27" s="204" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="206" t="s">
+      <c r="D27" s="205" t="s">
         <v>98</v>
       </c>
-      <c r="E27" s="207">
+      <c r="E27" s="206">
         <v>1.08</v>
       </c>
-      <c r="F27" s="197"/>
-      <c r="G27" s="198"/>
-      <c r="H27" s="199">
+      <c r="F27" s="196"/>
+      <c r="G27" s="197"/>
+      <c r="H27" s="198">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="200">
+      <c r="I27" s="199">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="201"/>
-      <c r="K27" s="202"/>
-      <c r="L27" s="203">
+      <c r="J27" s="200"/>
+      <c r="K27" s="201"/>
+      <c r="L27" s="202">
         <f t="shared" si="3"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="M27" s="204">
-        <v>0</v>
-      </c>
-      <c r="N27" s="199">
+      <c r="M27" s="203">
+        <v>0</v>
+      </c>
+      <c r="N27" s="198">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O27" s="99" t="e">
+      <c r="O27" s="99">
         <f>N27+'prorrateo '!L20</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>20984.280061680001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="100">
         <v>20</v>
       </c>
@@ -4945,12 +4910,12 @@
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O28" s="99" t="e">
+      <c r="O28" s="99">
         <f>N28+'prorrateo '!L21</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>20984.280061680001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="100"/>
       <c r="B29" s="92"/>
       <c r="C29" s="161" t="s">
@@ -4977,12 +4942,12 @@
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O29" s="99" t="e">
+      <c r="O29" s="99">
         <f>N29+'prorrateo '!L22</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>221115.02646168001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="100"/>
       <c r="B30" s="92"/>
       <c r="C30" s="172" t="s">
@@ -5009,12 +4974,12 @@
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O30" s="99" t="e">
+      <c r="O30" s="99">
         <f>N30+'prorrateo '!L23</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>20984.280061680001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="100"/>
       <c r="B31" s="92"/>
       <c r="C31" s="172" t="s">
@@ -5041,12 +5006,12 @@
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O31" s="99" t="e">
+      <c r="O31" s="99">
         <f>N31+'prorrateo '!L24</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <v>20984.280061680001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="100"/>
       <c r="B32" s="92"/>
       <c r="C32" s="132" t="s">
@@ -5073,12 +5038,12 @@
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O32" s="99" t="e">
+      <c r="O32" s="99">
         <f>N32+'prorrateo '!L25</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+        <v>44411.892061680002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="100"/>
       <c r="B33" s="92"/>
       <c r="C33" s="132" t="s">
@@ -5105,12 +5070,12 @@
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O33" s="99" t="e">
+      <c r="O33" s="99">
         <f>N33+'prorrateo '!L26</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+        <v>20984.280061680001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="100"/>
       <c r="B34" s="92"/>
       <c r="C34" s="132" t="s">
@@ -5137,12 +5102,12 @@
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O34" s="99" t="e">
+      <c r="O34" s="99">
         <f>N34+'prorrateo '!L27</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+        <v>20984.280061680001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="100">
         <v>21</v>
       </c>
@@ -5176,12 +5141,12 @@
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O35" s="99" t="e">
+      <c r="O35" s="99">
         <f>N35+'prorrateo '!L28</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+        <v>20984.280061680001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="100">
         <v>22</v>
       </c>
@@ -5215,12 +5180,12 @@
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O36" s="99" t="e">
+      <c r="O36" s="99">
         <f>N36+'prorrateo '!L29</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+        <v>20984.280061680001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="100">
         <v>23</v>
       </c>
@@ -5250,7 +5215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="100">
         <v>24</v>
       </c>
@@ -5278,7 +5243,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="80"/>
       <c r="C39" s="93"/>
       <c r="D39" s="94"/>
@@ -5303,41 +5268,41 @@
       <c r="N39" s="95"/>
       <c r="O39" s="81"/>
     </row>
-    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="235"/>
-      <c r="D40" s="233"/>
-      <c r="E40" s="233"/>
-      <c r="F40" s="233"/>
-      <c r="G40" s="233"/>
-      <c r="H40" s="233"/>
-      <c r="I40" s="233"/>
-      <c r="J40" s="233"/>
-      <c r="K40" s="233"/>
-      <c r="L40" s="233"/>
-      <c r="M40" s="233"/>
-      <c r="N40" s="233"/>
+      <c r="C40" s="226"/>
+      <c r="D40" s="224"/>
+      <c r="E40" s="224"/>
+      <c r="F40" s="224"/>
+      <c r="G40" s="224"/>
+      <c r="H40" s="224"/>
+      <c r="I40" s="224"/>
+      <c r="J40" s="224"/>
+      <c r="K40" s="224"/>
+      <c r="L40" s="224"/>
+      <c r="M40" s="224"/>
+      <c r="N40" s="224"/>
       <c r="O40" s="97"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H41" s="81"/>
       <c r="J41" s="98"/>
       <c r="K41" s="98"/>
       <c r="L41" s="98"/>
       <c r="N41" s="99"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L44" s="154"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L45" s="98"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E46" s="155"/>
       <c r="F46" s="155"/>
       <c r="G46" s="155"/>

--- a/ROSALES/Septiembre/expensas rosales Septiembre.xlsx
+++ b/ROSALES/Septiembre/expensas rosales Septiembre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7B0A7E-35F6-4BDD-B616-A96C70DA0323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4853207-CA0A-49FB-8BF4-8B6CFC875036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$68</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$37</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="142">
   <si>
     <t>TOTAL</t>
   </si>
@@ -80,9 +80,6 @@
     <t>Metrogas 0800-333-6427</t>
   </si>
   <si>
-    <t>EDESUR</t>
-  </si>
-  <si>
     <t>GASTOS EXTRAORDINARIOS</t>
   </si>
   <si>
@@ -393,9 +390,6 @@
   </si>
   <si>
     <t>ORDINARIAS</t>
-  </si>
-  <si>
-    <t>EXTRAORDINARIAS</t>
   </si>
   <si>
     <t>Seguro de consorcio obligatorio -  federacion patronal - poliza nro. 2027630</t>
@@ -452,6 +446,15 @@
   </si>
   <si>
     <t>CUOTA PLAN DE PAGOS</t>
+  </si>
+  <si>
+    <t>EXTRAORD.</t>
+  </si>
+  <si>
+    <t>ARBA:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARBA - REVALUO </t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1072,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="230">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1402,6 +1405,8 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1440,8 +1445,9 @@
     <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1859,7 +1865,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F68"/>
+  <dimension ref="A2:F69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1874,7 +1880,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1894,13 +1900,13 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1910,7 +1916,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1949,7 +1955,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B18" s="38"/>
       <c r="C18" s="33">
@@ -1971,7 +1977,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B20" s="39"/>
       <c r="C20" s="208"/>
@@ -1980,7 +1986,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="39"/>
       <c r="C21" s="33">
@@ -1991,7 +1997,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B22" s="39"/>
       <c r="C22" s="33">
@@ -2005,7 +2011,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="33">
         <v>83400</v>
@@ -2013,7 +2019,7 @@
       <c r="D23" s="4"/>
       <c r="E23" s="6"/>
       <c r="F23" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2033,7 +2039,7 @@
     </row>
     <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B26" s="42"/>
       <c r="C26" s="33">
@@ -2045,7 +2051,7 @@
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B27" s="42"/>
       <c r="C27" s="33">
@@ -2056,7 +2062,7 @@
     </row>
     <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="176" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B28" s="140"/>
       <c r="C28" s="33">
@@ -2067,7 +2073,7 @@
     </row>
     <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B29" s="42"/>
       <c r="C29" s="33">
@@ -2077,7 +2083,7 @@
     </row>
     <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B30" s="42"/>
       <c r="C30" s="33">
@@ -2087,7 +2093,7 @@
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B31" s="39"/>
       <c r="C31" s="34">
@@ -2124,7 +2130,7 @@
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C35" s="24"/>
       <c r="F35" s="12"/>
@@ -2153,7 +2159,7 @@
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="179" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B40" s="179"/>
       <c r="C40" s="180"/>
@@ -2185,26 +2191,26 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="218" t="s">
-        <v>130</v>
-      </c>
-      <c r="B46" s="219"/>
-      <c r="C46" s="219"/>
+      <c r="A46" s="220" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" s="221"/>
+      <c r="C46" s="221"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="219"/>
-      <c r="B47" s="219"/>
-      <c r="C47" s="219"/>
+      <c r="A47" s="221"/>
+      <c r="B47" s="221"/>
+      <c r="C47" s="221"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="219"/>
-      <c r="B48" s="219"/>
-      <c r="C48" s="219"/>
+      <c r="A48" s="221"/>
+      <c r="B48" s="221"/>
+      <c r="C48" s="221"/>
     </row>
     <row r="49" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="219"/>
-      <c r="B49" s="219"/>
-      <c r="C49" s="219"/>
+      <c r="A49" s="221"/>
+      <c r="B49" s="221"/>
+      <c r="C49" s="221"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
     </row>
@@ -2216,7 +2222,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="210" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B51" s="28"/>
       <c r="C51" s="211">
@@ -2227,7 +2233,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="210" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B52" s="28"/>
       <c r="C52" s="31">
@@ -2239,122 +2245,133 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="210" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="B53" s="28"/>
-      <c r="C53" s="212">
+      <c r="C53" s="31">
+        <v>-1360565.9</v>
+      </c>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="210" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="28"/>
+      <c r="C54" s="212">
         <f>'prorrateo '!F31</f>
         <v>2045051.5300000003</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="210" t="s">
-        <v>140</v>
-      </c>
-      <c r="B54" s="28"/>
-      <c r="C54" s="212">
-        <v>107386.2</v>
-      </c>
-    </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="210" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B55" s="28"/>
-      <c r="C55" s="213">
-        <v>-376000</v>
+      <c r="C55" s="212">
+        <v>107386.2</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="210" t="s">
+        <v>137</v>
+      </c>
+      <c r="B56" s="28"/>
+      <c r="C56" s="213">
+        <v>-376000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="210" t="s">
         <v>8</v>
       </c>
-      <c r="B56" s="28"/>
-      <c r="C56" s="211">
-        <f>SUM(C49:C55)</f>
-        <v>1510320.6241728256</v>
-      </c>
-      <c r="D56" s="5"/>
-    </row>
-    <row r="57" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="9"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="10"/>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="214"/>
-      <c r="B58" s="214"/>
-      <c r="C58" s="214"/>
-      <c r="F58" s="44"/>
-    </row>
-    <row r="59" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="215"/>
-      <c r="B59" s="215"/>
-      <c r="C59" s="215"/>
-    </row>
-    <row r="60" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B60" s="27"/>
-      <c r="C60" s="29"/>
-    </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B61" s="28"/>
-      <c r="C61" s="31">
+      <c r="B57" s="28"/>
+      <c r="C57" s="211">
+        <f>SUM(C49:C56)</f>
+        <v>149754.72417282569</v>
+      </c>
+      <c r="D57" s="5"/>
+    </row>
+    <row r="58" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="9"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="10"/>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="216"/>
+      <c r="B59" s="216"/>
+      <c r="C59" s="216"/>
+      <c r="F59" s="44"/>
+    </row>
+    <row r="60" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="217"/>
+      <c r="B60" s="217"/>
+      <c r="C60" s="217"/>
+    </row>
+    <row r="61" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B61" s="27"/>
+      <c r="C61" s="29"/>
+    </row>
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B62" s="28"/>
+      <c r="C62" s="31">
         <f>-C42</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="28"/>
-      <c r="B62" s="28"/>
-      <c r="C62" s="31"/>
     </row>
     <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="28"/>
       <c r="B63" s="28"/>
-      <c r="C63" s="32"/>
+      <c r="C63" s="31"/>
     </row>
     <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="158" t="s">
-        <v>0</v>
-      </c>
-      <c r="B64" s="159"/>
-      <c r="C64" s="160">
-        <f>SUM(C60:C63)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="216" t="s">
-        <v>127</v>
-      </c>
-      <c r="B65" s="217"/>
-      <c r="C65" s="217"/>
+      <c r="A64" s="28"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="32"/>
+    </row>
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="158" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="159"/>
+      <c r="C65" s="160">
+        <f>SUM(C61:C64)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="217"/>
-      <c r="B66" s="217"/>
-      <c r="C66" s="217"/>
+      <c r="A66" s="218" t="s">
+        <v>125</v>
+      </c>
+      <c r="B66" s="219"/>
+      <c r="C66" s="219"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="217"/>
-      <c r="B67" s="217"/>
-      <c r="C67" s="217"/>
+      <c r="A67" s="219"/>
+      <c r="B67" s="219"/>
+      <c r="C67" s="219"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
+      <c r="A68" s="219"/>
+      <c r="B68" s="219"/>
+      <c r="C68" s="219"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A58:C59"/>
-    <mergeCell ref="A65:C67"/>
+    <mergeCell ref="A59:C60"/>
+    <mergeCell ref="A66:C68"/>
     <mergeCell ref="A46:C49"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
@@ -2386,7 +2403,7 @@
     <col min="8" max="8" width="10.85546875" customWidth="1"/>
     <col min="9" max="9" width="10.7109375" customWidth="1"/>
     <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="0.140625" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" customWidth="1"/>
     <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.42578125" style="11"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
@@ -2394,68 +2411,76 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B1" s="220">
+        <v>119</v>
+      </c>
+      <c r="B1" s="222">
         <v>1500000</v>
       </c>
-      <c r="C1" s="220"/>
+      <c r="C1" s="222"/>
       <c r="D1" s="141" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
+        <v>118</v>
+      </c>
+      <c r="G1" s="224"/>
+      <c r="H1" s="224"/>
+      <c r="I1" s="230" t="s">
+        <v>140</v>
+      </c>
+      <c r="J1" s="230"/>
+      <c r="K1" s="222">
+        <v>1360565.9</v>
+      </c>
+      <c r="L1" s="222"/>
     </row>
     <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="139" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D2" s="47" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="G2" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="H2" s="209" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="J2" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="K2" s="50" t="s">
+        <v>127</v>
+      </c>
+      <c r="L2" s="51" t="s">
         <v>30</v>
-      </c>
-      <c r="H2" s="209" t="s">
-        <v>109</v>
-      </c>
-      <c r="I2" s="50" t="s">
-        <v>121</v>
-      </c>
-      <c r="J2" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="K2" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="51" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="54" t="s">
         <v>32</v>
-      </c>
-      <c r="B3" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="54" t="s">
-        <v>33</v>
       </c>
       <c r="D3" s="55">
         <v>5.1100000000000003</v>
@@ -2483,21 +2508,24 @@
         <f>G$1*D3/100</f>
         <v>0</v>
       </c>
-      <c r="K3" s="56"/>
+      <c r="K3" s="56">
+        <f>K$1*D3/100</f>
+        <v>69524.917489999993</v>
+      </c>
       <c r="L3" s="57">
         <f>I3+G3+K3+J3+H3</f>
-        <v>76650.000000000015</v>
+        <v>146174.91749000002</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="60" t="s">
         <v>34</v>
-      </c>
-      <c r="B4" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="60" t="s">
-        <v>35</v>
       </c>
       <c r="D4" s="61">
         <v>5.09</v>
@@ -2525,21 +2553,24 @@
         <f t="shared" ref="J4:J29" si="4">G$1*D4/100</f>
         <v>0</v>
       </c>
-      <c r="K4" s="56"/>
+      <c r="K4" s="56">
+        <f t="shared" ref="K4:K29" si="5">K$1*D4/100</f>
+        <v>69252.804309999992</v>
+      </c>
       <c r="L4" s="57">
-        <f t="shared" ref="L4:L29" si="5">I4+G4+K4+J4+H4</f>
-        <v>76350</v>
+        <f t="shared" ref="L4:L29" si="6">I4+G4+K4+J4+H4</f>
+        <v>145602.80430999998</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="59" t="s">
+      <c r="C5" s="60" t="s">
         <v>37</v>
-      </c>
-      <c r="C5" s="60" t="s">
-        <v>38</v>
       </c>
       <c r="D5" s="61">
         <v>5.04</v>
@@ -2567,19 +2598,22 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K5" s="56"/>
+      <c r="K5" s="56">
+        <f t="shared" si="5"/>
+        <v>68572.521359999999</v>
+      </c>
       <c r="L5" s="57">
-        <f t="shared" si="5"/>
-        <v>223193.74239999999</v>
+        <f t="shared" si="6"/>
+        <v>291766.26376</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="59"/>
       <c r="C6" s="60" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" s="61">
         <v>5.21</v>
@@ -2588,7 +2622,7 @@
         <v>108669.77</v>
       </c>
       <c r="F6" s="177">
-        <f>E6</f>
+        <f t="shared" ref="F6:F11" si="7">E6</f>
         <v>108669.77</v>
       </c>
       <c r="G6" s="56">
@@ -2607,22 +2641,25 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K6" s="56"/>
+      <c r="K6" s="56">
+        <f t="shared" si="5"/>
+        <v>70885.483389999994</v>
+      </c>
       <c r="L6" s="57">
-        <f t="shared" si="5"/>
-        <v>78150</v>
+        <f t="shared" si="6"/>
+        <v>149035.48339000001</v>
       </c>
       <c r="O6" s="182"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C7" s="60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" s="61">
         <v>5.1100000000000003</v>
@@ -2631,7 +2668,7 @@
         <v>106583.98</v>
       </c>
       <c r="F7" s="177">
-        <f>E7</f>
+        <f t="shared" si="7"/>
         <v>106583.98</v>
       </c>
       <c r="G7" s="56">
@@ -2650,20 +2687,23 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K7" s="56"/>
+      <c r="K7" s="56">
+        <f t="shared" si="5"/>
+        <v>69524.917489999993</v>
+      </c>
       <c r="L7" s="57">
-        <f t="shared" si="5"/>
-        <v>76650.000000000015</v>
+        <f t="shared" si="6"/>
+        <v>146174.91749000002</v>
       </c>
       <c r="O7" s="182"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="59"/>
       <c r="C8" s="60" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" s="61">
         <v>5.09</v>
@@ -2672,7 +2712,7 @@
         <v>106166.82</v>
       </c>
       <c r="F8" s="177">
-        <f>E8</f>
+        <f t="shared" si="7"/>
         <v>106166.82</v>
       </c>
       <c r="G8" s="56">
@@ -2691,19 +2731,22 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K8" s="56"/>
+      <c r="K8" s="56">
+        <f t="shared" si="5"/>
+        <v>69252.804309999992</v>
+      </c>
       <c r="L8" s="57">
-        <f t="shared" si="5"/>
-        <v>76350</v>
+        <f t="shared" si="6"/>
+        <v>145602.80430999998</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="59"/>
       <c r="C9" s="60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9" s="61">
         <v>5.1100000000000003</v>
@@ -2712,7 +2755,7 @@
         <v>106583.98</v>
       </c>
       <c r="F9" s="177">
-        <f>E9</f>
+        <f t="shared" si="7"/>
         <v>106583.98</v>
       </c>
       <c r="G9" s="56">
@@ -2731,22 +2774,25 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K9" s="56"/>
+      <c r="K9" s="56">
+        <f t="shared" si="5"/>
+        <v>69524.917489999993</v>
+      </c>
       <c r="L9" s="57">
-        <f t="shared" si="5"/>
-        <v>76650.000000000015</v>
+        <f t="shared" si="6"/>
+        <v>146174.91749000002</v>
       </c>
       <c r="O9" s="182"/>
     </row>
     <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="185" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="186" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="187" t="s">
         <v>46</v>
-      </c>
-      <c r="B10" s="186" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" s="187" t="s">
-        <v>47</v>
       </c>
       <c r="D10" s="188">
         <v>5.09</v>
@@ -2754,8 +2800,8 @@
       <c r="E10" s="189">
         <v>106166.82</v>
       </c>
-      <c r="F10" s="228">
-        <f>E10</f>
+      <c r="F10" s="214">
+        <f t="shared" si="7"/>
         <v>106166.82</v>
       </c>
       <c r="G10" s="190">
@@ -2771,19 +2817,22 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K10" s="190"/>
+      <c r="K10" s="190">
+        <f t="shared" si="5"/>
+        <v>69252.804309999992</v>
+      </c>
       <c r="L10" s="191">
-        <f t="shared" si="5"/>
-        <v>76350</v>
+        <f t="shared" si="6"/>
+        <v>145602.80430999998</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B11" s="59"/>
       <c r="C11" s="60" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" s="61">
         <v>5.04</v>
@@ -2792,7 +2841,7 @@
         <v>105123.92</v>
       </c>
       <c r="F11" s="177">
-        <f>E11</f>
+        <f t="shared" si="7"/>
         <v>105123.92</v>
       </c>
       <c r="G11" s="56">
@@ -2811,19 +2860,22 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K11" s="56"/>
+      <c r="K11" s="56">
+        <f t="shared" si="5"/>
+        <v>68572.521359999999</v>
+      </c>
       <c r="L11" s="57">
-        <f t="shared" si="5"/>
-        <v>75600</v>
+        <f t="shared" si="6"/>
+        <v>144172.52136000001</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B12" s="59"/>
       <c r="C12" s="60" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" s="61">
         <v>5.21</v>
@@ -2851,21 +2903,24 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K12" s="56"/>
+      <c r="K12" s="56">
+        <f t="shared" si="5"/>
+        <v>70885.483389999994</v>
+      </c>
       <c r="L12" s="57">
-        <f t="shared" si="5"/>
-        <v>78150</v>
+        <f t="shared" si="6"/>
+        <v>149035.48339000001</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="59" t="s">
+      <c r="C13" s="60" t="s">
         <v>52</v>
-      </c>
-      <c r="C13" s="60" t="s">
-        <v>53</v>
       </c>
       <c r="D13" s="61">
         <v>5.1100000000000003</v>
@@ -2893,21 +2948,24 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K13" s="56"/>
+      <c r="K13" s="56">
+        <f t="shared" si="5"/>
+        <v>69524.917489999993</v>
+      </c>
       <c r="L13" s="57">
-        <f t="shared" si="5"/>
-        <v>76650.000000000015</v>
+        <f t="shared" si="6"/>
+        <v>146174.91749000002</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="64" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="207" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C14" s="65" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="183">
         <v>5.09</v>
@@ -2932,21 +2990,24 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K14" s="66"/>
+      <c r="K14" s="56">
+        <f t="shared" si="5"/>
+        <v>69252.804309999992</v>
+      </c>
       <c r="L14" s="184">
-        <f t="shared" si="5"/>
-        <v>186763.49280000001</v>
+        <f t="shared" si="6"/>
+        <v>256016.29710999998</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="59" t="s">
+      <c r="C15" s="60" t="s">
         <v>56</v>
-      </c>
-      <c r="C15" s="60" t="s">
-        <v>57</v>
       </c>
       <c r="D15" s="61">
         <v>5.04</v>
@@ -2974,21 +3035,24 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K15" s="56"/>
+      <c r="K15" s="56">
+        <f t="shared" si="5"/>
+        <v>68572.521359999999</v>
+      </c>
       <c r="L15" s="57">
-        <f t="shared" si="5"/>
-        <v>246819.01679999998</v>
+        <f t="shared" si="6"/>
+        <v>315391.53816</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="59" t="s">
+      <c r="C16" s="60" t="s">
         <v>59</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>60</v>
       </c>
       <c r="D16" s="61">
         <v>5.21</v>
@@ -3016,19 +3080,22 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K16" s="56"/>
+      <c r="K16" s="56">
+        <f t="shared" si="5"/>
+        <v>70885.483389999994</v>
+      </c>
       <c r="L16" s="57">
-        <f t="shared" si="5"/>
-        <v>78150</v>
+        <f t="shared" si="6"/>
+        <v>149035.48339000001</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B17" s="59"/>
       <c r="C17" s="60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D17" s="61">
         <v>5.04</v>
@@ -3053,19 +3120,22 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K17" s="56"/>
+      <c r="K17" s="56">
+        <f t="shared" si="5"/>
+        <v>68572.521359999999</v>
+      </c>
       <c r="L17" s="57">
-        <f t="shared" si="5"/>
-        <v>184928.87679999997</v>
+        <f t="shared" si="6"/>
+        <v>253501.39815999998</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B18" s="63"/>
       <c r="C18" s="60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18" s="61">
         <v>5.21</v>
@@ -3090,19 +3160,22 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K18" s="56"/>
+      <c r="K18" s="56">
+        <f t="shared" si="5"/>
+        <v>70885.483389999994</v>
+      </c>
       <c r="L18" s="57">
-        <f t="shared" si="5"/>
-        <v>191166.56080000001</v>
+        <f t="shared" si="6"/>
+        <v>262052.04419000002</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B19" s="59"/>
       <c r="C19" s="60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D19" s="61">
         <v>7.4</v>
@@ -3130,19 +3203,22 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K19" s="56"/>
+      <c r="K19" s="56">
+        <f t="shared" si="5"/>
+        <v>100681.8766</v>
+      </c>
       <c r="L19" s="57">
-        <f t="shared" si="5"/>
-        <v>111000</v>
+        <f t="shared" si="6"/>
+        <v>211681.87660000002</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="192"/>
       <c r="B20" s="186" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C20" s="187" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D20" s="188">
         <v>1.08</v>
@@ -3150,7 +3226,7 @@
       <c r="E20" s="189">
         <v>22526.55</v>
       </c>
-      <c r="F20" s="228">
+      <c r="F20" s="214">
         <f>E20</f>
         <v>22526.55</v>
       </c>
@@ -3167,19 +3243,22 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K20" s="190"/>
+      <c r="K20" s="190">
+        <f t="shared" si="5"/>
+        <v>14694.111720000001</v>
+      </c>
       <c r="L20" s="191">
-        <f t="shared" si="5"/>
-        <v>16200</v>
+        <f t="shared" si="6"/>
+        <v>30894.111720000001</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="64"/>
       <c r="B21" s="59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C21" s="65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D21" s="61">
         <v>1.08</v>
@@ -3207,17 +3286,20 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K21" s="66"/>
+      <c r="K21" s="56">
+        <f t="shared" si="5"/>
+        <v>14694.111720000001</v>
+      </c>
       <c r="L21" s="57">
-        <f t="shared" si="5"/>
-        <v>16200</v>
+        <f t="shared" si="6"/>
+        <v>30894.111720000001</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="142"/>
       <c r="B22" s="143"/>
       <c r="C22" s="144" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D22" s="145">
         <v>1.08</v>
@@ -3244,19 +3326,22 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K22" s="147"/>
+      <c r="K22" s="147">
+        <f t="shared" si="5"/>
+        <v>14694.111720000001</v>
+      </c>
       <c r="L22" s="148">
-        <f t="shared" si="5"/>
-        <v>216330.7464</v>
+        <f t="shared" si="6"/>
+        <v>231024.85812000002</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="58"/>
       <c r="B23" s="59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" s="60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D23" s="61">
         <v>1.08</v>
@@ -3284,21 +3369,24 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K23" s="56"/>
+      <c r="K23" s="56">
+        <f t="shared" si="5"/>
+        <v>14694.111720000001</v>
+      </c>
       <c r="L23" s="57">
-        <f t="shared" si="5"/>
-        <v>16200</v>
+        <f t="shared" si="6"/>
+        <v>30894.111720000001</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="59" t="s">
-        <v>52</v>
-      </c>
       <c r="C24" s="60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D24" s="61">
         <v>1.08</v>
@@ -3307,7 +3395,7 @@
         <v>22526.55</v>
       </c>
       <c r="F24" s="177">
-        <f t="shared" ref="F24" si="6">E24</f>
+        <f t="shared" ref="F24" si="8">E24</f>
         <v>22526.55</v>
       </c>
       <c r="G24" s="56">
@@ -3326,21 +3414,24 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K24" s="56"/>
+      <c r="K24" s="56">
+        <f t="shared" si="5"/>
+        <v>14694.111720000001</v>
+      </c>
       <c r="L24" s="57">
-        <f t="shared" si="5"/>
-        <v>16200</v>
+        <f t="shared" si="6"/>
+        <v>30894.111720000001</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25" s="207" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C25" s="60" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D25" s="61">
         <v>1.08</v>
@@ -3365,19 +3456,22 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K25" s="56"/>
+      <c r="K25" s="56">
+        <f t="shared" si="5"/>
+        <v>14694.111720000001</v>
+      </c>
       <c r="L25" s="57">
-        <f t="shared" si="5"/>
-        <v>39627.612000000001</v>
+        <f t="shared" si="6"/>
+        <v>54321.723720000002</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B26" s="59"/>
       <c r="C26" s="60" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D26" s="61">
         <v>1.08</v>
@@ -3386,7 +3480,7 @@
         <v>22526.55</v>
       </c>
       <c r="F26" s="177">
-        <f t="shared" ref="F26:F28" si="7">E26</f>
+        <f t="shared" ref="F26:F28" si="9">E26</f>
         <v>22526.55</v>
       </c>
       <c r="G26" s="56">
@@ -3405,19 +3499,22 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K26" s="56"/>
+      <c r="K26" s="56">
+        <f t="shared" si="5"/>
+        <v>14694.111720000001</v>
+      </c>
       <c r="L26" s="57">
-        <f t="shared" si="5"/>
-        <v>16200</v>
+        <f t="shared" si="6"/>
+        <v>30894.111720000001</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B27" s="67"/>
       <c r="C27" s="60" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D27" s="61">
         <v>1.08</v>
@@ -3426,7 +3523,7 @@
         <v>22526.55</v>
       </c>
       <c r="F27" s="177">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>22526.55</v>
       </c>
       <c r="G27" s="56">
@@ -3445,10 +3542,13 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K27" s="56"/>
+      <c r="K27" s="56">
+        <f t="shared" si="5"/>
+        <v>14694.111720000001</v>
+      </c>
       <c r="L27" s="57">
-        <f t="shared" si="5"/>
-        <v>16200</v>
+        <f t="shared" si="6"/>
+        <v>30894.111720000001</v>
       </c>
       <c r="O27" s="44">
         <f>F27+F26+F19</f>
@@ -3462,7 +3562,7 @@
         <v>Leandro</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D28" s="61">
         <v>1.08</v>
@@ -3471,7 +3571,7 @@
         <v>22526.55</v>
       </c>
       <c r="F28" s="177">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>22526.55</v>
       </c>
       <c r="G28" s="56">
@@ -3490,21 +3590,24 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K28" s="56"/>
+      <c r="K28" s="56">
+        <f t="shared" si="5"/>
+        <v>14694.111720000001</v>
+      </c>
       <c r="L28" s="57">
-        <f t="shared" si="5"/>
-        <v>16200</v>
+        <f t="shared" si="6"/>
+        <v>30894.111720000001</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="59" t="s">
-        <v>56</v>
-      </c>
       <c r="C29" s="60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D29" s="61">
         <v>1.08</v>
@@ -3532,10 +3635,13 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K29" s="56"/>
+      <c r="K29" s="56">
+        <f t="shared" si="5"/>
+        <v>14694.111720000001</v>
+      </c>
       <c r="L29" s="57">
-        <f t="shared" si="5"/>
-        <v>16200</v>
+        <f t="shared" si="6"/>
+        <v>30894.111720000001</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -3556,7 +3662,7 @@
       <c r="A31" s="74"/>
       <c r="B31" s="75"/>
       <c r="C31" s="76" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D31" s="76">
         <f>SUM(D3:D30)</f>
@@ -3580,82 +3686,84 @@
       <c r="K31" s="137"/>
       <c r="L31" s="137">
         <f>SUM(L3:L29)</f>
-        <v>2375130.048</v>
+        <v>3735695.9479999999</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="221" t="s">
-        <v>132</v>
-      </c>
-      <c r="B33" s="221"/>
-      <c r="C33" s="221"/>
-      <c r="D33" s="221"/>
-      <c r="E33" s="221"/>
-      <c r="F33" s="221"/>
-      <c r="G33" s="221"/>
-      <c r="H33" s="221"/>
-      <c r="I33" s="221"/>
-      <c r="J33" s="221"/>
-      <c r="K33" s="221"/>
-      <c r="L33" s="221"/>
+      <c r="A33" s="223" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" s="223"/>
+      <c r="C33" s="223"/>
+      <c r="D33" s="223"/>
+      <c r="E33" s="223"/>
+      <c r="F33" s="223"/>
+      <c r="G33" s="223"/>
+      <c r="H33" s="223"/>
+      <c r="I33" s="223"/>
+      <c r="J33" s="223"/>
+      <c r="K33" s="223"/>
+      <c r="L33" s="223"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="221"/>
-      <c r="B34" s="221"/>
-      <c r="C34" s="221"/>
-      <c r="D34" s="221"/>
-      <c r="E34" s="221"/>
-      <c r="F34" s="221"/>
-      <c r="G34" s="221"/>
-      <c r="H34" s="221"/>
-      <c r="I34" s="221"/>
-      <c r="J34" s="221"/>
-      <c r="K34" s="221"/>
-      <c r="L34" s="221"/>
+      <c r="A34" s="223"/>
+      <c r="B34" s="223"/>
+      <c r="C34" s="223"/>
+      <c r="D34" s="223"/>
+      <c r="E34" s="223"/>
+      <c r="F34" s="223"/>
+      <c r="G34" s="223"/>
+      <c r="H34" s="223"/>
+      <c r="I34" s="223"/>
+      <c r="J34" s="223"/>
+      <c r="K34" s="223"/>
+      <c r="L34" s="223"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="221"/>
-      <c r="B35" s="221"/>
-      <c r="C35" s="221"/>
-      <c r="D35" s="221"/>
-      <c r="E35" s="221"/>
-      <c r="F35" s="221"/>
-      <c r="G35" s="221"/>
-      <c r="H35" s="221"/>
-      <c r="I35" s="221"/>
-      <c r="J35" s="221"/>
-      <c r="K35" s="221"/>
-      <c r="L35" s="221"/>
+      <c r="A35" s="223"/>
+      <c r="B35" s="223"/>
+      <c r="C35" s="223"/>
+      <c r="D35" s="223"/>
+      <c r="E35" s="223"/>
+      <c r="F35" s="223"/>
+      <c r="G35" s="223"/>
+      <c r="H35" s="223"/>
+      <c r="I35" s="223"/>
+      <c r="J35" s="223"/>
+      <c r="K35" s="223"/>
+      <c r="L35" s="223"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="221"/>
-      <c r="B36" s="221"/>
-      <c r="C36" s="221"/>
-      <c r="D36" s="221"/>
-      <c r="E36" s="221"/>
-      <c r="F36" s="221"/>
-      <c r="G36" s="221"/>
-      <c r="H36" s="221"/>
-      <c r="I36" s="221"/>
-      <c r="J36" s="221"/>
-      <c r="K36" s="221"/>
-      <c r="L36" s="221"/>
+      <c r="A36" s="223"/>
+      <c r="B36" s="223"/>
+      <c r="C36" s="223"/>
+      <c r="D36" s="223"/>
+      <c r="E36" s="223"/>
+      <c r="F36" s="223"/>
+      <c r="G36" s="223"/>
+      <c r="H36" s="223"/>
+      <c r="I36" s="223"/>
+      <c r="J36" s="223"/>
+      <c r="K36" s="223"/>
+      <c r="L36" s="223"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A33:L36"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="97" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="96" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3682,22 +3790,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="223" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="224"/>
-      <c r="C1" s="224"/>
-      <c r="D1" s="224"/>
-      <c r="E1" s="224"/>
-      <c r="F1" s="224"/>
-      <c r="G1" s="224"/>
-      <c r="H1" s="224"/>
-      <c r="I1" s="224"/>
-      <c r="J1" s="224"/>
-      <c r="K1" s="224"/>
-      <c r="L1" s="224"/>
-      <c r="M1" s="224"/>
-      <c r="N1" s="225"/>
+      <c r="A1" s="225" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="226"/>
+      <c r="C1" s="226"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="226"/>
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
+      <c r="I1" s="226"/>
+      <c r="J1" s="226"/>
+      <c r="K1" s="226"/>
+      <c r="L1" s="226"/>
+      <c r="M1" s="226"/>
+      <c r="N1" s="227"/>
       <c r="O1" s="78"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -3746,7 +3854,7 @@
       <c r="G4" s="166"/>
       <c r="H4" s="165"/>
       <c r="I4" s="164" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J4" s="164"/>
       <c r="K4" s="164"/>
@@ -3795,15 +3903,15 @@
     <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="83"/>
       <c r="B7" s="83" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="229">
+        <v>78</v>
+      </c>
+      <c r="C7" s="215">
         <v>639397.63</v>
       </c>
       <c r="D7" s="28"/>
       <c r="E7" s="164"/>
       <c r="F7" s="164" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G7" s="164"/>
       <c r="H7" s="165"/>
@@ -3822,7 +3930,7 @@
     <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="83"/>
       <c r="B8" s="82" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" s="87"/>
       <c r="E8" s="84"/>
@@ -3835,57 +3943,57 @@
         <f>C8-J38</f>
         <v>-196408.73539999995</v>
       </c>
-      <c r="L8" s="227">
+      <c r="L8" s="229">
         <f>C7-J38</f>
         <v>442988.89460000006</v>
       </c>
-      <c r="M8" s="227"/>
+      <c r="M8" s="229"/>
       <c r="N8" s="86"/>
       <c r="O8" s="80"/>
       <c r="P8" s="11"/>
     </row>
     <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="89" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="89" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="121" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="89" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="121" t="s">
+      <c r="D9" s="122" t="s">
         <v>81</v>
-      </c>
-      <c r="D9" s="122" t="s">
-        <v>82</v>
       </c>
       <c r="E9" s="122" t="s">
         <v>1</v>
       </c>
       <c r="F9" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="120" t="s">
+      <c r="H9" s="123" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" s="124" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="123" t="s">
+      <c r="J9" s="125" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="126" t="s">
+        <v>85</v>
+      </c>
+      <c r="L9" s="126" t="s">
+        <v>85</v>
+      </c>
+      <c r="M9" s="127" t="s">
+        <v>86</v>
+      </c>
+      <c r="N9" s="120" t="s">
         <v>87</v>
-      </c>
-      <c r="I9" s="124" t="s">
-        <v>85</v>
-      </c>
-      <c r="J9" s="125" t="s">
-        <v>79</v>
-      </c>
-      <c r="K9" s="126" t="s">
-        <v>86</v>
-      </c>
-      <c r="L9" s="126" t="s">
-        <v>86</v>
-      </c>
-      <c r="M9" s="127" t="s">
-        <v>87</v>
-      </c>
-      <c r="N9" s="120" t="s">
-        <v>88</v>
       </c>
       <c r="P9" s="11"/>
     </row>
@@ -3897,10 +4005,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="117" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="102" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E10" s="103">
         <v>5.1100000000000003</v>
@@ -3941,7 +4049,7 @@
       </c>
       <c r="O10" s="99">
         <f>N10+'prorrateo '!L3</f>
-        <v>120313.77791406</v>
+        <v>189838.69540406001</v>
       </c>
       <c r="P10" s="11"/>
     </row>
@@ -3953,10 +4061,10 @@
         <v>2</v>
       </c>
       <c r="C11" s="117" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" s="102" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E11" s="103">
         <v>5.09</v>
@@ -3997,7 +4105,7 @@
       </c>
       <c r="O11" s="99">
         <f>N11+'prorrateo '!L4</f>
-        <v>121482.04433514002</v>
+        <v>190734.84864514001</v>
       </c>
       <c r="P11" s="11"/>
     </row>
@@ -4009,10 +4117,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="117" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12" s="102" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E12" s="103">
         <v>5.04</v>
@@ -4053,7 +4161,7 @@
       </c>
       <c r="O12" s="99">
         <f>N12+'prorrateo '!L5</f>
-        <v>248315.23528783998</v>
+        <v>316887.75664784003</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
@@ -4065,13 +4173,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="91" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="167" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="102" t="s">
         <v>92</v>
-      </c>
-      <c r="C13" s="167" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="102" t="s">
-        <v>93</v>
       </c>
       <c r="E13" s="168">
         <v>5.21</v>
@@ -4112,7 +4220,7 @@
       </c>
       <c r="O13" s="99">
         <f>N13+'prorrateo '!L6</f>
-        <v>108488.83520866002</v>
+        <v>179374.31859866003</v>
       </c>
       <c r="P13" s="11"/>
     </row>
@@ -4124,10 +4232,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="117" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" s="102" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E14" s="103">
         <v>5.1100000000000003</v>
@@ -4168,7 +4276,7 @@
       </c>
       <c r="O14" s="99">
         <f>N14+'prorrateo '!L7</f>
-        <v>105101.52651406002</v>
+        <v>174626.44400406003</v>
       </c>
       <c r="P14" s="11"/>
     </row>
@@ -4180,10 +4288,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="117" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="102" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E15" s="103">
         <v>5.09</v>
@@ -4224,7 +4332,7 @@
       </c>
       <c r="O15" s="99">
         <f>N15+'prorrateo '!L8</f>
-        <v>109280.35563514003</v>
+        <v>178533.15994514001</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -4235,10 +4343,10 @@
         <v>8</v>
       </c>
       <c r="C16" s="117" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D16" s="102" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E16" s="103">
         <v>5.1100000000000003</v>
@@ -4279,7 +4387,7 @@
       </c>
       <c r="O16" s="99">
         <f>N16+'prorrateo '!L9</f>
-        <v>107042.91741406004</v>
+        <v>176567.83490406006</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -4290,10 +4398,10 @@
         <v>9</v>
       </c>
       <c r="C17" s="193" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" s="194" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E17" s="195">
         <v>5.09</v>
@@ -4334,7 +4442,7 @@
       </c>
       <c r="O17" s="99">
         <f>N17+'prorrateo '!L10</f>
-        <v>101195.91623514</v>
+        <v>170448.72054513998</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -4345,10 +4453,10 @@
         <v>10</v>
       </c>
       <c r="C18" s="117" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" s="102" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E18" s="103">
         <v>5.04</v>
@@ -4389,7 +4497,7 @@
       </c>
       <c r="O18" s="99">
         <f>N18+'prorrateo '!L11</f>
-        <v>106630.07388784</v>
+        <v>175202.59524784001</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4400,10 +4508,10 @@
         <v>11</v>
       </c>
       <c r="C19" s="117" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="110" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E19" s="103">
         <v>5.21</v>
@@ -4444,7 +4552,7 @@
       </c>
       <c r="O19" s="99">
         <f>N19+'prorrateo '!L12</f>
-        <v>125933.21720865997</v>
+        <v>196818.70059865998</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4455,10 +4563,10 @@
         <v>12</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20" s="110" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E20" s="103">
         <v>5.1100000000000003</v>
@@ -4499,7 +4607,7 @@
       </c>
       <c r="O20" s="99">
         <f>N20+'prorrateo '!L13</f>
-        <v>118634.99061406004</v>
+        <v>188159.90810406004</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -4510,10 +4618,10 @@
         <v>13</v>
       </c>
       <c r="C21" s="117" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="102" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E21" s="103">
         <v>5.09</v>
@@ -4554,7 +4662,7 @@
       </c>
       <c r="O21" s="99">
         <f>N21+'prorrateo '!L14</f>
-        <v>219759.49933514002</v>
+        <v>289012.30364514003</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -4565,10 +4673,10 @@
         <v>14</v>
       </c>
       <c r="C22" s="117" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D22" s="102" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E22" s="103">
         <v>5.04</v>
@@ -4609,7 +4717,7 @@
       </c>
       <c r="O22" s="99">
         <f>N22+'prorrateo '!L15</f>
-        <v>273900.65798783995</v>
+        <v>342473.17934783996</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -4620,10 +4728,10 @@
         <v>15</v>
       </c>
       <c r="C23" s="117" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D23" s="102" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E23" s="103">
         <v>5.21</v>
@@ -4664,7 +4772,7 @@
       </c>
       <c r="O23" s="99">
         <f>N23+'prorrateo '!L16</f>
-        <v>112043.36250866002</v>
+        <v>182928.84589866002</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -4675,10 +4783,10 @@
         <v>16</v>
       </c>
       <c r="C24" s="117" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D24" s="102" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E24" s="103">
         <v>5.04</v>
@@ -4719,7 +4827,7 @@
       </c>
       <c r="O24" s="99">
         <f>N24+'prorrateo '!L17</f>
-        <v>212057.41148783997</v>
+        <v>280629.93284784001</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -4730,10 +4838,10 @@
         <v>17</v>
       </c>
       <c r="C25" s="117" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D25" s="102" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E25" s="103">
         <v>5.21</v>
@@ -4774,7 +4882,7 @@
       </c>
       <c r="O25" s="99">
         <f>N25+'prorrateo '!L18</f>
-        <v>221355.33680866001</v>
+        <v>292240.82019866002</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -4785,10 +4893,10 @@
         <v>18</v>
       </c>
       <c r="C26" s="117" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D26" s="102" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E26" s="103">
         <v>7.4</v>
@@ -4829,7 +4937,7 @@
       </c>
       <c r="O26" s="99">
         <f>N26+'prorrateo '!L19</f>
-        <v>169591.3606003999</v>
+        <v>270273.23720039992</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4840,10 +4948,10 @@
         <v>19</v>
       </c>
       <c r="C27" s="204" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D27" s="205" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E27" s="206">
         <v>1.08</v>
@@ -4873,7 +4981,7 @@
       </c>
       <c r="O27" s="99">
         <f>N27+'prorrateo '!L20</f>
-        <v>20984.280061680001</v>
+        <v>35678.391781680002</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -4882,7 +4990,7 @@
       </c>
       <c r="B28" s="92"/>
       <c r="C28" s="172" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D28" s="104"/>
       <c r="E28" s="104">
@@ -4912,14 +5020,14 @@
       </c>
       <c r="O28" s="99">
         <f>N28+'prorrateo '!L21</f>
-        <v>20984.280061680001</v>
+        <v>35678.391781680002</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="100"/>
       <c r="B29" s="92"/>
       <c r="C29" s="161" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D29" s="149"/>
       <c r="E29" s="149">
@@ -4944,14 +5052,14 @@
       </c>
       <c r="O29" s="99">
         <f>N29+'prorrateo '!L22</f>
-        <v>221115.02646168001</v>
+        <v>235809.13818168003</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="100"/>
       <c r="B30" s="92"/>
       <c r="C30" s="172" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D30" s="104"/>
       <c r="E30" s="104">
@@ -4976,14 +5084,14 @@
       </c>
       <c r="O30" s="99">
         <f>N30+'prorrateo '!L23</f>
-        <v>20984.280061680001</v>
+        <v>35678.391781680002</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="100"/>
       <c r="B31" s="92"/>
       <c r="C31" s="172" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D31" s="104"/>
       <c r="E31" s="104">
@@ -5008,14 +5116,14 @@
       </c>
       <c r="O31" s="99">
         <f>N31+'prorrateo '!L24</f>
-        <v>20984.280061680001</v>
+        <v>35678.391781680002</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="100"/>
       <c r="B32" s="92"/>
       <c r="C32" s="132" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D32" s="111"/>
       <c r="E32" s="111">
@@ -5040,14 +5148,14 @@
       </c>
       <c r="O32" s="99">
         <f>N32+'prorrateo '!L25</f>
-        <v>44411.892061680002</v>
+        <v>59106.003781680003</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="100"/>
       <c r="B33" s="92"/>
       <c r="C33" s="132" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D33" s="111"/>
       <c r="E33" s="111">
@@ -5072,14 +5180,14 @@
       </c>
       <c r="O33" s="99">
         <f>N33+'prorrateo '!L26</f>
-        <v>20984.280061680001</v>
+        <v>35678.391781680002</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="100"/>
       <c r="B34" s="92"/>
       <c r="C34" s="132" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D34" s="111"/>
       <c r="E34" s="111">
@@ -5104,7 +5212,7 @@
       </c>
       <c r="O34" s="99">
         <f>N34+'prorrateo '!L27</f>
-        <v>20984.280061680001</v>
+        <v>35678.391781680002</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -5113,7 +5221,7 @@
       </c>
       <c r="B35" s="92"/>
       <c r="C35" s="172" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D35" s="104"/>
       <c r="E35" s="104">
@@ -5143,7 +5251,7 @@
       </c>
       <c r="O35" s="99">
         <f>N35+'prorrateo '!L28</f>
-        <v>20984.280061680001</v>
+        <v>35678.391781680002</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -5152,7 +5260,7 @@
       </c>
       <c r="B36" s="92"/>
       <c r="C36" s="172" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D36" s="104"/>
       <c r="E36" s="104">
@@ -5182,7 +5290,7 @@
       </c>
       <c r="O36" s="99">
         <f>N36+'prorrateo '!L29</f>
-        <v>20984.280061680001</v>
+        <v>35678.391781680002</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -5270,20 +5378,20 @@
     </row>
     <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="97" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" s="226"/>
-      <c r="D40" s="224"/>
-      <c r="E40" s="224"/>
-      <c r="F40" s="224"/>
-      <c r="G40" s="224"/>
-      <c r="H40" s="224"/>
-      <c r="I40" s="224"/>
-      <c r="J40" s="224"/>
-      <c r="K40" s="224"/>
-      <c r="L40" s="224"/>
-      <c r="M40" s="224"/>
-      <c r="N40" s="224"/>
+        <v>104</v>
+      </c>
+      <c r="C40" s="228"/>
+      <c r="D40" s="226"/>
+      <c r="E40" s="226"/>
+      <c r="F40" s="226"/>
+      <c r="G40" s="226"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="226"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="226"/>
+      <c r="M40" s="226"/>
+      <c r="N40" s="226"/>
       <c r="O40" s="97"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">

--- a/ROSALES/Septiembre/expensas rosales Septiembre.xlsx
+++ b/ROSALES/Septiembre/expensas rosales Septiembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ROSALES\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4853207-CA0A-49FB-8BF4-8B6CFC875036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720AB209-1F1E-49A9-8420-77A53E3E1FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="143">
   <si>
     <t>TOTAL</t>
   </si>
@@ -455,6 +455,9 @@
   </si>
   <si>
     <t xml:space="preserve">ARBA - REVALUO </t>
+  </si>
+  <si>
+    <t>Silvia del 8B pago el mes pasado pero la pusimos impaga, le enviamos un pdf con eso corregido en donde figura que ella abonando $149035,38 abona sus expensas correctamente, corregir eso para el mes siguiente descontando punitorios</t>
   </si>
 </sst>
 </file>
@@ -701,7 +704,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -771,6 +774,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF09FF09"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1072,7 +1081,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="239">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1161,12 +1170,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1434,6 +1437,9 @@
     <xf numFmtId="174" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1445,9 +1451,20 @@
     <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="19" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="13" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="13" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1866,16 +1883,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F69"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1883,22 +1900,22 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
@@ -1909,51 +1926,51 @@
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="28" t="s">
         <v>121</v>
       </c>
@@ -1964,27 +1981,27 @@
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="208">
+      <c r="C19" s="206">
         <v>236760.8</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="28" t="s">
         <v>127</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="208"/>
+      <c r="C20" s="206"/>
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="28" t="s">
         <v>25</v>
       </c>
@@ -1995,7 +2012,7 @@
       <c r="D21" s="20"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="28" t="s">
         <v>126</v>
       </c>
@@ -2006,7 +2023,7 @@
       <c r="D22" s="20"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="28" t="s">
         <v>11</v>
       </c>
@@ -2022,7 +2039,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="40"/>
       <c r="B24" s="41"/>
       <c r="C24" s="23">
@@ -2030,14 +2047,14 @@
         <v>486670.8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="35" t="s">
         <v>12</v>
       </c>
       <c r="B25" s="39"/>
-      <c r="C25" s="178"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C25" s="176"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="28" t="s">
         <v>113</v>
       </c>
@@ -2049,7 +2066,7 @@
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="28" t="s">
         <v>114</v>
       </c>
@@ -2060,18 +2077,18 @@
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="176" t="s">
+    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="174" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="140"/>
+      <c r="B28" s="138"/>
       <c r="C28" s="33">
         <v>0</v>
       </c>
       <c r="D28" s="45"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="28" t="s">
         <v>135</v>
       </c>
@@ -2081,7 +2098,7 @@
       </c>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="28" t="s">
         <v>136</v>
       </c>
@@ -2091,7 +2108,7 @@
       </c>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="28" t="s">
         <v>107</v>
       </c>
@@ -2104,7 +2121,7 @@
       <c r="E31" s="6"/>
       <c r="F31" s="12"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="40"/>
       <c r="B32" s="41"/>
       <c r="C32" s="23">
@@ -2113,7 +2130,7 @@
       </c>
       <c r="F32" s="12"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="30" t="s">
         <v>6</v>
       </c>
@@ -2124,52 +2141,52 @@
       </c>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C34" s="24"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C35" s="24"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="28"/>
       <c r="B36" s="28"/>
       <c r="C36" s="33"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="28"/>
       <c r="B37" s="28"/>
       <c r="C37" s="34"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="28"/>
       <c r="B38" s="28"/>
       <c r="C38" s="34"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C39" s="25"/>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="179" t="s">
+    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="177" t="s">
         <v>129</v>
       </c>
-      <c r="B40" s="179"/>
-      <c r="C40" s="180"/>
+      <c r="B40" s="177"/>
+      <c r="C40" s="178"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C41" s="25"/>
       <c r="F41" s="12"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>15</v>
       </c>
@@ -2180,7 +2197,7 @@
       </c>
       <c r="E42" s="6"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="18" t="s">
         <v>7</v>
       </c>
@@ -2190,49 +2207,49 @@
         <v>1499999.997</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="220" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="218" t="s">
         <v>128</v>
       </c>
-      <c r="B46" s="221"/>
-      <c r="C46" s="221"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="221"/>
-      <c r="B47" s="221"/>
-      <c r="C47" s="221"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="221"/>
-      <c r="B48" s="221"/>
-      <c r="C48" s="221"/>
-    </row>
-    <row r="49" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="221"/>
-      <c r="B49" s="221"/>
-      <c r="C49" s="221"/>
+      <c r="B46" s="219"/>
+      <c r="C46" s="219"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="219"/>
+      <c r="B47" s="219"/>
+      <c r="C47" s="219"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="219"/>
+      <c r="B48" s="219"/>
+      <c r="C48" s="219"/>
+    </row>
+    <row r="49" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="219"/>
+      <c r="B49" s="219"/>
+      <c r="C49" s="219"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
     </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
-      <c r="C50" s="157"/>
+      <c r="C50" s="155"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="210" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="208" t="s">
         <v>116</v>
       </c>
       <c r="B51" s="28"/>
-      <c r="C51" s="211">
+      <c r="C51" s="209">
         <v>675304.75117282523</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="210" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="208" t="s">
         <v>134</v>
       </c>
       <c r="B52" s="28"/>
@@ -2243,8 +2260,8 @@
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="210" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="208" t="s">
         <v>141</v>
       </c>
       <c r="B53" s="28"/>
@@ -2254,69 +2271,69 @@
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="210" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="208" t="s">
         <v>112</v>
       </c>
       <c r="B54" s="28"/>
-      <c r="C54" s="212">
+      <c r="C54" s="210">
         <f>'prorrateo '!F31</f>
         <v>2045051.5300000003</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="210" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="208" t="s">
         <v>138</v>
       </c>
       <c r="B55" s="28"/>
-      <c r="C55" s="212">
+      <c r="C55" s="210">
         <v>107386.2</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="210" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="208" t="s">
         <v>137</v>
       </c>
       <c r="B56" s="28"/>
-      <c r="C56" s="213">
+      <c r="C56" s="211">
         <v>-376000</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="210" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="208" t="s">
         <v>8</v>
       </c>
       <c r="B57" s="28"/>
-      <c r="C57" s="211">
+      <c r="C57" s="209">
         <f>SUM(C49:C56)</f>
         <v>149754.72417282569</v>
       </c>
       <c r="D57" s="5"/>
     </row>
-    <row r="58" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9"/>
       <c r="B58" s="8"/>
       <c r="C58" s="10"/>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="216"/>
-      <c r="B59" s="216"/>
-      <c r="C59" s="216"/>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="214"/>
+      <c r="B59" s="214"/>
+      <c r="C59" s="214"/>
       <c r="F59" s="44"/>
     </row>
-    <row r="60" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="217"/>
-      <c r="B60" s="217"/>
-      <c r="C60" s="217"/>
-    </row>
-    <row r="61" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="215"/>
+      <c r="B60" s="215"/>
+      <c r="C60" s="215"/>
+    </row>
+    <row r="61" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="26" t="s">
         <v>20</v>
       </c>
       <c r="B61" s="27"/>
       <c r="C61" s="29"/>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="28" t="s">
         <v>23</v>
       </c>
@@ -2326,44 +2343,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="28"/>
       <c r="B63" s="28"/>
       <c r="C63" s="31"/>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="28"/>
       <c r="B64" s="28"/>
       <c r="C64" s="32"/>
     </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="158" t="s">
-        <v>0</v>
-      </c>
-      <c r="B65" s="159"/>
-      <c r="C65" s="160">
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="156" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="157"/>
+      <c r="C65" s="158">
         <f>SUM(C61:C64)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="218" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="216" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="219"/>
-      <c r="C66" s="219"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="219"/>
-      <c r="B67" s="219"/>
-      <c r="C67" s="219"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="219"/>
-      <c r="B68" s="219"/>
-      <c r="C68" s="219"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="217"/>
+      <c r="C66" s="217"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="217"/>
+      <c r="B67" s="217"/>
+      <c r="C67" s="217"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="217"/>
+      <c r="B68" s="217"/>
+      <c r="C68" s="217"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -2390,58 +2407,58 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="11"/>
+    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" customWidth="1"/>
+    <col min="11" max="11" width="10.109375" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" style="11"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="222">
+      <c r="B1" s="220">
         <v>1500000</v>
       </c>
-      <c r="C1" s="222"/>
-      <c r="D1" s="141" t="s">
+      <c r="C1" s="220"/>
+      <c r="D1" s="139" t="s">
         <v>131</v>
       </c>
       <c r="E1" t="s">
         <v>118</v>
       </c>
-      <c r="G1" s="224"/>
-      <c r="H1" s="224"/>
-      <c r="I1" s="230" t="s">
+      <c r="G1" s="222"/>
+      <c r="H1" s="222"/>
+      <c r="I1" s="223" t="s">
         <v>140</v>
       </c>
-      <c r="J1" s="230"/>
-      <c r="K1" s="222">
+      <c r="J1" s="223"/>
+      <c r="K1" s="220">
         <v>1360565.9</v>
       </c>
-      <c r="L1" s="222"/>
-    </row>
-    <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L1" s="220"/>
+    </row>
+    <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="46" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="139" t="s">
+      <c r="C2" s="137" t="s">
         <v>105</v>
       </c>
       <c r="D2" s="47" t="s">
@@ -2456,7 +2473,7 @@
       <c r="G2" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="209" t="s">
+      <c r="H2" s="207" t="s">
         <v>108</v>
       </c>
       <c r="I2" s="50" t="s">
@@ -2472,7 +2489,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="52" t="s">
         <v>31</v>
       </c>
@@ -2485,10 +2502,10 @@
       <c r="D3" s="55">
         <v>5.1100000000000003</v>
       </c>
-      <c r="E3" s="131">
+      <c r="E3" s="129">
         <v>106583.98</v>
       </c>
-      <c r="F3" s="177">
+      <c r="F3" s="175">
         <f>E3</f>
         <v>106583.98</v>
       </c>
@@ -2517,7 +2534,7 @@
         <v>146174.91749000002</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
@@ -2530,10 +2547,10 @@
       <c r="D4" s="61">
         <v>5.09</v>
       </c>
-      <c r="E4" s="131">
+      <c r="E4" s="129">
         <v>106166.82</v>
       </c>
-      <c r="F4" s="177">
+      <c r="F4" s="175">
         <f t="shared" ref="F4:F12" si="0">E4</f>
         <v>106166.82</v>
       </c>
@@ -2562,7 +2579,7 @@
         <v>145602.80430999998</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>35</v>
       </c>
@@ -2575,10 +2592,10 @@
       <c r="D5" s="61">
         <v>5.04</v>
       </c>
-      <c r="E5" s="131">
+      <c r="E5" s="129">
         <v>251925.51</v>
       </c>
-      <c r="F5" s="177">
+      <c r="F5" s="175">
         <f>132535-F23</f>
         <v>110008.45</v>
       </c>
@@ -2607,7 +2624,7 @@
         <v>291766.26376</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="58" t="s">
         <v>38</v>
       </c>
@@ -2618,10 +2635,10 @@
       <c r="D6" s="61">
         <v>5.21</v>
       </c>
-      <c r="E6" s="131">
+      <c r="E6" s="129">
         <v>108669.77</v>
       </c>
-      <c r="F6" s="177">
+      <c r="F6" s="175">
         <f t="shared" ref="F6:F11" si="7">E6</f>
         <v>108669.77</v>
       </c>
@@ -2649,9 +2666,9 @@
         <f t="shared" si="6"/>
         <v>149035.48339000001</v>
       </c>
-      <c r="O6" s="182"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O6" s="180"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>35</v>
       </c>
@@ -2664,10 +2681,10 @@
       <c r="D7" s="61">
         <v>5.1100000000000003</v>
       </c>
-      <c r="E7" s="131">
+      <c r="E7" s="129">
         <v>106583.98</v>
       </c>
-      <c r="F7" s="177">
+      <c r="F7" s="175">
         <f t="shared" si="7"/>
         <v>106583.98</v>
       </c>
@@ -2695,9 +2712,9 @@
         <f t="shared" si="6"/>
         <v>146174.91749000002</v>
       </c>
-      <c r="O7" s="182"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O7" s="180"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="58" t="s">
         <v>41</v>
       </c>
@@ -2708,10 +2725,10 @@
       <c r="D8" s="61">
         <v>5.09</v>
       </c>
-      <c r="E8" s="131">
+      <c r="E8" s="129">
         <v>106166.82</v>
       </c>
-      <c r="F8" s="177">
+      <c r="F8" s="175">
         <f t="shared" si="7"/>
         <v>106166.82</v>
       </c>
@@ -2740,7 +2757,7 @@
         <v>145602.80430999998</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>43</v>
       </c>
@@ -2751,10 +2768,10 @@
       <c r="D9" s="61">
         <v>5.1100000000000003</v>
       </c>
-      <c r="E9" s="131">
+      <c r="E9" s="129">
         <v>106583.98</v>
       </c>
-      <c r="F9" s="177">
+      <c r="F9" s="175">
         <f t="shared" si="7"/>
         <v>106583.98</v>
       </c>
@@ -2782,51 +2799,51 @@
         <f t="shared" si="6"/>
         <v>146174.91749000002</v>
       </c>
-      <c r="O9" s="182"/>
-    </row>
-    <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="185" t="s">
+      <c r="O9" s="180"/>
+    </row>
+    <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="183" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="186" t="s">
+      <c r="B10" s="184" t="s">
         <v>115</v>
       </c>
-      <c r="C10" s="187" t="s">
+      <c r="C10" s="185" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="188">
+      <c r="D10" s="186">
         <v>5.09</v>
       </c>
-      <c r="E10" s="189">
+      <c r="E10" s="187">
         <v>106166.82</v>
       </c>
-      <c r="F10" s="214">
+      <c r="F10" s="212">
         <f t="shared" si="7"/>
         <v>106166.82</v>
       </c>
-      <c r="G10" s="190">
+      <c r="G10" s="188">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H10" s="190"/>
-      <c r="I10" s="190">
+      <c r="H10" s="188"/>
+      <c r="I10" s="188">
         <f t="shared" si="3"/>
         <v>76350</v>
       </c>
-      <c r="J10" s="190">
+      <c r="J10" s="188">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K10" s="190">
+      <c r="K10" s="188">
         <f t="shared" si="5"/>
         <v>69252.804309999992</v>
       </c>
-      <c r="L10" s="191">
+      <c r="L10" s="189">
         <f t="shared" si="6"/>
         <v>145602.80430999998</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>111</v>
       </c>
@@ -2837,10 +2854,10 @@
       <c r="D11" s="61">
         <v>5.04</v>
       </c>
-      <c r="E11" s="131">
+      <c r="E11" s="129">
         <v>105123.92</v>
       </c>
-      <c r="F11" s="177">
+      <c r="F11" s="175">
         <f t="shared" si="7"/>
         <v>105123.92</v>
       </c>
@@ -2869,7 +2886,7 @@
         <v>144172.52136000001</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="58" t="s">
         <v>48</v>
       </c>
@@ -2880,10 +2897,10 @@
       <c r="D12" s="61">
         <v>5.21</v>
       </c>
-      <c r="E12" s="131">
+      <c r="E12" s="129">
         <v>108669.77</v>
       </c>
-      <c r="F12" s="177">
+      <c r="F12" s="175">
         <f t="shared" si="0"/>
         <v>108669.77</v>
       </c>
@@ -2912,7 +2929,7 @@
         <v>149035.48339000001</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>50</v>
       </c>
@@ -2925,10 +2942,10 @@
       <c r="D13" s="61">
         <v>5.1100000000000003</v>
       </c>
-      <c r="E13" s="131">
+      <c r="E13" s="129">
         <v>106583.98</v>
       </c>
-      <c r="F13" s="177">
+      <c r="F13" s="175">
         <f>E13</f>
         <v>106583.98</v>
       </c>
@@ -2957,36 +2974,36 @@
         <v>146174.91749000002</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="64" t="s">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="207" t="s">
+      <c r="B14" s="205" t="s">
         <v>122</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="183">
+      <c r="D14" s="181">
         <v>5.09</v>
       </c>
-      <c r="E14" s="131">
+      <c r="E14" s="129">
         <v>106166.82</v>
       </c>
-      <c r="F14" s="177"/>
-      <c r="G14" s="66">
+      <c r="F14" s="175"/>
+      <c r="G14" s="64">
         <f t="shared" si="1"/>
         <v>106166.82</v>
       </c>
-      <c r="H14" s="66">
+      <c r="H14" s="64">
         <f t="shared" si="2"/>
         <v>4246.6728000000003</v>
       </c>
-      <c r="I14" s="66">
+      <c r="I14" s="64">
         <f t="shared" si="3"/>
         <v>76350</v>
       </c>
-      <c r="J14" s="66">
+      <c r="J14" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2994,12 +3011,12 @@
         <f t="shared" si="5"/>
         <v>69252.804309999992</v>
       </c>
-      <c r="L14" s="184">
+      <c r="L14" s="182">
         <f t="shared" si="6"/>
         <v>256016.29710999998</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>54</v>
       </c>
@@ -3012,10 +3029,10 @@
       <c r="D15" s="61">
         <v>5.04</v>
       </c>
-      <c r="E15" s="131">
+      <c r="E15" s="129">
         <v>503730.43</v>
       </c>
-      <c r="F15" s="177">
+      <c r="F15" s="175">
         <f>447039-F29</f>
         <v>339096.76</v>
       </c>
@@ -3044,7 +3061,7 @@
         <v>315391.53816</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="58" t="s">
         <v>57</v>
       </c>
@@ -3057,10 +3074,10 @@
       <c r="D16" s="61">
         <v>5.21</v>
       </c>
-      <c r="E16" s="131">
+      <c r="E16" s="129">
         <v>108669.77</v>
       </c>
-      <c r="F16" s="177">
+      <c r="F16" s="175">
         <f>E16</f>
         <v>108669.77</v>
       </c>
@@ -3089,7 +3106,7 @@
         <v>149035.48339000001</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>60</v>
       </c>
@@ -3100,10 +3117,10 @@
       <c r="D17" s="61">
         <v>5.04</v>
       </c>
-      <c r="E17" s="131">
+      <c r="E17" s="129">
         <v>105123.92</v>
       </c>
-      <c r="F17" s="177"/>
+      <c r="F17" s="175"/>
       <c r="G17" s="56">
         <f t="shared" si="1"/>
         <v>105123.92</v>
@@ -3129,47 +3146,53 @@
         <v>253501.39815999998</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="62" t="s">
+    <row r="18" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="229" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="63"/>
-      <c r="C18" s="60" t="s">
+      <c r="B18" s="230"/>
+      <c r="C18" s="231" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="61">
+      <c r="D18" s="232">
         <v>5.21</v>
       </c>
-      <c r="E18" s="131">
+      <c r="E18" s="233">
         <v>108669.77</v>
       </c>
-      <c r="F18" s="177"/>
-      <c r="G18" s="56">
+      <c r="F18" s="234"/>
+      <c r="G18" s="235">
         <f t="shared" si="1"/>
         <v>108669.77</v>
       </c>
-      <c r="H18" s="56">
+      <c r="H18" s="235">
         <f t="shared" si="2"/>
         <v>4346.7908000000007</v>
       </c>
-      <c r="I18" s="56">
+      <c r="I18" s="235">
         <f t="shared" si="3"/>
         <v>78150</v>
       </c>
-      <c r="J18" s="56">
+      <c r="J18" s="235">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K18" s="56">
+      <c r="K18" s="235">
         <f t="shared" si="5"/>
         <v>70885.483389999994</v>
       </c>
-      <c r="L18" s="57">
+      <c r="L18" s="236">
         <f t="shared" si="6"/>
         <v>262052.04419000002</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M18" s="237"/>
+      <c r="N18" s="238" t="s">
+        <v>142</v>
+      </c>
+      <c r="O18" s="237"/>
+      <c r="P18" s="237"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>64</v>
       </c>
@@ -3180,10 +3203,10 @@
       <c r="D19" s="61">
         <v>7.4</v>
       </c>
-      <c r="E19" s="131">
+      <c r="E19" s="129">
         <v>154348.62</v>
       </c>
-      <c r="F19" s="177">
+      <c r="F19" s="175">
         <f>E19</f>
         <v>154348.62</v>
       </c>
@@ -3212,61 +3235,61 @@
         <v>211681.87660000002</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="24" x14ac:dyDescent="0.25">
-      <c r="A20" s="192"/>
-      <c r="B20" s="186" t="s">
+    <row r="20" spans="1:16" ht="24" x14ac:dyDescent="0.3">
+      <c r="A20" s="190"/>
+      <c r="B20" s="184" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="187" t="s">
+      <c r="C20" s="185" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="188">
+      <c r="D20" s="186">
         <v>1.08</v>
       </c>
-      <c r="E20" s="189">
+      <c r="E20" s="187">
         <v>22526.55</v>
       </c>
-      <c r="F20" s="214">
+      <c r="F20" s="212">
         <f>E20</f>
         <v>22526.55</v>
       </c>
-      <c r="G20" s="190">
+      <c r="G20" s="188">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H20" s="190"/>
-      <c r="I20" s="190">
+      <c r="H20" s="188"/>
+      <c r="I20" s="188">
         <f t="shared" si="3"/>
         <v>16200</v>
       </c>
-      <c r="J20" s="190">
+      <c r="J20" s="188">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K20" s="190">
+      <c r="K20" s="188">
         <f t="shared" si="5"/>
         <v>14694.111720000001</v>
       </c>
-      <c r="L20" s="191">
+      <c r="L20" s="189">
         <f t="shared" si="6"/>
         <v>30894.111720000001</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="64"/>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21" s="62"/>
       <c r="B21" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="65" t="s">
+      <c r="C21" s="63" t="s">
         <v>67</v>
       </c>
       <c r="D21" s="61">
         <v>1.08</v>
       </c>
-      <c r="E21" s="131">
+      <c r="E21" s="129">
         <v>22526.55</v>
       </c>
-      <c r="F21" s="177">
+      <c r="F21" s="175">
         <f>E21</f>
         <v>22526.55</v>
       </c>
@@ -3295,47 +3318,47 @@
         <v>30894.111720000001</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="142"/>
-      <c r="B22" s="143"/>
-      <c r="C22" s="144" t="s">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" s="140"/>
+      <c r="B22" s="141"/>
+      <c r="C22" s="142" t="s">
         <v>68</v>
       </c>
-      <c r="D22" s="145">
+      <c r="D22" s="143">
         <v>1.08</v>
       </c>
-      <c r="E22" s="146">
+      <c r="E22" s="144">
         <v>192433.41</v>
       </c>
-      <c r="F22" s="181">
-        <v>0</v>
-      </c>
-      <c r="G22" s="147">
+      <c r="F22" s="179">
+        <v>0</v>
+      </c>
+      <c r="G22" s="145">
         <f t="shared" si="1"/>
         <v>192433.41</v>
       </c>
-      <c r="H22" s="147">
+      <c r="H22" s="145">
         <f t="shared" si="2"/>
         <v>7697.3364000000001</v>
       </c>
-      <c r="I22" s="147">
+      <c r="I22" s="145">
         <f t="shared" si="3"/>
         <v>16200</v>
       </c>
-      <c r="J22" s="147">
+      <c r="J22" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K22" s="147">
+      <c r="K22" s="145">
         <f t="shared" si="5"/>
         <v>14694.111720000001</v>
       </c>
-      <c r="L22" s="148">
+      <c r="L22" s="146">
         <f t="shared" si="6"/>
         <v>231024.85812000002</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="58"/>
       <c r="B23" s="59" t="s">
         <v>36</v>
@@ -3346,10 +3369,10 @@
       <c r="D23" s="61">
         <v>1.08</v>
       </c>
-      <c r="E23" s="131">
+      <c r="E23" s="129">
         <v>22526.55</v>
       </c>
-      <c r="F23" s="177">
+      <c r="F23" s="175">
         <f>E23</f>
         <v>22526.55</v>
       </c>
@@ -3378,7 +3401,7 @@
         <v>30894.111720000001</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="58" t="s">
         <v>50</v>
       </c>
@@ -3391,10 +3414,10 @@
       <c r="D24" s="61">
         <v>1.08</v>
       </c>
-      <c r="E24" s="131">
+      <c r="E24" s="129">
         <v>22526.55</v>
       </c>
-      <c r="F24" s="177">
+      <c r="F24" s="175">
         <f t="shared" ref="F24" si="8">E24</f>
         <v>22526.55</v>
       </c>
@@ -3423,11 +3446,11 @@
         <v>30894.111720000001</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="207" t="s">
+      <c r="B25" s="205" t="s">
         <v>122</v>
       </c>
       <c r="C25" s="60" t="s">
@@ -3436,10 +3459,10 @@
       <c r="D25" s="61">
         <v>1.08</v>
       </c>
-      <c r="E25" s="131">
+      <c r="E25" s="129">
         <v>22526.55</v>
       </c>
-      <c r="F25" s="177"/>
+      <c r="F25" s="175"/>
       <c r="G25" s="56">
         <f t="shared" si="1"/>
         <v>22526.55</v>
@@ -3465,7 +3488,7 @@
         <v>54321.723720000002</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="58" t="s">
         <v>64</v>
       </c>
@@ -3476,10 +3499,10 @@
       <c r="D26" s="61">
         <v>1.08</v>
       </c>
-      <c r="E26" s="131">
+      <c r="E26" s="129">
         <v>22526.55</v>
       </c>
-      <c r="F26" s="177">
+      <c r="F26" s="175">
         <f t="shared" ref="F26:F28" si="9">E26</f>
         <v>22526.55</v>
       </c>
@@ -3508,21 +3531,21 @@
         <v>30894.111720000001</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="67"/>
+      <c r="B27" s="65"/>
       <c r="C27" s="60" t="s">
         <v>73</v>
       </c>
       <c r="D27" s="61">
         <v>1.08</v>
       </c>
-      <c r="E27" s="131">
+      <c r="E27" s="129">
         <v>22526.55</v>
       </c>
-      <c r="F27" s="177">
+      <c r="F27" s="175">
         <f t="shared" si="9"/>
         <v>22526.55</v>
       </c>
@@ -3555,9 +3578,9 @@
         <v>199401.72</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="68"/>
-      <c r="B28" s="67" t="str">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" s="66"/>
+      <c r="B28" s="65" t="str">
         <f>B7</f>
         <v>Leandro</v>
       </c>
@@ -3567,10 +3590,10 @@
       <c r="D28" s="61">
         <v>1.08</v>
       </c>
-      <c r="E28" s="131">
+      <c r="E28" s="129">
         <v>22526.55</v>
       </c>
-      <c r="F28" s="177">
+      <c r="F28" s="175">
         <f t="shared" si="9"/>
         <v>22526.55</v>
       </c>
@@ -3599,8 +3622,8 @@
         <v>30894.111720000001</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="68" t="s">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" s="66" t="s">
         <v>54</v>
       </c>
       <c r="B29" s="59" t="s">
@@ -3612,10 +3635,10 @@
       <c r="D29" s="61">
         <v>1.08</v>
       </c>
-      <c r="E29" s="131">
+      <c r="E29" s="129">
         <v>107942.24</v>
       </c>
-      <c r="F29" s="177">
+      <c r="F29" s="175">
         <f>E29</f>
         <v>107942.24</v>
       </c>
@@ -3644,113 +3667,113 @@
         <v>30894.111720000001</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="69"/>
-      <c r="B30" s="69"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="73"/>
-      <c r="K30" s="73"/>
-      <c r="L30" s="73"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="74"/>
-      <c r="B31" s="75"/>
-      <c r="C31" s="76" t="s">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" s="67"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="71"/>
+      <c r="L30" s="71"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" s="72"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="76">
+      <c r="D31" s="74">
         <f>SUM(D3:D30)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="E31" s="75"/>
-      <c r="F31" s="137">
+      <c r="E31" s="73"/>
+      <c r="F31" s="135">
         <f>SUM(F3:F30)</f>
         <v>2045051.5300000003</v>
       </c>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="138">
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
+      <c r="I31" s="136">
         <f>SUM(I3:I30)</f>
         <v>1500000</v>
       </c>
-      <c r="J31" s="138">
+      <c r="J31" s="136">
         <f>SUM(J3:J30)</f>
         <v>0</v>
       </c>
-      <c r="K31" s="137"/>
-      <c r="L31" s="137">
+      <c r="K31" s="135"/>
+      <c r="L31" s="135">
         <f>SUM(L3:L29)</f>
         <v>3735695.9479999999</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="J32" s="22"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="223" t="s">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="221" t="s">
         <v>130</v>
       </c>
-      <c r="B33" s="223"/>
-      <c r="C33" s="223"/>
-      <c r="D33" s="223"/>
-      <c r="E33" s="223"/>
-      <c r="F33" s="223"/>
-      <c r="G33" s="223"/>
-      <c r="H33" s="223"/>
-      <c r="I33" s="223"/>
-      <c r="J33" s="223"/>
-      <c r="K33" s="223"/>
-      <c r="L33" s="223"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="223"/>
-      <c r="B34" s="223"/>
-      <c r="C34" s="223"/>
-      <c r="D34" s="223"/>
-      <c r="E34" s="223"/>
-      <c r="F34" s="223"/>
-      <c r="G34" s="223"/>
-      <c r="H34" s="223"/>
-      <c r="I34" s="223"/>
-      <c r="J34" s="223"/>
-      <c r="K34" s="223"/>
-      <c r="L34" s="223"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="223"/>
-      <c r="B35" s="223"/>
-      <c r="C35" s="223"/>
-      <c r="D35" s="223"/>
-      <c r="E35" s="223"/>
-      <c r="F35" s="223"/>
-      <c r="G35" s="223"/>
-      <c r="H35" s="223"/>
-      <c r="I35" s="223"/>
-      <c r="J35" s="223"/>
-      <c r="K35" s="223"/>
-      <c r="L35" s="223"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="223"/>
-      <c r="B36" s="223"/>
-      <c r="C36" s="223"/>
-      <c r="D36" s="223"/>
-      <c r="E36" s="223"/>
-      <c r="F36" s="223"/>
-      <c r="G36" s="223"/>
-      <c r="H36" s="223"/>
-      <c r="I36" s="223"/>
-      <c r="J36" s="223"/>
-      <c r="K36" s="223"/>
-      <c r="L36" s="223"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B33" s="221"/>
+      <c r="C33" s="221"/>
+      <c r="D33" s="221"/>
+      <c r="E33" s="221"/>
+      <c r="F33" s="221"/>
+      <c r="G33" s="221"/>
+      <c r="H33" s="221"/>
+      <c r="I33" s="221"/>
+      <c r="J33" s="221"/>
+      <c r="K33" s="221"/>
+      <c r="L33" s="221"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="221"/>
+      <c r="B34" s="221"/>
+      <c r="C34" s="221"/>
+      <c r="D34" s="221"/>
+      <c r="E34" s="221"/>
+      <c r="F34" s="221"/>
+      <c r="G34" s="221"/>
+      <c r="H34" s="221"/>
+      <c r="I34" s="221"/>
+      <c r="J34" s="221"/>
+      <c r="K34" s="221"/>
+      <c r="L34" s="221"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="221"/>
+      <c r="B35" s="221"/>
+      <c r="C35" s="221"/>
+      <c r="D35" s="221"/>
+      <c r="E35" s="221"/>
+      <c r="F35" s="221"/>
+      <c r="G35" s="221"/>
+      <c r="H35" s="221"/>
+      <c r="I35" s="221"/>
+      <c r="J35" s="221"/>
+      <c r="K35" s="221"/>
+      <c r="L35" s="221"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="221"/>
+      <c r="B36" s="221"/>
+      <c r="C36" s="221"/>
+      <c r="D36" s="221"/>
+      <c r="E36" s="221"/>
+      <c r="F36" s="221"/>
+      <c r="G36" s="221"/>
+      <c r="H36" s="221"/>
+      <c r="I36" s="221"/>
+      <c r="J36" s="221"/>
+      <c r="K36" s="221"/>
+      <c r="L36" s="221"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
@@ -3770,396 +3793,396 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="6" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="225" t="s">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="224" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="226"/>
-      <c r="C1" s="226"/>
-      <c r="D1" s="226"/>
-      <c r="E1" s="226"/>
-      <c r="F1" s="226"/>
-      <c r="G1" s="226"/>
-      <c r="H1" s="226"/>
-      <c r="I1" s="226"/>
-      <c r="J1" s="226"/>
-      <c r="K1" s="226"/>
-      <c r="L1" s="226"/>
-      <c r="M1" s="226"/>
-      <c r="N1" s="227"/>
-      <c r="O1" s="78"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
-      <c r="G2" s="164"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="164"/>
-      <c r="J2" s="164"/>
-      <c r="K2" s="164"/>
-      <c r="L2" s="164"/>
-      <c r="M2" s="164"/>
-      <c r="N2" s="164"/>
-      <c r="O2" s="80"/>
+      <c r="B1" s="225"/>
+      <c r="C1" s="225"/>
+      <c r="D1" s="225"/>
+      <c r="E1" s="225"/>
+      <c r="F1" s="225"/>
+      <c r="G1" s="225"/>
+      <c r="H1" s="225"/>
+      <c r="I1" s="225"/>
+      <c r="J1" s="225"/>
+      <c r="K1" s="225"/>
+      <c r="L1" s="225"/>
+      <c r="M1" s="225"/>
+      <c r="N1" s="226"/>
+      <c r="O1" s="76"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="162"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="162"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="162"/>
+      <c r="J2" s="162"/>
+      <c r="K2" s="162"/>
+      <c r="L2" s="162"/>
+      <c r="M2" s="162"/>
+      <c r="N2" s="162"/>
+      <c r="O2" s="78"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="82"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="166"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="165"/>
-      <c r="I3" s="164"/>
-      <c r="J3" s="164"/>
-      <c r="K3" s="164"/>
-      <c r="L3" s="164"/>
-      <c r="M3" s="164"/>
-      <c r="N3" s="164"/>
-      <c r="O3" s="80"/>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="80"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="163"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="162"/>
+      <c r="K3" s="162"/>
+      <c r="L3" s="162"/>
+      <c r="M3" s="162"/>
+      <c r="N3" s="162"/>
+      <c r="O3" s="78"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="82"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="166"/>
-      <c r="D4" s="166"/>
-      <c r="E4" s="166"/>
-      <c r="F4" s="166"/>
-      <c r="G4" s="166"/>
-      <c r="H4" s="165"/>
-      <c r="I4" s="164" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="80"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="164"/>
+      <c r="D4" s="164"/>
+      <c r="E4" s="164"/>
+      <c r="F4" s="164"/>
+      <c r="G4" s="164"/>
+      <c r="H4" s="163"/>
+      <c r="I4" s="162" t="s">
         <v>77</v>
       </c>
-      <c r="J4" s="164"/>
-      <c r="K4" s="164"/>
-      <c r="L4" s="164"/>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="80"/>
+      <c r="J4" s="162"/>
+      <c r="K4" s="162"/>
+      <c r="L4" s="162"/>
+      <c r="M4" s="162"/>
+      <c r="N4" s="162"/>
+      <c r="O4" s="78"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="82"/>
-      <c r="B5" s="82"/>
-      <c r="C5" s="166"/>
-      <c r="D5" s="166"/>
-      <c r="E5" s="166"/>
-      <c r="F5" s="166"/>
-      <c r="G5" s="166"/>
-      <c r="H5" s="165"/>
-      <c r="I5" s="164"/>
-      <c r="J5" s="164"/>
-      <c r="K5" s="164"/>
-      <c r="L5" s="164"/>
-      <c r="M5" s="164"/>
-      <c r="N5" s="164"/>
-      <c r="O5" s="80"/>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="80"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="164"/>
+      <c r="D5" s="164"/>
+      <c r="E5" s="164"/>
+      <c r="F5" s="164"/>
+      <c r="G5" s="164"/>
+      <c r="H5" s="163"/>
+      <c r="I5" s="162"/>
+      <c r="J5" s="162"/>
+      <c r="K5" s="162"/>
+      <c r="L5" s="162"/>
+      <c r="M5" s="162"/>
+      <c r="N5" s="162"/>
+      <c r="O5" s="78"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="82"/>
-      <c r="B6" s="82"/>
-      <c r="C6" s="164"/>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="80"/>
+      <c r="B6" s="80"/>
+      <c r="C6" s="162"/>
       <c r="D6" s="28"/>
-      <c r="E6" s="164"/>
-      <c r="F6" s="164"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="165"/>
-      <c r="I6" s="164"/>
-      <c r="J6" s="164"/>
-      <c r="K6" s="164"/>
-      <c r="L6" s="164"/>
-      <c r="M6" s="164"/>
-      <c r="N6" s="164"/>
-      <c r="O6" s="80"/>
+      <c r="E6" s="162"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="162"/>
+      <c r="H6" s="163"/>
+      <c r="I6" s="162"/>
+      <c r="J6" s="162"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="162"/>
+      <c r="O6" s="78"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="83"/>
-      <c r="B7" s="83" t="s">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="81"/>
+      <c r="B7" s="81" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="215">
+      <c r="C7" s="213">
         <v>639397.63</v>
       </c>
       <c r="D7" s="28"/>
-      <c r="E7" s="164"/>
-      <c r="F7" s="164" t="s">
+      <c r="E7" s="162"/>
+      <c r="F7" s="162" t="s">
         <v>109</v>
       </c>
-      <c r="G7" s="164"/>
-      <c r="H7" s="165"/>
-      <c r="I7" s="164"/>
-      <c r="J7" s="164" t="str">
+      <c r="G7" s="162"/>
+      <c r="H7" s="163"/>
+      <c r="I7" s="162"/>
+      <c r="J7" s="162" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 15/10</v>
       </c>
-      <c r="K7" s="164"/>
-      <c r="L7" s="164"/>
-      <c r="M7" s="164"/>
-      <c r="N7" s="164"/>
-      <c r="O7" s="80"/>
+      <c r="K7" s="162"/>
+      <c r="L7" s="162"/>
+      <c r="M7" s="162"/>
+      <c r="N7" s="162"/>
+      <c r="O7" s="78"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="83"/>
-      <c r="B8" s="82" t="s">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="81"/>
+      <c r="B8" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="87"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="84"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="88">
+      <c r="C8" s="85"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="78"/>
+      <c r="K8" s="86">
         <f>C8-J38</f>
         <v>-196408.73539999995</v>
       </c>
-      <c r="L8" s="229">
+      <c r="L8" s="228">
         <f>C7-J38</f>
         <v>442988.89460000006</v>
       </c>
-      <c r="M8" s="229"/>
-      <c r="N8" s="86"/>
-      <c r="O8" s="80"/>
+      <c r="M8" s="228"/>
+      <c r="N8" s="84"/>
+      <c r="O8" s="78"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="89" t="s">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="87" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="89" t="s">
+      <c r="B9" s="87" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="121" t="s">
+      <c r="C9" s="119" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="122" t="s">
+      <c r="D9" s="120" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="122" t="s">
+      <c r="E9" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="120" t="s">
+      <c r="F9" s="118" t="s">
         <v>82</v>
       </c>
-      <c r="G9" s="120" t="s">
+      <c r="G9" s="118" t="s">
         <v>83</v>
       </c>
-      <c r="H9" s="123" t="s">
+      <c r="H9" s="121" t="s">
         <v>86</v>
       </c>
-      <c r="I9" s="124" t="s">
+      <c r="I9" s="122" t="s">
         <v>84</v>
       </c>
-      <c r="J9" s="125" t="s">
+      <c r="J9" s="123" t="s">
         <v>78</v>
       </c>
-      <c r="K9" s="126" t="s">
+      <c r="K9" s="124" t="s">
         <v>85</v>
       </c>
-      <c r="L9" s="126" t="s">
+      <c r="L9" s="124" t="s">
         <v>85</v>
       </c>
-      <c r="M9" s="127" t="s">
+      <c r="M9" s="125" t="s">
         <v>86</v>
       </c>
-      <c r="N9" s="120" t="s">
+      <c r="N9" s="118" t="s">
         <v>87</v>
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="100">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="98">
         <v>1</v>
       </c>
-      <c r="B10" s="90">
+      <c r="B10" s="88">
         <v>1</v>
       </c>
-      <c r="C10" s="117" t="s">
+      <c r="C10" s="115" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="102" t="s">
+      <c r="D10" s="100" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="103">
+      <c r="E10" s="101">
         <v>5.1100000000000003</v>
       </c>
-      <c r="F10" s="105">
+      <c r="F10" s="103">
         <v>3850.8</v>
       </c>
-      <c r="G10" s="105">
+      <c r="G10" s="103">
         <v>4075</v>
       </c>
-      <c r="H10" s="106">
+      <c r="H10" s="104">
         <f>G10-F10</f>
         <v>224.19999999999982</v>
       </c>
-      <c r="I10" s="107">
+      <c r="I10" s="105">
         <f t="shared" ref="I10:I37" si="0">H10*7%</f>
         <v>15.693999999999988</v>
       </c>
-      <c r="J10" s="118">
+      <c r="J10" s="116">
         <f>M10*93.787</f>
         <v>21027.045399999985</v>
       </c>
-      <c r="K10" s="108">
+      <c r="K10" s="106">
         <f>K8*E10%</f>
         <v>-10036.486378939999</v>
       </c>
-      <c r="L10" s="129">
+      <c r="L10" s="127">
         <f>L$8*E10/S$12</f>
         <v>22636.732514060004</v>
       </c>
-      <c r="M10" s="109">
+      <c r="M10" s="107">
         <f>G10-F10</f>
         <v>224.19999999999982</v>
       </c>
-      <c r="N10" s="106">
+      <c r="N10" s="104">
         <f>J10+L10</f>
         <v>43663.777914059989</v>
       </c>
-      <c r="O10" s="99">
+      <c r="O10" s="97">
         <f>N10+'prorrateo '!L3</f>
         <v>189838.69540406001</v>
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="101">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" s="99">
         <v>2</v>
       </c>
-      <c r="B11" s="91">
+      <c r="B11" s="89">
         <v>2</v>
       </c>
-      <c r="C11" s="117" t="s">
+      <c r="C11" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="102" t="s">
+      <c r="D11" s="100" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="103">
+      <c r="E11" s="101">
         <v>5.09</v>
       </c>
-      <c r="F11" s="105">
+      <c r="F11" s="103">
         <v>3632.1</v>
       </c>
-      <c r="G11" s="105">
+      <c r="G11" s="103">
         <v>3872.9</v>
       </c>
-      <c r="H11" s="106">
+      <c r="H11" s="104">
         <f t="shared" ref="H11:H27" si="1">G11-F11</f>
         <v>240.80000000000018</v>
       </c>
-      <c r="I11" s="107">
+      <c r="I11" s="105">
         <f t="shared" si="0"/>
         <v>16.856000000000016</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="116">
         <f t="shared" ref="J11:J26" si="2">M11*93.787</f>
         <v>22583.909600000017</v>
       </c>
-      <c r="K11" s="108">
+      <c r="K11" s="106">
         <f>K8*E11%</f>
         <v>-9997.2046318599969</v>
       </c>
-      <c r="L11" s="129">
+      <c r="L11" s="127">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
         <v>22548.134735140004</v>
       </c>
-      <c r="M11" s="109">
+      <c r="M11" s="107">
         <f t="shared" ref="M11:M26" si="4">G11-F11</f>
         <v>240.80000000000018</v>
       </c>
-      <c r="N11" s="106">
+      <c r="N11" s="104">
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
         <v>45132.044335140017</v>
       </c>
-      <c r="O11" s="99">
+      <c r="O11" s="97">
         <f>N11+'prorrateo '!L4</f>
         <v>190734.84864514001</v>
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="100">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="98">
         <v>3</v>
       </c>
-      <c r="B12" s="91">
+      <c r="B12" s="89">
         <v>3</v>
       </c>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="102" t="s">
+      <c r="D12" s="100" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="103">
+      <c r="E12" s="101">
         <v>5.04</v>
       </c>
-      <c r="F12" s="105">
+      <c r="F12" s="103">
         <v>1394.3</v>
       </c>
-      <c r="G12" s="105">
+      <c r="G12" s="103">
         <v>1424.1</v>
       </c>
-      <c r="H12" s="106">
+      <c r="H12" s="104">
         <f t="shared" si="1"/>
         <v>29.799999999999955</v>
       </c>
-      <c r="I12" s="107">
+      <c r="I12" s="105">
         <f t="shared" si="0"/>
         <v>2.0859999999999972</v>
       </c>
-      <c r="J12" s="118">
+      <c r="J12" s="116">
         <f t="shared" si="2"/>
         <v>2794.8525999999961</v>
       </c>
-      <c r="K12" s="108">
+      <c r="K12" s="106">
         <f>K8*E12%</f>
         <v>-9899.0002641599967</v>
       </c>
-      <c r="L12" s="129">
+      <c r="L12" s="127">
         <f t="shared" si="3"/>
         <v>22326.640287840004</v>
       </c>
-      <c r="M12" s="109">
+      <c r="M12" s="107">
         <f>G12-F12</f>
         <v>29.799999999999955</v>
       </c>
-      <c r="N12" s="106">
+      <c r="N12" s="104">
         <f t="shared" si="5"/>
         <v>25121.492887839999</v>
       </c>
-      <c r="O12" s="99">
+      <c r="O12" s="97">
         <f>N12+'prorrateo '!L5</f>
         <v>316887.75664784003</v>
       </c>
@@ -4168,1257 +4191,1257 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="100">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="98">
         <v>4</v>
       </c>
-      <c r="B13" s="91" t="s">
+      <c r="B13" s="89" t="s">
         <v>91</v>
       </c>
-      <c r="C13" s="167" t="s">
+      <c r="C13" s="165" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="102" t="s">
+      <c r="D13" s="100" t="s">
         <v>92</v>
       </c>
-      <c r="E13" s="168">
+      <c r="E13" s="166">
         <v>5.21</v>
       </c>
-      <c r="F13" s="105">
+      <c r="F13" s="103">
         <v>981.5</v>
       </c>
-      <c r="G13" s="105">
+      <c r="G13" s="103">
         <v>1058.9000000000001</v>
       </c>
-      <c r="H13" s="106">
+      <c r="H13" s="104">
         <f t="shared" si="1"/>
         <v>77.400000000000091</v>
       </c>
-      <c r="I13" s="169">
+      <c r="I13" s="167">
         <f t="shared" si="0"/>
         <v>5.4180000000000073</v>
       </c>
-      <c r="J13" s="118">
+      <c r="J13" s="116">
         <f t="shared" si="2"/>
         <v>7259.1138000000092</v>
       </c>
-      <c r="K13" s="170">
+      <c r="K13" s="168">
         <f>K8*E13%</f>
         <v>-10232.895114339997</v>
       </c>
-      <c r="L13" s="129">
+      <c r="L13" s="127">
         <f t="shared" si="3"/>
         <v>23079.721408660003</v>
       </c>
-      <c r="M13" s="171">
+      <c r="M13" s="169">
         <f t="shared" si="4"/>
         <v>77.400000000000091</v>
       </c>
-      <c r="N13" s="106">
+      <c r="N13" s="104">
         <f t="shared" si="5"/>
         <v>30338.835208660013</v>
       </c>
-      <c r="O13" s="99">
+      <c r="O13" s="97">
         <f>N13+'prorrateo '!L6</f>
         <v>179374.31859866003</v>
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="100">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="98">
         <v>6</v>
       </c>
-      <c r="B14" s="91">
+      <c r="B14" s="89">
         <v>6</v>
       </c>
-      <c r="C14" s="117" t="s">
+      <c r="C14" s="115" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="102" t="s">
+      <c r="D14" s="100" t="s">
         <v>93</v>
       </c>
-      <c r="E14" s="103">
+      <c r="E14" s="101">
         <v>5.1100000000000003</v>
       </c>
-      <c r="F14" s="105">
+      <c r="F14" s="103">
         <v>1583.5</v>
       </c>
-      <c r="G14" s="105">
+      <c r="G14" s="103">
         <v>1645.5</v>
       </c>
-      <c r="H14" s="106">
+      <c r="H14" s="104">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
-      <c r="I14" s="107">
+      <c r="I14" s="105">
         <f t="shared" si="0"/>
         <v>4.3400000000000007</v>
       </c>
-      <c r="J14" s="118">
+      <c r="J14" s="116">
         <f t="shared" si="2"/>
         <v>5814.7940000000008</v>
       </c>
-      <c r="K14" s="108">
+      <c r="K14" s="106">
         <f>K8*E14%</f>
         <v>-10036.486378939999</v>
       </c>
-      <c r="L14" s="129">
+      <c r="L14" s="127">
         <f t="shared" si="3"/>
         <v>22636.732514060004</v>
       </c>
-      <c r="M14" s="109">
+      <c r="M14" s="107">
         <f t="shared" si="4"/>
         <v>62</v>
       </c>
-      <c r="N14" s="106">
+      <c r="N14" s="104">
         <f t="shared" si="5"/>
         <v>28451.526514060006</v>
       </c>
-      <c r="O14" s="99">
+      <c r="O14" s="97">
         <f>N14+'prorrateo '!L7</f>
         <v>174626.44400406003</v>
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="100">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="98">
         <v>7</v>
       </c>
-      <c r="B15" s="91">
+      <c r="B15" s="89">
         <v>7</v>
       </c>
-      <c r="C15" s="117" t="s">
+      <c r="C15" s="115" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="102" t="s">
+      <c r="D15" s="100" t="s">
         <v>93</v>
       </c>
-      <c r="E15" s="103">
+      <c r="E15" s="101">
         <v>5.09</v>
       </c>
-      <c r="F15" s="105">
+      <c r="F15" s="103">
         <v>2726.2</v>
       </c>
-      <c r="G15" s="105">
+      <c r="G15" s="103">
         <v>2836.9</v>
       </c>
-      <c r="H15" s="106">
+      <c r="H15" s="104">
         <f t="shared" si="1"/>
         <v>110.70000000000027</v>
       </c>
-      <c r="I15" s="107">
+      <c r="I15" s="105">
         <f t="shared" si="0"/>
         <v>7.7490000000000201</v>
       </c>
-      <c r="J15" s="118">
+      <c r="J15" s="116">
         <f t="shared" si="2"/>
         <v>10382.220900000026</v>
       </c>
-      <c r="K15" s="108">
+      <c r="K15" s="106">
         <f>K8*E15%</f>
         <v>-9997.2046318599969</v>
       </c>
-      <c r="L15" s="129">
+      <c r="L15" s="127">
         <f t="shared" si="3"/>
         <v>22548.134735140004</v>
       </c>
-      <c r="M15" s="109">
+      <c r="M15" s="107">
         <f t="shared" si="4"/>
         <v>110.70000000000027</v>
       </c>
-      <c r="N15" s="106">
+      <c r="N15" s="104">
         <f t="shared" si="5"/>
         <v>32930.355635140033</v>
       </c>
-      <c r="O15" s="99">
+      <c r="O15" s="97">
         <f>N15+'prorrateo '!L8</f>
         <v>178533.15994514001</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="100">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="98">
         <v>8</v>
       </c>
-      <c r="B16" s="91">
+      <c r="B16" s="89">
         <v>8</v>
       </c>
-      <c r="C16" s="117" t="s">
+      <c r="C16" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="102" t="s">
+      <c r="D16" s="100" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="103">
+      <c r="E16" s="101">
         <v>5.1100000000000003</v>
       </c>
-      <c r="F16" s="105">
+      <c r="F16" s="103">
         <v>2244.6999999999998</v>
       </c>
-      <c r="G16" s="105">
+      <c r="G16" s="103">
         <v>2327.4</v>
       </c>
-      <c r="H16" s="106">
+      <c r="H16" s="104">
         <f t="shared" si="1"/>
         <v>82.700000000000273</v>
       </c>
-      <c r="I16" s="107">
+      <c r="I16" s="105">
         <f t="shared" si="0"/>
         <v>5.7890000000000192</v>
       </c>
-      <c r="J16" s="118">
+      <c r="J16" s="116">
         <f t="shared" si="2"/>
         <v>7756.1849000000257</v>
       </c>
-      <c r="K16" s="108">
+      <c r="K16" s="106">
         <f>K8*E16%</f>
         <v>-10036.486378939999</v>
       </c>
-      <c r="L16" s="129">
+      <c r="L16" s="127">
         <f t="shared" si="3"/>
         <v>22636.732514060004</v>
       </c>
-      <c r="M16" s="109">
+      <c r="M16" s="107">
         <f t="shared" si="4"/>
         <v>82.700000000000273</v>
       </c>
-      <c r="N16" s="106">
+      <c r="N16" s="104">
         <f t="shared" si="5"/>
         <v>30392.91741406003</v>
       </c>
-      <c r="O16" s="99">
+      <c r="O16" s="97">
         <f>N16+'prorrateo '!L9</f>
         <v>176567.83490406006</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="100">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="98">
         <v>9</v>
       </c>
-      <c r="B17" s="91">
+      <c r="B17" s="89">
         <v>9</v>
       </c>
-      <c r="C17" s="193" t="s">
+      <c r="C17" s="191" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="194" t="s">
+      <c r="D17" s="192" t="s">
         <v>95</v>
       </c>
-      <c r="E17" s="195">
+      <c r="E17" s="193">
         <v>5.09</v>
       </c>
-      <c r="F17" s="197">
+      <c r="F17" s="195">
         <v>3290.2</v>
       </c>
-      <c r="G17" s="197">
+      <c r="G17" s="195">
         <v>3314.7</v>
       </c>
-      <c r="H17" s="198">
+      <c r="H17" s="196">
         <f t="shared" si="1"/>
         <v>24.5</v>
       </c>
-      <c r="I17" s="199">
+      <c r="I17" s="197">
         <f t="shared" si="0"/>
         <v>1.7150000000000001</v>
       </c>
-      <c r="J17" s="200">
+      <c r="J17" s="198">
         <f t="shared" si="2"/>
         <v>2297.7815000000001</v>
       </c>
-      <c r="K17" s="201">
+      <c r="K17" s="199">
         <f>K8*E17%</f>
         <v>-9997.2046318599969</v>
       </c>
-      <c r="L17" s="202">
+      <c r="L17" s="200">
         <f t="shared" si="3"/>
         <v>22548.134735140004</v>
       </c>
-      <c r="M17" s="203">
+      <c r="M17" s="201">
         <f t="shared" si="4"/>
         <v>24.5</v>
       </c>
-      <c r="N17" s="198">
+      <c r="N17" s="196">
         <f t="shared" si="5"/>
         <v>24845.916235140005</v>
       </c>
-      <c r="O17" s="99">
+      <c r="O17" s="97">
         <f>N17+'prorrateo '!L10</f>
         <v>170448.72054513998</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="100">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="98">
         <v>10</v>
       </c>
-      <c r="B18" s="91">
+      <c r="B18" s="89">
         <v>10</v>
       </c>
-      <c r="C18" s="117" t="s">
+      <c r="C18" s="115" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="102" t="s">
+      <c r="D18" s="100" t="s">
         <v>96</v>
       </c>
-      <c r="E18" s="103">
+      <c r="E18" s="101">
         <v>5.04</v>
       </c>
-      <c r="F18" s="105">
+      <c r="F18" s="103">
         <v>1987.7</v>
       </c>
-      <c r="G18" s="105">
+      <c r="G18" s="103">
         <v>2080.5</v>
       </c>
-      <c r="H18" s="106">
+      <c r="H18" s="104">
         <f t="shared" si="1"/>
         <v>92.799999999999955</v>
       </c>
-      <c r="I18" s="107">
+      <c r="I18" s="105">
         <f t="shared" si="0"/>
         <v>6.4959999999999978</v>
       </c>
-      <c r="J18" s="118">
+      <c r="J18" s="116">
         <f t="shared" si="2"/>
         <v>8703.4335999999967</v>
       </c>
-      <c r="K18" s="108">
+      <c r="K18" s="106">
         <f>K8*E18%</f>
         <v>-9899.0002641599967</v>
       </c>
-      <c r="L18" s="129">
+      <c r="L18" s="127">
         <f t="shared" si="3"/>
         <v>22326.640287840004</v>
       </c>
-      <c r="M18" s="109">
+      <c r="M18" s="107">
         <f t="shared" si="4"/>
         <v>92.799999999999955</v>
       </c>
-      <c r="N18" s="106">
+      <c r="N18" s="104">
         <f t="shared" si="5"/>
         <v>31030.073887840001</v>
       </c>
-      <c r="O18" s="99">
+      <c r="O18" s="97">
         <f>N18+'prorrateo '!L11</f>
         <v>175202.59524784001</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="100">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="98">
         <v>11</v>
       </c>
-      <c r="B19" s="91">
+      <c r="B19" s="89">
         <v>11</v>
       </c>
-      <c r="C19" s="117" t="s">
+      <c r="C19" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="110" t="s">
+      <c r="D19" s="108" t="s">
         <v>97</v>
       </c>
-      <c r="E19" s="103">
+      <c r="E19" s="101">
         <v>5.21</v>
       </c>
-      <c r="F19" s="105">
+      <c r="F19" s="103">
         <v>3555.8</v>
       </c>
-      <c r="G19" s="105">
+      <c r="G19" s="103">
         <v>3819.2</v>
       </c>
-      <c r="H19" s="106">
+      <c r="H19" s="104">
         <f t="shared" si="1"/>
         <v>263.39999999999964</v>
       </c>
-      <c r="I19" s="107">
+      <c r="I19" s="105">
         <f t="shared" si="0"/>
         <v>18.437999999999978</v>
       </c>
-      <c r="J19" s="118">
+      <c r="J19" s="116">
         <f t="shared" si="2"/>
         <v>24703.495799999968</v>
       </c>
-      <c r="K19" s="108">
+      <c r="K19" s="106">
         <f>K8*E19%</f>
         <v>-10232.895114339997</v>
       </c>
-      <c r="L19" s="129">
+      <c r="L19" s="127">
         <f t="shared" si="3"/>
         <v>23079.721408660003</v>
       </c>
-      <c r="M19" s="109">
+      <c r="M19" s="107">
         <f>G19-F19</f>
         <v>263.39999999999964</v>
       </c>
-      <c r="N19" s="106">
+      <c r="N19" s="104">
         <f t="shared" si="5"/>
         <v>47783.217208659975</v>
       </c>
-      <c r="O19" s="99">
+      <c r="O19" s="97">
         <f>N19+'prorrateo '!L12</f>
         <v>196818.70059865998</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="100">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="98">
         <v>12</v>
       </c>
-      <c r="B20" s="91">
+      <c r="B20" s="89">
         <v>12</v>
       </c>
-      <c r="C20" s="117" t="s">
+      <c r="C20" s="115" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="110" t="s">
+      <c r="D20" s="108" t="s">
         <v>97</v>
       </c>
-      <c r="E20" s="103">
+      <c r="E20" s="101">
         <v>5.1100000000000003</v>
       </c>
-      <c r="F20" s="105">
+      <c r="F20" s="103">
         <v>5174.2</v>
       </c>
-      <c r="G20" s="105">
+      <c r="G20" s="103">
         <v>5380.5</v>
       </c>
-      <c r="H20" s="106">
+      <c r="H20" s="104">
         <f t="shared" si="1"/>
         <v>206.30000000000018</v>
       </c>
-      <c r="I20" s="107">
+      <c r="I20" s="105">
         <f t="shared" si="0"/>
         <v>14.441000000000015</v>
       </c>
-      <c r="J20" s="118">
+      <c r="J20" s="116">
         <f t="shared" si="2"/>
         <v>19348.258100000017</v>
       </c>
-      <c r="K20" s="108">
+      <c r="K20" s="106">
         <f>K8*E20%</f>
         <v>-10036.486378939999</v>
       </c>
-      <c r="L20" s="129">
+      <c r="L20" s="127">
         <f t="shared" si="3"/>
         <v>22636.732514060004</v>
       </c>
-      <c r="M20" s="109">
+      <c r="M20" s="107">
         <f t="shared" si="4"/>
         <v>206.30000000000018</v>
       </c>
-      <c r="N20" s="106">
+      <c r="N20" s="104">
         <f t="shared" si="5"/>
         <v>41984.990614060021</v>
       </c>
-      <c r="O20" s="99">
+      <c r="O20" s="97">
         <f>N20+'prorrateo '!L13</f>
         <v>188159.90810406004</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="100">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="98">
         <v>13</v>
       </c>
-      <c r="B21" s="91">
+      <c r="B21" s="89">
         <v>13</v>
       </c>
-      <c r="C21" s="117" t="s">
+      <c r="C21" s="115" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="102" t="s">
+      <c r="D21" s="100" t="s">
         <v>98</v>
       </c>
-      <c r="E21" s="103">
+      <c r="E21" s="101">
         <v>5.09</v>
       </c>
-      <c r="F21" s="105">
+      <c r="F21" s="103">
         <v>3739.6</v>
       </c>
-      <c r="G21" s="105">
+      <c r="G21" s="103">
         <v>3851</v>
       </c>
-      <c r="H21" s="106">
+      <c r="H21" s="104">
         <f t="shared" si="1"/>
         <v>111.40000000000009</v>
       </c>
-      <c r="I21" s="107">
+      <c r="I21" s="105">
         <f t="shared" si="0"/>
         <v>7.7980000000000071</v>
       </c>
-      <c r="J21" s="118">
+      <c r="J21" s="116">
         <f t="shared" si="2"/>
         <v>10447.87180000001</v>
       </c>
-      <c r="K21" s="108">
+      <c r="K21" s="106">
         <f>K8*E21%</f>
         <v>-9997.2046318599969</v>
       </c>
-      <c r="L21" s="129">
+      <c r="L21" s="127">
         <f t="shared" si="3"/>
         <v>22548.134735140004</v>
       </c>
-      <c r="M21" s="109">
+      <c r="M21" s="107">
         <f t="shared" si="4"/>
         <v>111.40000000000009</v>
       </c>
-      <c r="N21" s="106">
+      <c r="N21" s="104">
         <f t="shared" si="5"/>
         <v>32996.006535140012</v>
       </c>
-      <c r="O21" s="99">
+      <c r="O21" s="97">
         <f>N21+'prorrateo '!L14</f>
         <v>289012.30364514003</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="100">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="98">
         <v>14</v>
       </c>
-      <c r="B22" s="91">
+      <c r="B22" s="89">
         <v>14</v>
       </c>
-      <c r="C22" s="117" t="s">
+      <c r="C22" s="115" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="102" t="s">
+      <c r="D22" s="100" t="s">
         <v>99</v>
       </c>
-      <c r="E22" s="103">
+      <c r="E22" s="101">
         <v>5.04</v>
       </c>
-      <c r="F22" s="105">
+      <c r="F22" s="103">
         <v>2282.3000000000002</v>
       </c>
-      <c r="G22" s="105">
+      <c r="G22" s="103">
         <v>2333</v>
       </c>
-      <c r="H22" s="106">
+      <c r="H22" s="104">
         <f t="shared" si="1"/>
         <v>50.699999999999818</v>
       </c>
-      <c r="I22" s="107">
+      <c r="I22" s="105">
         <f t="shared" si="0"/>
         <v>3.5489999999999875</v>
       </c>
-      <c r="J22" s="118">
+      <c r="J22" s="116">
         <f t="shared" si="2"/>
         <v>4755.0008999999836</v>
       </c>
-      <c r="K22" s="108">
+      <c r="K22" s="106">
         <f>K8*E22%</f>
         <v>-9899.0002641599967</v>
       </c>
-      <c r="L22" s="129">
+      <c r="L22" s="127">
         <f t="shared" si="3"/>
         <v>22326.640287840004</v>
       </c>
-      <c r="M22" s="109">
+      <c r="M22" s="107">
         <f t="shared" si="4"/>
         <v>50.699999999999818</v>
       </c>
-      <c r="N22" s="106">
+      <c r="N22" s="104">
         <f t="shared" si="5"/>
         <v>27081.641187839989</v>
       </c>
-      <c r="O22" s="99">
+      <c r="O22" s="97">
         <f>N22+'prorrateo '!L15</f>
         <v>342473.17934783996</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="100">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="98">
         <v>15</v>
       </c>
-      <c r="B23" s="91">
+      <c r="B23" s="89">
         <v>15</v>
       </c>
-      <c r="C23" s="117" t="s">
+      <c r="C23" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="102" t="s">
+      <c r="D23" s="100" t="s">
         <v>100</v>
       </c>
-      <c r="E23" s="103">
+      <c r="E23" s="101">
         <v>5.21</v>
       </c>
-      <c r="F23" s="105">
+      <c r="F23" s="103">
         <v>4515.3</v>
       </c>
-      <c r="G23" s="105">
+      <c r="G23" s="103">
         <v>4630.6000000000004</v>
       </c>
-      <c r="H23" s="106">
+      <c r="H23" s="104">
         <f t="shared" si="1"/>
         <v>115.30000000000018</v>
       </c>
-      <c r="I23" s="107">
+      <c r="I23" s="105">
         <f t="shared" si="0"/>
         <v>8.0710000000000139</v>
       </c>
-      <c r="J23" s="118">
+      <c r="J23" s="116">
         <f t="shared" si="2"/>
         <v>10813.641100000017</v>
       </c>
-      <c r="K23" s="108">
+      <c r="K23" s="106">
         <f>K8*E23%</f>
         <v>-10232.895114339997</v>
       </c>
-      <c r="L23" s="129">
+      <c r="L23" s="127">
         <f t="shared" si="3"/>
         <v>23079.721408660003</v>
       </c>
-      <c r="M23" s="109">
+      <c r="M23" s="107">
         <f t="shared" si="4"/>
         <v>115.30000000000018</v>
       </c>
-      <c r="N23" s="106">
+      <c r="N23" s="104">
         <f t="shared" si="5"/>
         <v>33893.362508660022</v>
       </c>
-      <c r="O23" s="99">
+      <c r="O23" s="97">
         <f>N23+'prorrateo '!L16</f>
         <v>182928.84589866002</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="100">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="98">
         <v>16</v>
       </c>
-      <c r="B24" s="91">
+      <c r="B24" s="89">
         <v>16</v>
       </c>
-      <c r="C24" s="117" t="s">
+      <c r="C24" s="115" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="102" t="s">
+      <c r="D24" s="100" t="s">
         <v>101</v>
       </c>
-      <c r="E24" s="103">
+      <c r="E24" s="101">
         <v>5.04</v>
       </c>
-      <c r="F24" s="105">
+      <c r="F24" s="103">
         <v>1624.6</v>
       </c>
-      <c r="G24" s="105">
+      <c r="G24" s="103">
         <v>1675.8</v>
       </c>
-      <c r="H24" s="106">
+      <c r="H24" s="104">
         <f t="shared" si="1"/>
         <v>51.200000000000045</v>
       </c>
-      <c r="I24" s="107">
+      <c r="I24" s="105">
         <f t="shared" si="0"/>
         <v>3.5840000000000036</v>
       </c>
-      <c r="J24" s="118">
+      <c r="J24" s="116">
         <f t="shared" si="2"/>
         <v>4801.8944000000047</v>
       </c>
-      <c r="K24" s="108">
+      <c r="K24" s="106">
         <f>K8*E24%</f>
         <v>-9899.0002641599967</v>
       </c>
-      <c r="L24" s="129">
+      <c r="L24" s="127">
         <f t="shared" si="3"/>
         <v>22326.640287840004</v>
       </c>
-      <c r="M24" s="109">
+      <c r="M24" s="107">
         <f t="shared" si="4"/>
         <v>51.200000000000045</v>
       </c>
-      <c r="N24" s="106">
+      <c r="N24" s="104">
         <f t="shared" si="5"/>
         <v>27128.534687840009</v>
       </c>
-      <c r="O24" s="99">
+      <c r="O24" s="97">
         <f>N24+'prorrateo '!L17</f>
         <v>280629.93284784001</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="100">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="98">
         <v>17</v>
       </c>
-      <c r="B25" s="91">
+      <c r="B25" s="89">
         <v>17</v>
       </c>
-      <c r="C25" s="117" t="s">
+      <c r="C25" s="115" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="102" t="s">
+      <c r="D25" s="100" t="s">
         <v>102</v>
       </c>
-      <c r="E25" s="103">
+      <c r="E25" s="101">
         <v>5.21</v>
       </c>
-      <c r="F25" s="105">
+      <c r="F25" s="103">
         <v>1613.2</v>
       </c>
-      <c r="G25" s="105">
+      <c r="G25" s="103">
         <v>1689</v>
       </c>
-      <c r="H25" s="106">
+      <c r="H25" s="104">
         <f t="shared" si="1"/>
         <v>75.799999999999955</v>
       </c>
-      <c r="I25" s="107">
+      <c r="I25" s="105">
         <f t="shared" si="0"/>
         <v>5.3059999999999974</v>
       </c>
-      <c r="J25" s="118">
+      <c r="J25" s="116">
         <f t="shared" si="2"/>
         <v>7109.0545999999958</v>
       </c>
-      <c r="K25" s="108">
+      <c r="K25" s="106">
         <f>K8*E25%</f>
         <v>-10232.895114339997</v>
       </c>
-      <c r="L25" s="129">
+      <c r="L25" s="127">
         <f t="shared" si="3"/>
         <v>23079.721408660003</v>
       </c>
-      <c r="M25" s="109">
+      <c r="M25" s="107">
         <f t="shared" si="4"/>
         <v>75.799999999999955</v>
       </c>
-      <c r="N25" s="106">
+      <c r="N25" s="104">
         <f t="shared" si="5"/>
         <v>30188.776008659999</v>
       </c>
-      <c r="O25" s="99">
+      <c r="O25" s="97">
         <f>N25+'prorrateo '!L18</f>
         <v>292240.82019866002</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="100">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="98">
         <v>18</v>
       </c>
-      <c r="B26" s="91">
+      <c r="B26" s="89">
         <v>18</v>
       </c>
-      <c r="C26" s="117" t="s">
+      <c r="C26" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="102" t="s">
+      <c r="D26" s="100" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="103">
+      <c r="E26" s="101">
         <v>7.4</v>
       </c>
-      <c r="F26" s="105">
+      <c r="F26" s="103">
         <v>8204.6</v>
       </c>
-      <c r="G26" s="105">
+      <c r="G26" s="103">
         <v>8479.7999999999993</v>
       </c>
-      <c r="H26" s="106">
+      <c r="H26" s="104">
         <f t="shared" si="1"/>
         <v>275.19999999999891</v>
       </c>
-      <c r="I26" s="107">
+      <c r="I26" s="105">
         <f t="shared" si="0"/>
         <v>19.263999999999925</v>
       </c>
-      <c r="J26" s="118">
+      <c r="J26" s="116">
         <f t="shared" si="2"/>
         <v>25810.1823999999</v>
       </c>
-      <c r="K26" s="108">
+      <c r="K26" s="106">
         <f>K8*E26%</f>
         <v>-14534.246419599998</v>
       </c>
-      <c r="L26" s="129">
+      <c r="L26" s="127">
         <f t="shared" si="3"/>
         <v>32781.178200400005</v>
       </c>
-      <c r="M26" s="109">
+      <c r="M26" s="107">
         <f t="shared" si="4"/>
         <v>275.19999999999891</v>
       </c>
-      <c r="N26" s="106">
+      <c r="N26" s="104">
         <f>J26+L26</f>
         <v>58591.360600399901</v>
       </c>
-      <c r="O26" s="99">
+      <c r="O26" s="97">
         <f>N26+'prorrateo '!L19</f>
         <v>270273.23720039992</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="100">
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="98">
         <v>19</v>
       </c>
-      <c r="B27" s="92">
+      <c r="B27" s="90">
         <v>19</v>
       </c>
-      <c r="C27" s="204" t="s">
+      <c r="C27" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="D27" s="205" t="s">
+      <c r="D27" s="203" t="s">
         <v>97</v>
       </c>
-      <c r="E27" s="206">
+      <c r="E27" s="204">
         <v>1.08</v>
       </c>
-      <c r="F27" s="196"/>
-      <c r="G27" s="197"/>
-      <c r="H27" s="198">
+      <c r="F27" s="194"/>
+      <c r="G27" s="195"/>
+      <c r="H27" s="196">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="199">
+      <c r="I27" s="197">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="200"/>
-      <c r="K27" s="201"/>
-      <c r="L27" s="202">
+      <c r="J27" s="198"/>
+      <c r="K27" s="199"/>
+      <c r="L27" s="200">
         <f t="shared" si="3"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="M27" s="203">
-        <v>0</v>
-      </c>
-      <c r="N27" s="198">
+      <c r="M27" s="201">
+        <v>0</v>
+      </c>
+      <c r="N27" s="196">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O27" s="99">
+      <c r="O27" s="97">
         <f>N27+'prorrateo '!L20</f>
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="100">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="98">
         <v>20</v>
       </c>
-      <c r="B28" s="92"/>
-      <c r="C28" s="172" t="s">
+      <c r="B28" s="90"/>
+      <c r="C28" s="170" t="s">
         <v>67</v>
       </c>
-      <c r="D28" s="104"/>
-      <c r="E28" s="104">
+      <c r="D28" s="102"/>
+      <c r="E28" s="102">
         <v>1.08</v>
       </c>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="106">
-        <v>0</v>
-      </c>
-      <c r="I28" s="173">
+      <c r="F28" s="102"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="104">
+        <v>0</v>
+      </c>
+      <c r="I28" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="174"/>
-      <c r="K28" s="108"/>
-      <c r="L28" s="129">
+      <c r="J28" s="172"/>
+      <c r="K28" s="106"/>
+      <c r="L28" s="127">
         <f t="shared" si="3"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="M28" s="109">
-        <v>0</v>
-      </c>
-      <c r="N28" s="106">
+      <c r="M28" s="107">
+        <v>0</v>
+      </c>
+      <c r="N28" s="104">
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O28" s="99">
+      <c r="O28" s="97">
         <f>N28+'prorrateo '!L21</f>
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="100"/>
-      <c r="B29" s="92"/>
-      <c r="C29" s="161" t="s">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="98"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="159" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="149"/>
-      <c r="E29" s="149">
+      <c r="D29" s="147"/>
+      <c r="E29" s="147">
         <v>1.08</v>
       </c>
-      <c r="F29" s="149"/>
-      <c r="G29" s="149"/>
-      <c r="H29" s="150"/>
-      <c r="I29" s="162"/>
-      <c r="J29" s="163"/>
-      <c r="K29" s="151"/>
-      <c r="L29" s="152">
+      <c r="F29" s="147"/>
+      <c r="G29" s="147"/>
+      <c r="H29" s="148"/>
+      <c r="I29" s="160"/>
+      <c r="J29" s="161"/>
+      <c r="K29" s="149"/>
+      <c r="L29" s="150">
         <f t="shared" si="3"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="M29" s="153">
-        <v>0</v>
-      </c>
-      <c r="N29" s="150">
+      <c r="M29" s="151">
+        <v>0</v>
+      </c>
+      <c r="N29" s="148">
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O29" s="99">
+      <c r="O29" s="97">
         <f>N29+'prorrateo '!L22</f>
         <v>235809.13818168003</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="100"/>
-      <c r="B30" s="92"/>
-      <c r="C30" s="172" t="s">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="98"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="170" t="s">
         <v>69</v>
       </c>
-      <c r="D30" s="104"/>
-      <c r="E30" s="104">
+      <c r="D30" s="102"/>
+      <c r="E30" s="102">
         <v>1.08</v>
       </c>
-      <c r="F30" s="104"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="106"/>
-      <c r="I30" s="173"/>
-      <c r="J30" s="174"/>
-      <c r="K30" s="108"/>
-      <c r="L30" s="129">
+      <c r="F30" s="102"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="104"/>
+      <c r="I30" s="171"/>
+      <c r="J30" s="172"/>
+      <c r="K30" s="106"/>
+      <c r="L30" s="127">
         <f t="shared" si="3"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="M30" s="109">
-        <v>0</v>
-      </c>
-      <c r="N30" s="106">
+      <c r="M30" s="107">
+        <v>0</v>
+      </c>
+      <c r="N30" s="104">
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O30" s="99">
+      <c r="O30" s="97">
         <f>N30+'prorrateo '!L23</f>
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="100"/>
-      <c r="B31" s="92"/>
-      <c r="C31" s="172" t="s">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="98"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="170" t="s">
         <v>70</v>
       </c>
-      <c r="D31" s="104"/>
-      <c r="E31" s="104">
+      <c r="D31" s="102"/>
+      <c r="E31" s="102">
         <v>1.08</v>
       </c>
-      <c r="F31" s="104"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="106"/>
-      <c r="I31" s="173"/>
-      <c r="J31" s="174"/>
-      <c r="K31" s="108"/>
-      <c r="L31" s="129">
+      <c r="F31" s="102"/>
+      <c r="G31" s="102"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="171"/>
+      <c r="J31" s="172"/>
+      <c r="K31" s="106"/>
+      <c r="L31" s="127">
         <f t="shared" si="3"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="M31" s="109">
-        <v>0</v>
-      </c>
-      <c r="N31" s="106">
+      <c r="M31" s="107">
+        <v>0</v>
+      </c>
+      <c r="N31" s="104">
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O31" s="99">
+      <c r="O31" s="97">
         <f>N31+'prorrateo '!L24</f>
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="100"/>
-      <c r="B32" s="92"/>
-      <c r="C32" s="132" t="s">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="98"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="130" t="s">
         <v>71</v>
       </c>
-      <c r="D32" s="111"/>
-      <c r="E32" s="111">
+      <c r="D32" s="109"/>
+      <c r="E32" s="109">
         <v>1.08</v>
       </c>
-      <c r="F32" s="111"/>
-      <c r="G32" s="111"/>
-      <c r="H32" s="112"/>
-      <c r="I32" s="113"/>
-      <c r="J32" s="133"/>
-      <c r="K32" s="115"/>
-      <c r="L32" s="129">
+      <c r="F32" s="109"/>
+      <c r="G32" s="109"/>
+      <c r="H32" s="110"/>
+      <c r="I32" s="111"/>
+      <c r="J32" s="131"/>
+      <c r="K32" s="113"/>
+      <c r="L32" s="127">
         <f t="shared" si="3"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="M32" s="109">
-        <v>0</v>
-      </c>
-      <c r="N32" s="106">
+      <c r="M32" s="107">
+        <v>0</v>
+      </c>
+      <c r="N32" s="104">
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O32" s="99">
+      <c r="O32" s="97">
         <f>N32+'prorrateo '!L25</f>
         <v>59106.003781680003</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="100"/>
-      <c r="B33" s="92"/>
-      <c r="C33" s="132" t="s">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" s="98"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="130" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="111"/>
-      <c r="E33" s="111">
+      <c r="D33" s="109"/>
+      <c r="E33" s="109">
         <v>1.08</v>
       </c>
-      <c r="F33" s="111"/>
-      <c r="G33" s="111"/>
-      <c r="H33" s="112"/>
-      <c r="I33" s="113"/>
-      <c r="J33" s="133"/>
-      <c r="K33" s="115"/>
-      <c r="L33" s="129">
+      <c r="F33" s="109"/>
+      <c r="G33" s="109"/>
+      <c r="H33" s="110"/>
+      <c r="I33" s="111"/>
+      <c r="J33" s="131"/>
+      <c r="K33" s="113"/>
+      <c r="L33" s="127">
         <f t="shared" si="3"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="M33" s="109">
-        <v>0</v>
-      </c>
-      <c r="N33" s="106">
+      <c r="M33" s="107">
+        <v>0</v>
+      </c>
+      <c r="N33" s="104">
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O33" s="99">
+      <c r="O33" s="97">
         <f>N33+'prorrateo '!L26</f>
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="100"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="132" t="s">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" s="98"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="111"/>
-      <c r="E34" s="111">
+      <c r="D34" s="109"/>
+      <c r="E34" s="109">
         <v>1.08</v>
       </c>
-      <c r="F34" s="111"/>
-      <c r="G34" s="111"/>
-      <c r="H34" s="112"/>
-      <c r="I34" s="113"/>
-      <c r="J34" s="133"/>
-      <c r="K34" s="115"/>
-      <c r="L34" s="129">
+      <c r="F34" s="109"/>
+      <c r="G34" s="109"/>
+      <c r="H34" s="110"/>
+      <c r="I34" s="111"/>
+      <c r="J34" s="131"/>
+      <c r="K34" s="113"/>
+      <c r="L34" s="127">
         <f t="shared" si="3"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="M34" s="109">
-        <v>0</v>
-      </c>
-      <c r="N34" s="106">
+      <c r="M34" s="107">
+        <v>0</v>
+      </c>
+      <c r="N34" s="104">
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O34" s="99">
+      <c r="O34" s="97">
         <f>N34+'prorrateo '!L27</f>
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="100">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35" s="98">
         <v>21</v>
       </c>
-      <c r="B35" s="92"/>
-      <c r="C35" s="172" t="s">
+      <c r="B35" s="90"/>
+      <c r="C35" s="170" t="s">
         <v>74</v>
       </c>
-      <c r="D35" s="104"/>
-      <c r="E35" s="104">
+      <c r="D35" s="102"/>
+      <c r="E35" s="102">
         <v>1.08</v>
       </c>
-      <c r="F35" s="104"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="106">
-        <v>0</v>
-      </c>
-      <c r="I35" s="173">
+      <c r="F35" s="102"/>
+      <c r="G35" s="102"/>
+      <c r="H35" s="104">
+        <v>0</v>
+      </c>
+      <c r="I35" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="175"/>
-      <c r="K35" s="108"/>
-      <c r="L35" s="129">
+      <c r="J35" s="173"/>
+      <c r="K35" s="106"/>
+      <c r="L35" s="127">
         <f t="shared" si="3"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="M35" s="109">
-        <v>0</v>
-      </c>
-      <c r="N35" s="106">
+      <c r="M35" s="107">
+        <v>0</v>
+      </c>
+      <c r="N35" s="104">
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O35" s="99">
+      <c r="O35" s="97">
         <f>N35+'prorrateo '!L28</f>
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="100">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" s="98">
         <v>22</v>
       </c>
-      <c r="B36" s="92"/>
-      <c r="C36" s="172" t="s">
+      <c r="B36" s="90"/>
+      <c r="C36" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="D36" s="104"/>
-      <c r="E36" s="104">
+      <c r="D36" s="102"/>
+      <c r="E36" s="102">
         <v>1.08</v>
       </c>
-      <c r="F36" s="104"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="106">
-        <v>0</v>
-      </c>
-      <c r="I36" s="173">
+      <c r="F36" s="102"/>
+      <c r="G36" s="102"/>
+      <c r="H36" s="104">
+        <v>0</v>
+      </c>
+      <c r="I36" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J36" s="175"/>
-      <c r="K36" s="108"/>
-      <c r="L36" s="129">
+      <c r="J36" s="173"/>
+      <c r="K36" s="106"/>
+      <c r="L36" s="127">
         <f t="shared" si="3"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="M36" s="109">
-        <v>0</v>
-      </c>
-      <c r="N36" s="106">
+      <c r="M36" s="107">
+        <v>0</v>
+      </c>
+      <c r="N36" s="104">
         <f t="shared" si="6"/>
         <v>4784.2800616800014</v>
       </c>
-      <c r="O36" s="99">
+      <c r="O36" s="97">
         <f>N36+'prorrateo '!L29</f>
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="100">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A37" s="98">
         <v>23</v>
       </c>
-      <c r="B37" s="92"/>
-      <c r="C37" s="111"/>
-      <c r="D37" s="111"/>
-      <c r="E37" s="111"/>
-      <c r="F37" s="111"/>
-      <c r="G37" s="111"/>
-      <c r="H37" s="112">
-        <v>0</v>
-      </c>
-      <c r="I37" s="113">
+      <c r="B37" s="90"/>
+      <c r="C37" s="109"/>
+      <c r="D37" s="109"/>
+      <c r="E37" s="109"/>
+      <c r="F37" s="109"/>
+      <c r="G37" s="109"/>
+      <c r="H37" s="110">
+        <v>0</v>
+      </c>
+      <c r="I37" s="111">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J37" s="134"/>
-      <c r="K37" s="115"/>
-      <c r="L37" s="129">
-        <v>0</v>
-      </c>
-      <c r="M37" s="129">
-        <v>0</v>
-      </c>
-      <c r="N37" s="106">
+      <c r="J37" s="132"/>
+      <c r="K37" s="113"/>
+      <c r="L37" s="127">
+        <v>0</v>
+      </c>
+      <c r="M37" s="127">
+        <v>0</v>
+      </c>
+      <c r="N37" s="104">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="100">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="98">
         <v>24</v>
       </c>
-      <c r="B38" s="92"/>
-      <c r="C38" s="111"/>
-      <c r="D38" s="111"/>
-      <c r="E38" s="130"/>
-      <c r="F38" s="111"/>
-      <c r="G38" s="111"/>
-      <c r="H38" s="112"/>
-      <c r="I38" s="114"/>
-      <c r="J38" s="119">
+      <c r="B38" s="90"/>
+      <c r="C38" s="109"/>
+      <c r="D38" s="109"/>
+      <c r="E38" s="128"/>
+      <c r="F38" s="109"/>
+      <c r="G38" s="109"/>
+      <c r="H38" s="110"/>
+      <c r="I38" s="112"/>
+      <c r="J38" s="117">
         <f>SUM(J10:J37)</f>
         <v>196408.73539999995</v>
       </c>
-      <c r="K38" s="115"/>
-      <c r="L38" s="115">
+      <c r="K38" s="113"/>
+      <c r="L38" s="113">
         <f>SUM(L10:L37)</f>
         <v>442988.89460000017</v>
       </c>
-      <c r="M38" s="116"/>
-      <c r="N38" s="112">
+      <c r="M38" s="114"/>
+      <c r="N38" s="110">
         <f>SUM(N10:N37)</f>
         <v>639397.63000000012</v>
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="80"/>
-      <c r="C39" s="93"/>
-      <c r="D39" s="94"/>
-      <c r="E39" s="136">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="78"/>
+      <c r="C39" s="91"/>
+      <c r="D39" s="92"/>
+      <c r="E39" s="134">
         <f>SUM(E10:E38)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F39" s="94"/>
-      <c r="G39" s="94"/>
-      <c r="H39" s="95"/>
-      <c r="I39" s="96">
+      <c r="F39" s="92"/>
+      <c r="G39" s="92"/>
+      <c r="H39" s="93"/>
+      <c r="I39" s="94">
         <f>SUM(I10:I38)</f>
         <v>146.59399999999997</v>
       </c>
-      <c r="J39" s="128"/>
-      <c r="K39" s="96"/>
-      <c r="L39" s="135">
+      <c r="J39" s="126"/>
+      <c r="K39" s="94"/>
+      <c r="L39" s="133">
         <f>L38+J38</f>
         <v>639397.63000000012</v>
       </c>
-      <c r="M39" s="95"/>
-      <c r="N39" s="95"/>
-      <c r="O39" s="81"/>
-    </row>
-    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="97" t="s">
+      <c r="M39" s="93"/>
+      <c r="N39" s="93"/>
+      <c r="O39" s="79"/>
+    </row>
+    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="C40" s="228"/>
-      <c r="D40" s="226"/>
-      <c r="E40" s="226"/>
-      <c r="F40" s="226"/>
-      <c r="G40" s="226"/>
-      <c r="H40" s="226"/>
-      <c r="I40" s="226"/>
-      <c r="J40" s="226"/>
-      <c r="K40" s="226"/>
-      <c r="L40" s="226"/>
-      <c r="M40" s="226"/>
-      <c r="N40" s="226"/>
-      <c r="O40" s="97"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H41" s="81"/>
-      <c r="J41" s="98"/>
-      <c r="K41" s="98"/>
-      <c r="L41" s="98"/>
-      <c r="N41" s="99"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C40" s="227"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="225"/>
+      <c r="I40" s="225"/>
+      <c r="J40" s="225"/>
+      <c r="K40" s="225"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="225"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="95"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H41" s="79"/>
+      <c r="J41" s="96"/>
+      <c r="K41" s="96"/>
+      <c r="L41" s="96"/>
+      <c r="N41" s="97"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L44" s="154"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L45" s="98"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E46" s="155"/>
-      <c r="F46" s="155"/>
-      <c r="G46" s="155"/>
-      <c r="H46" s="155"/>
-      <c r="I46" s="155"/>
-      <c r="J46" s="155"/>
-      <c r="K46" s="155"/>
-      <c r="L46" s="156"/>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L44" s="152"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L45" s="96"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E46" s="153"/>
+      <c r="F46" s="153"/>
+      <c r="G46" s="153"/>
+      <c r="H46" s="153"/>
+      <c r="I46" s="153"/>
+      <c r="J46" s="153"/>
+      <c r="K46" s="153"/>
+      <c r="L46" s="154"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/ROSALES/Septiembre/expensas rosales Septiembre.xlsx
+++ b/ROSALES/Septiembre/expensas rosales Septiembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ROSALES\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720AB209-1F1E-49A9-8420-77A53E3E1FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{986573CD-D72A-4530-B1ED-659B636901B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="142">
   <si>
     <t>TOTAL</t>
   </si>
@@ -408,9 +408,6 @@
 </t>
   </si>
   <si>
-    <t>TSG MES 8</t>
-  </si>
-  <si>
     <t>ARBA</t>
   </si>
   <si>
@@ -427,21 +424,9 @@
     <t>}</t>
   </si>
   <si>
-    <t>Vto. 15/10</t>
-  </si>
-  <si>
-    <t>LIQUIDACIÓN EXPENSAS SEPTIEMBRE 2025</t>
-  </si>
-  <si>
-    <t>EGRESOS DEL MES DE SEPTIEMBRE</t>
-  </si>
-  <si>
     <t>Fumigacion</t>
   </si>
   <si>
-    <t>Fumigacion - diferencia mes anterior</t>
-  </si>
-  <si>
     <t>ADELANTO PAGO 2 - TERRAZA</t>
   </si>
   <si>
@@ -458,6 +443,18 @@
   </si>
   <si>
     <t>Silvia del 8B pago el mes pasado pero la pusimos impaga, le enviamos un pdf con eso corregido en donde figura que ella abonando $149035,38 abona sus expensas correctamente, corregir eso para el mes siguiente descontando punitorios</t>
+  </si>
+  <si>
+    <t>Vto. 14/11</t>
+  </si>
+  <si>
+    <t>LIQUIDACIÓN EXPENSAS OCTUBRE 2025</t>
+  </si>
+  <si>
+    <t>EGRESOS DEL MES DE OCTUBRE</t>
+  </si>
+  <si>
+    <t>TSG MES 9</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1078,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1398,9 +1395,6 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1410,47 +1404,6 @@
     <xf numFmtId="4" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1465,6 +1418,51 @@
     <xf numFmtId="164" fontId="19" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1883,16 +1881,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F69"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1900,215 +1898,218 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>121</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="33">
+      <c r="C18" s="238">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="206">
-        <v>236760.8</v>
+      <c r="C19" s="239">
+        <v>320979.07</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="206"/>
+      <c r="C20" s="239">
+        <v>663170.30000000005</v>
+      </c>
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="33">
-        <v>75000</v>
+      <c r="C21" s="239">
+        <v>697395.6</v>
       </c>
       <c r="D21" s="20"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="B22" s="39"/>
-      <c r="C22" s="33">
-        <v>14856</v>
+      <c r="C22" s="238">
+        <v>75000</v>
       </c>
       <c r="D22" s="20"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="39"/>
+      <c r="C23" s="238">
+        <v>15748</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B24" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="33">
+      <c r="C24" s="238">
         <v>83400</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="6"/>
-      <c r="F23" t="s">
+      <c r="D24" s="4"/>
+      <c r="E24" s="6"/>
+      <c r="F24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="40"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="23">
-        <f>SUM(C17:C23)</f>
-        <v>486670.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="35" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="40"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="23">
+        <f>SUM(C17:C24)</f>
+        <v>1932346.9700000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="176"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="28" t="s">
+      <c r="B26" s="39"/>
+      <c r="C26" s="176"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="33">
+      <c r="B27" s="42"/>
+      <c r="C27" s="33">
         <f>349151.87+ (349151.87*10%)</f>
         <v>384067.05699999997</v>
       </c>
-      <c r="D26" s="45"/>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="B27" s="42"/>
-      <c r="C27" s="33">
-        <v>5684</v>
-      </c>
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="174" t="s">
-        <v>123</v>
-      </c>
-      <c r="B28" s="138"/>
-      <c r="C28" s="33">
-        <v>0</v>
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="42"/>
+      <c r="C28" s="238">
+        <v>5684</v>
       </c>
       <c r="D28" s="45"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="B29" s="42"/>
-      <c r="C29" s="33">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="174" t="s">
+        <v>123</v>
+      </c>
+      <c r="B29" s="138"/>
+      <c r="C29" s="238">
+        <v>41110</v>
+      </c>
+      <c r="D29" s="45"/>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" s="42"/>
+      <c r="C30" s="238">
         <v>55000</v>
       </c>
-      <c r="F29" s="12"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="33">
-        <v>10000</v>
-      </c>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
         <v>107</v>
       </c>
@@ -2121,72 +2122,72 @@
       <c r="E31" s="6"/>
       <c r="F31" s="12"/>
     </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="40"/>
       <c r="B32" s="41"/>
       <c r="C32" s="23">
-        <f>SUM(C25:C31)</f>
-        <v>1013329.1969999999</v>
+        <f>SUM(C26:C31)</f>
+        <v>1044439.1969999999</v>
       </c>
       <c r="F32" s="12"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="30" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="30"/>
       <c r="C33" s="43">
-        <f>+C32+C24</f>
-        <v>1499999.997</v>
+        <f>+C32+C25</f>
+        <v>2976786.1670000004</v>
       </c>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C34" s="24"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C35" s="24"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="28"/>
       <c r="B36" s="28"/>
       <c r="C36" s="33"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="28"/>
       <c r="B37" s="28"/>
       <c r="C37" s="34"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="28"/>
       <c r="B38" s="28"/>
       <c r="C38" s="34"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C39" s="25"/>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="177" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B40" s="177"/>
       <c r="C40" s="178"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C41" s="25"/>
       <c r="F41" s="12"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>15</v>
       </c>
@@ -2197,72 +2198,72 @@
       </c>
       <c r="E42" s="6"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="18" t="s">
         <v>7</v>
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="19">
         <f>+C42+C33</f>
-        <v>1499999.997</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="218" t="s">
-        <v>128</v>
-      </c>
-      <c r="B46" s="219"/>
-      <c r="C46" s="219"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="219"/>
-      <c r="B47" s="219"/>
-      <c r="C47" s="219"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="219"/>
-      <c r="B48" s="219"/>
-      <c r="C48" s="219"/>
-    </row>
-    <row r="49" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="219"/>
-      <c r="B49" s="219"/>
-      <c r="C49" s="219"/>
+        <v>2976786.1670000004</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="227" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" s="228"/>
+      <c r="C46" s="228"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="228"/>
+      <c r="B47" s="228"/>
+      <c r="C47" s="228"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="228"/>
+      <c r="B48" s="228"/>
+      <c r="C48" s="228"/>
+    </row>
+    <row r="49" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="228"/>
+      <c r="B49" s="228"/>
+      <c r="C49" s="228"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
     </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="C50" s="155"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="208" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="207" t="s">
         <v>116</v>
       </c>
       <c r="B51" s="28"/>
-      <c r="C51" s="209">
+      <c r="C51" s="208">
         <v>675304.75117282523</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="208" t="s">
-        <v>134</v>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="207" t="s">
+        <v>140</v>
       </c>
       <c r="B52" s="28"/>
       <c r="C52" s="31">
         <f>-(C33-C31)</f>
-        <v>-941421.85699999996</v>
+        <v>-2418208.0270000002</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="208" t="s">
-        <v>141</v>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="207" t="s">
+        <v>136</v>
       </c>
       <c r="B53" s="28"/>
       <c r="C53" s="31">
@@ -2271,69 +2272,69 @@
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="208" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="207" t="s">
         <v>112</v>
       </c>
       <c r="B54" s="28"/>
-      <c r="C54" s="210">
+      <c r="C54" s="209">
         <f>'prorrateo '!F31</f>
         <v>2045051.5300000003</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="208" t="s">
-        <v>138</v>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="207" t="s">
+        <v>133</v>
       </c>
       <c r="B55" s="28"/>
-      <c r="C55" s="210">
+      <c r="C55" s="209">
         <v>107386.2</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="208" t="s">
-        <v>137</v>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="207" t="s">
+        <v>132</v>
       </c>
       <c r="B56" s="28"/>
-      <c r="C56" s="211">
+      <c r="C56" s="210">
         <v>-376000</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="208" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="207" t="s">
         <v>8</v>
       </c>
       <c r="B57" s="28"/>
-      <c r="C57" s="209">
+      <c r="C57" s="208">
         <f>SUM(C49:C56)</f>
-        <v>149754.72417282569</v>
+        <v>-1327031.4458271747</v>
       </c>
       <c r="D57" s="5"/>
     </row>
-    <row r="58" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9"/>
       <c r="B58" s="8"/>
       <c r="C58" s="10"/>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="214"/>
-      <c r="B59" s="214"/>
-      <c r="C59" s="214"/>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="223"/>
+      <c r="B59" s="223"/>
+      <c r="C59" s="223"/>
       <c r="F59" s="44"/>
     </row>
-    <row r="60" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="215"/>
-      <c r="B60" s="215"/>
-      <c r="C60" s="215"/>
-    </row>
-    <row r="61" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="224"/>
+      <c r="B60" s="224"/>
+      <c r="C60" s="224"/>
+    </row>
+    <row r="61" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
         <v>20</v>
       </c>
       <c r="B61" s="27"/>
       <c r="C61" s="29"/>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="28" t="s">
         <v>23</v>
       </c>
@@ -2343,17 +2344,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="28"/>
       <c r="B63" s="28"/>
       <c r="C63" s="31"/>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="28"/>
       <c r="B64" s="28"/>
       <c r="C64" s="32"/>
     </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="156" t="s">
         <v>0</v>
       </c>
@@ -2363,24 +2364,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="216" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="225" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="217"/>
-      <c r="C66" s="217"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="217"/>
-      <c r="B67" s="217"/>
-      <c r="C67" s="217"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="217"/>
-      <c r="B68" s="217"/>
-      <c r="C68" s="217"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B66" s="226"/>
+      <c r="C66" s="226"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="226"/>
+      <c r="B67" s="226"/>
+      <c r="C67" s="226"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="226"/>
+      <c r="B68" s="226"/>
+      <c r="C68" s="226"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -2408,50 +2409,50 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="10.109375" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="11"/>
+    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="11"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="220">
+      <c r="B1" s="229">
         <v>1500000</v>
       </c>
-      <c r="C1" s="220"/>
+      <c r="C1" s="229"/>
       <c r="D1" s="139" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E1" t="s">
         <v>118</v>
       </c>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
-      <c r="I1" s="223" t="s">
-        <v>140</v>
-      </c>
-      <c r="J1" s="223"/>
-      <c r="K1" s="220">
+      <c r="G1" s="231"/>
+      <c r="H1" s="231"/>
+      <c r="I1" s="232" t="s">
+        <v>135</v>
+      </c>
+      <c r="J1" s="232"/>
+      <c r="K1" s="229">
         <v>1360565.9</v>
       </c>
-      <c r="L1" s="220"/>
-    </row>
-    <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L1" s="229"/>
+    </row>
+    <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
         <v>26</v>
       </c>
@@ -2473,23 +2474,23 @@
       <c r="G2" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="207" t="s">
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
       <c r="I2" s="50" t="s">
         <v>120</v>
       </c>
       <c r="J2" s="50" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="K2" s="50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L2" s="51" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
         <v>31</v>
       </c>
@@ -2534,7 +2535,7 @@
         <v>146174.91749000002</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
@@ -2579,7 +2580,7 @@
         <v>145602.80430999998</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>35</v>
       </c>
@@ -2624,7 +2625,7 @@
         <v>291766.26376</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="58" t="s">
         <v>38</v>
       </c>
@@ -2668,7 +2669,7 @@
       </c>
       <c r="O6" s="180"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>35</v>
       </c>
@@ -2714,7 +2715,7 @@
       </c>
       <c r="O7" s="180"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
         <v>41</v>
       </c>
@@ -2757,7 +2758,7 @@
         <v>145602.80430999998</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>43</v>
       </c>
@@ -2801,7 +2802,7 @@
       </c>
       <c r="O9" s="180"/>
     </row>
-    <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="183" t="s">
         <v>45</v>
       </c>
@@ -2817,7 +2818,7 @@
       <c r="E10" s="187">
         <v>106166.82</v>
       </c>
-      <c r="F10" s="212">
+      <c r="F10" s="211">
         <f t="shared" si="7"/>
         <v>106166.82</v>
       </c>
@@ -2843,7 +2844,7 @@
         <v>145602.80430999998</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>111</v>
       </c>
@@ -2886,7 +2887,7 @@
         <v>144172.52136000001</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
         <v>48</v>
       </c>
@@ -2929,7 +2930,7 @@
         <v>149035.48339000001</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>50</v>
       </c>
@@ -2974,7 +2975,7 @@
         <v>146174.91749000002</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="62" t="s">
         <v>50</v>
       </c>
@@ -3016,7 +3017,7 @@
         <v>256016.29710999998</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>54</v>
       </c>
@@ -3061,7 +3062,7 @@
         <v>315391.53816</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
         <v>57</v>
       </c>
@@ -3106,7 +3107,7 @@
         <v>149035.48339000001</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>60</v>
       </c>
@@ -3146,53 +3147,53 @@
         <v>253501.39815999998</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="229" t="s">
+    <row r="18" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="213" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="230"/>
-      <c r="C18" s="231" t="s">
+      <c r="B18" s="214"/>
+      <c r="C18" s="215" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="232">
+      <c r="D18" s="216">
         <v>5.21</v>
       </c>
-      <c r="E18" s="233">
+      <c r="E18" s="217">
         <v>108669.77</v>
       </c>
-      <c r="F18" s="234"/>
-      <c r="G18" s="235">
+      <c r="F18" s="218"/>
+      <c r="G18" s="219">
         <f t="shared" si="1"/>
         <v>108669.77</v>
       </c>
-      <c r="H18" s="235">
+      <c r="H18" s="219">
         <f t="shared" si="2"/>
         <v>4346.7908000000007</v>
       </c>
-      <c r="I18" s="235">
+      <c r="I18" s="219">
         <f t="shared" si="3"/>
         <v>78150</v>
       </c>
-      <c r="J18" s="235">
+      <c r="J18" s="219">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K18" s="235">
+      <c r="K18" s="219">
         <f t="shared" si="5"/>
         <v>70885.483389999994</v>
       </c>
-      <c r="L18" s="236">
+      <c r="L18" s="220">
         <f t="shared" si="6"/>
         <v>262052.04419000002</v>
       </c>
-      <c r="M18" s="237"/>
-      <c r="N18" s="238" t="s">
-        <v>142</v>
-      </c>
-      <c r="O18" s="237"/>
-      <c r="P18" s="237"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M18" s="221"/>
+      <c r="N18" s="222" t="s">
+        <v>137</v>
+      </c>
+      <c r="O18" s="221"/>
+      <c r="P18" s="221"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>64</v>
       </c>
@@ -3235,7 +3236,7 @@
         <v>211681.87660000002</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="190"/>
       <c r="B20" s="184" t="s">
         <v>115</v>
@@ -3249,7 +3250,7 @@
       <c r="E20" s="187">
         <v>22526.55</v>
       </c>
-      <c r="F20" s="212">
+      <c r="F20" s="211">
         <f>E20</f>
         <v>22526.55</v>
       </c>
@@ -3275,7 +3276,7 @@
         <v>30894.111720000001</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="62"/>
       <c r="B21" s="59" t="s">
         <v>58</v>
@@ -3318,7 +3319,7 @@
         <v>30894.111720000001</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="140"/>
       <c r="B22" s="141"/>
       <c r="C22" s="142" t="s">
@@ -3358,7 +3359,7 @@
         <v>231024.85812000002</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="58"/>
       <c r="B23" s="59" t="s">
         <v>36</v>
@@ -3401,7 +3402,7 @@
         <v>30894.111720000001</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>50</v>
       </c>
@@ -3446,7 +3447,7 @@
         <v>30894.111720000001</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>50</v>
       </c>
@@ -3488,7 +3489,7 @@
         <v>54321.723720000002</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
         <v>64</v>
       </c>
@@ -3531,7 +3532,7 @@
         <v>30894.111720000001</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>64</v>
       </c>
@@ -3578,7 +3579,7 @@
         <v>199401.72</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="66"/>
       <c r="B28" s="65" t="str">
         <f>B7</f>
@@ -3622,7 +3623,7 @@
         <v>30894.111720000001</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="66" t="s">
         <v>54</v>
       </c>
@@ -3667,7 +3668,7 @@
         <v>30894.111720000001</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="67"/>
       <c r="B30" s="67"/>
       <c r="C30" s="68"/>
@@ -3681,7 +3682,7 @@
       <c r="K30" s="71"/>
       <c r="L30" s="71"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="72"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74" t="s">
@@ -3712,68 +3713,68 @@
         <v>3735695.9479999999</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J32" s="22"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="221" t="s">
-        <v>130</v>
-      </c>
-      <c r="B33" s="221"/>
-      <c r="C33" s="221"/>
-      <c r="D33" s="221"/>
-      <c r="E33" s="221"/>
-      <c r="F33" s="221"/>
-      <c r="G33" s="221"/>
-      <c r="H33" s="221"/>
-      <c r="I33" s="221"/>
-      <c r="J33" s="221"/>
-      <c r="K33" s="221"/>
-      <c r="L33" s="221"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="221"/>
-      <c r="B34" s="221"/>
-      <c r="C34" s="221"/>
-      <c r="D34" s="221"/>
-      <c r="E34" s="221"/>
-      <c r="F34" s="221"/>
-      <c r="G34" s="221"/>
-      <c r="H34" s="221"/>
-      <c r="I34" s="221"/>
-      <c r="J34" s="221"/>
-      <c r="K34" s="221"/>
-      <c r="L34" s="221"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="221"/>
-      <c r="B35" s="221"/>
-      <c r="C35" s="221"/>
-      <c r="D35" s="221"/>
-      <c r="E35" s="221"/>
-      <c r="F35" s="221"/>
-      <c r="G35" s="221"/>
-      <c r="H35" s="221"/>
-      <c r="I35" s="221"/>
-      <c r="J35" s="221"/>
-      <c r="K35" s="221"/>
-      <c r="L35" s="221"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="221"/>
-      <c r="B36" s="221"/>
-      <c r="C36" s="221"/>
-      <c r="D36" s="221"/>
-      <c r="E36" s="221"/>
-      <c r="F36" s="221"/>
-      <c r="G36" s="221"/>
-      <c r="H36" s="221"/>
-      <c r="I36" s="221"/>
-      <c r="J36" s="221"/>
-      <c r="K36" s="221"/>
-      <c r="L36" s="221"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="230" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="230"/>
+      <c r="C33" s="230"/>
+      <c r="D33" s="230"/>
+      <c r="E33" s="230"/>
+      <c r="F33" s="230"/>
+      <c r="G33" s="230"/>
+      <c r="H33" s="230"/>
+      <c r="I33" s="230"/>
+      <c r="J33" s="230"/>
+      <c r="K33" s="230"/>
+      <c r="L33" s="230"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="230"/>
+      <c r="B34" s="230"/>
+      <c r="C34" s="230"/>
+      <c r="D34" s="230"/>
+      <c r="E34" s="230"/>
+      <c r="F34" s="230"/>
+      <c r="G34" s="230"/>
+      <c r="H34" s="230"/>
+      <c r="I34" s="230"/>
+      <c r="J34" s="230"/>
+      <c r="K34" s="230"/>
+      <c r="L34" s="230"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="230"/>
+      <c r="B35" s="230"/>
+      <c r="C35" s="230"/>
+      <c r="D35" s="230"/>
+      <c r="E35" s="230"/>
+      <c r="F35" s="230"/>
+      <c r="G35" s="230"/>
+      <c r="H35" s="230"/>
+      <c r="I35" s="230"/>
+      <c r="J35" s="230"/>
+      <c r="K35" s="230"/>
+      <c r="L35" s="230"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="230"/>
+      <c r="B36" s="230"/>
+      <c r="C36" s="230"/>
+      <c r="D36" s="230"/>
+      <c r="E36" s="230"/>
+      <c r="F36" s="230"/>
+      <c r="G36" s="230"/>
+      <c r="H36" s="230"/>
+      <c r="I36" s="230"/>
+      <c r="J36" s="230"/>
+      <c r="K36" s="230"/>
+      <c r="L36" s="230"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
@@ -3793,45 +3794,45 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="6" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="224" t="s">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="233" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="225"/>
-      <c r="C1" s="225"/>
-      <c r="D1" s="225"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225"/>
-      <c r="K1" s="225"/>
-      <c r="L1" s="225"/>
-      <c r="M1" s="225"/>
-      <c r="N1" s="226"/>
+      <c r="B1" s="234"/>
+      <c r="C1" s="234"/>
+      <c r="D1" s="234"/>
+      <c r="E1" s="234"/>
+      <c r="F1" s="234"/>
+      <c r="G1" s="234"/>
+      <c r="H1" s="234"/>
+      <c r="I1" s="234"/>
+      <c r="J1" s="234"/>
+      <c r="K1" s="234"/>
+      <c r="L1" s="234"/>
+      <c r="M1" s="234"/>
+      <c r="N1" s="235"/>
       <c r="O1" s="76"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="77"/>
       <c r="B2" s="77"/>
       <c r="C2" s="162"/>
@@ -3849,7 +3850,7 @@
       <c r="O2" s="78"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
       <c r="C3" s="164"/>
@@ -3867,7 +3868,7 @@
       <c r="O3" s="78"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
       <c r="C4" s="164"/>
@@ -3887,7 +3888,7 @@
       <c r="O4" s="78"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="80"/>
       <c r="B5" s="80"/>
       <c r="C5" s="164"/>
@@ -3905,7 +3906,7 @@
       <c r="O5" s="78"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="80"/>
       <c r="B6" s="80"/>
       <c r="C6" s="162"/>
@@ -3923,12 +3924,12 @@
       <c r="O6" s="78"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="81"/>
       <c r="B7" s="81" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="213">
+      <c r="C7" s="212">
         <v>639397.63</v>
       </c>
       <c r="D7" s="28"/>
@@ -3941,7 +3942,7 @@
       <c r="I7" s="162"/>
       <c r="J7" s="162" t="str">
         <f>'detalle y gastos'!C7</f>
-        <v>Vto. 15/10</v>
+        <v>Vto. 14/11</v>
       </c>
       <c r="K7" s="162"/>
       <c r="L7" s="162"/>
@@ -3950,7 +3951,7 @@
       <c r="O7" s="78"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="81"/>
       <c r="B8" s="80" t="s">
         <v>78</v>
@@ -3966,16 +3967,16 @@
         <f>C8-J38</f>
         <v>-196408.73539999995</v>
       </c>
-      <c r="L8" s="228">
+      <c r="L8" s="237">
         <f>C7-J38</f>
         <v>442988.89460000006</v>
       </c>
-      <c r="M8" s="228"/>
+      <c r="M8" s="237"/>
       <c r="N8" s="84"/>
       <c r="O8" s="78"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="87" t="s">
         <v>79</v>
       </c>
@@ -4020,7 +4021,7 @@
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="98">
         <v>1</v>
       </c>
@@ -4076,7 +4077,7 @@
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="99">
         <v>2</v>
       </c>
@@ -4132,7 +4133,7 @@
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="98">
         <v>3</v>
       </c>
@@ -4191,7 +4192,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="98">
         <v>4</v>
       </c>
@@ -4247,7 +4248,7 @@
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="98">
         <v>6</v>
       </c>
@@ -4303,7 +4304,7 @@
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="98">
         <v>7</v>
       </c>
@@ -4358,7 +4359,7 @@
         <v>178533.15994514001</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="98">
         <v>8</v>
       </c>
@@ -4413,7 +4414,7 @@
         <v>176567.83490406006</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="98">
         <v>9</v>
       </c>
@@ -4468,7 +4469,7 @@
         <v>170448.72054513998</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="98">
         <v>10</v>
       </c>
@@ -4523,7 +4524,7 @@
         <v>175202.59524784001</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="98">
         <v>11</v>
       </c>
@@ -4578,7 +4579,7 @@
         <v>196818.70059865998</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="98">
         <v>12</v>
       </c>
@@ -4633,7 +4634,7 @@
         <v>188159.90810406004</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="98">
         <v>13</v>
       </c>
@@ -4688,7 +4689,7 @@
         <v>289012.30364514003</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="98">
         <v>14</v>
       </c>
@@ -4743,7 +4744,7 @@
         <v>342473.17934783996</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="98">
         <v>15</v>
       </c>
@@ -4798,7 +4799,7 @@
         <v>182928.84589866002</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="98">
         <v>16</v>
       </c>
@@ -4853,7 +4854,7 @@
         <v>280629.93284784001</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="98">
         <v>17</v>
       </c>
@@ -4908,7 +4909,7 @@
         <v>292240.82019866002</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="98">
         <v>18</v>
       </c>
@@ -4963,7 +4964,7 @@
         <v>270273.23720039992</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="98">
         <v>19</v>
       </c>
@@ -5007,7 +5008,7 @@
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="98">
         <v>20</v>
       </c>
@@ -5046,7 +5047,7 @@
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="98"/>
       <c r="B29" s="90"/>
       <c r="C29" s="159" t="s">
@@ -5078,7 +5079,7 @@
         <v>235809.13818168003</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="98"/>
       <c r="B30" s="90"/>
       <c r="C30" s="170" t="s">
@@ -5110,7 +5111,7 @@
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="98"/>
       <c r="B31" s="90"/>
       <c r="C31" s="170" t="s">
@@ -5142,7 +5143,7 @@
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="98"/>
       <c r="B32" s="90"/>
       <c r="C32" s="130" t="s">
@@ -5174,7 +5175,7 @@
         <v>59106.003781680003</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="98"/>
       <c r="B33" s="90"/>
       <c r="C33" s="130" t="s">
@@ -5206,7 +5207,7 @@
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="98"/>
       <c r="B34" s="90"/>
       <c r="C34" s="130" t="s">
@@ -5238,7 +5239,7 @@
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="98">
         <v>21</v>
       </c>
@@ -5277,7 +5278,7 @@
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="98">
         <v>22</v>
       </c>
@@ -5316,7 +5317,7 @@
         <v>35678.391781680002</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="98">
         <v>23</v>
       </c>
@@ -5346,7 +5347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="98">
         <v>24</v>
       </c>
@@ -5374,7 +5375,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="78"/>
       <c r="C39" s="91"/>
       <c r="D39" s="92"/>
@@ -5399,41 +5400,41 @@
       <c r="N39" s="93"/>
       <c r="O39" s="79"/>
     </row>
-    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="C40" s="227"/>
-      <c r="D40" s="225"/>
-      <c r="E40" s="225"/>
-      <c r="F40" s="225"/>
-      <c r="G40" s="225"/>
-      <c r="H40" s="225"/>
-      <c r="I40" s="225"/>
-      <c r="J40" s="225"/>
-      <c r="K40" s="225"/>
-      <c r="L40" s="225"/>
-      <c r="M40" s="225"/>
-      <c r="N40" s="225"/>
+      <c r="C40" s="236"/>
+      <c r="D40" s="234"/>
+      <c r="E40" s="234"/>
+      <c r="F40" s="234"/>
+      <c r="G40" s="234"/>
+      <c r="H40" s="234"/>
+      <c r="I40" s="234"/>
+      <c r="J40" s="234"/>
+      <c r="K40" s="234"/>
+      <c r="L40" s="234"/>
+      <c r="M40" s="234"/>
+      <c r="N40" s="234"/>
       <c r="O40" s="95"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H41" s="79"/>
       <c r="J41" s="96"/>
       <c r="K41" s="96"/>
       <c r="L41" s="96"/>
       <c r="N41" s="97"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L44" s="152"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L45" s="96"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E46" s="153"/>
       <c r="F46" s="153"/>
       <c r="G46" s="153"/>
